--- a/features.xlsx
+++ b/features.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="205" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="419" uniqueCount="38">
   <si>
     <t>TestNumber</t>
   </si>
@@ -101,6 +101,33 @@
   <si>
     <t>TCiclo</t>
   </si>
+  <si>
+    <t>inicioCiclo</t>
+  </si>
+  <si>
+    <t>fimCiclo</t>
+  </si>
+  <si>
+    <t>TRelativoVmax</t>
+  </si>
+  <si>
+    <t>TRelativoImax</t>
+  </si>
+  <si>
+    <t>TRelativoRmax</t>
+  </si>
+  <si>
+    <t>dVMax</t>
+  </si>
+  <si>
+    <t>dIMax</t>
+  </si>
+  <si>
+    <t>dPMax</t>
+  </si>
+  <si>
+    <t>dRMax</t>
+  </si>
 </sst>
 </file>
 
@@ -145,7 +172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q186"/>
+  <dimension ref="A1:Z186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="true"/>
@@ -165,6 +192,15 @@
     <col min="15" max="15" width="12.5546875" customWidth="true"/>
     <col min="16" max="16" width="12.5546875" customWidth="true"/>
     <col min="17" max="17" width="12.5546875" customWidth="true"/>
+    <col min="18" max="18" width="12.5546875" customWidth="true"/>
+    <col min="19" max="19" width="12.5546875" customWidth="true"/>
+    <col min="20" max="20" width="13.21875" customWidth="true"/>
+    <col min="21" max="21" width="12.6640625" customWidth="true"/>
+    <col min="22" max="22" width="13.21875" customWidth="true"/>
+    <col min="23" max="23" width="8.5546875" customWidth="true"/>
+    <col min="24" max="24" width="7.5546875" customWidth="true"/>
+    <col min="25" max="25" width="11.5546875" customWidth="true"/>
+    <col min="26" max="26" width="15.5546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -217,7 +253,34 @@
         <v>27</v>
       </c>
       <c r="Q1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="S1" s="0" t="s">
         <v>28</v>
+      </c>
+      <c r="T1" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="V1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="W1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="X1" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y1" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z1" s="0" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="2">
@@ -268,7 +331,34 @@
         <v>0.049921875000000004</v>
       </c>
       <c r="Q2" s="0">
+        <v>0.024023437500000001</v>
+      </c>
+      <c r="R2" s="0">
+        <v>0.0481640625</v>
+      </c>
+      <c r="S2" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T2" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U2" s="0">
+        <v>0.014101562499999998</v>
+      </c>
+      <c r="V2" s="0">
+        <v>0.025898437500000003</v>
+      </c>
+      <c r="W2" s="0">
+        <v>0.28350799999999998</v>
+      </c>
+      <c r="X2" s="0">
+        <v>402.84700000000021</v>
+      </c>
+      <c r="Y2" s="0">
+        <v>770.13897130599935</v>
+      </c>
+      <c r="Z2" s="0">
+        <v>0.012138380782745397</v>
       </c>
     </row>
     <row r="3">
@@ -319,7 +409,34 @@
         <v>0.063867187500000006</v>
       </c>
       <c r="Q3" s="0">
+        <v>0.038828124999999998</v>
+      </c>
+      <c r="R3" s="0">
+        <v>0.062460937500000001</v>
+      </c>
+      <c r="S3" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T3" s="0">
+        <v>0.010000000000000002</v>
+      </c>
+      <c r="U3" s="0">
+        <v>0.014101562500000005</v>
+      </c>
+      <c r="V3" s="0">
+        <v>0.025039062500000007</v>
+      </c>
+      <c r="W3" s="0">
+        <v>0.28839100000000001</v>
+      </c>
+      <c r="X3" s="0">
+        <v>347.94000000000005</v>
+      </c>
+      <c r="Y3" s="0">
+        <v>772.40805613400016</v>
+      </c>
+      <c r="Z3" s="0">
+        <v>0.016199931059953036</v>
       </c>
     </row>
     <row r="4">
@@ -370,7 +487,34 @@
         <v>0.033789062500000001</v>
       </c>
       <c r="Q4" s="0">
+        <v>0.034375000000000003</v>
+      </c>
+      <c r="R4" s="0">
+        <v>0.058046874999999998</v>
+      </c>
+      <c r="S4" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T4" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U4" s="0">
+        <v>0.0146484375</v>
+      </c>
+      <c r="V4" s="0">
+        <v>-0.00058593750000000139</v>
+      </c>
+      <c r="W4" s="0">
+        <v>0.28228799999999998</v>
+      </c>
+      <c r="X4" s="0">
+        <v>384.54500000000007</v>
+      </c>
+      <c r="Y4" s="0">
+        <v>792.40563442600023</v>
+      </c>
+      <c r="Z4" s="0">
+        <v>0.061380492205549968</v>
       </c>
     </row>
     <row r="5">
@@ -421,7 +565,34 @@
         <v>0.024335937500000002</v>
       </c>
       <c r="Q5" s="0">
+        <v>0.024453124999999999</v>
+      </c>
+      <c r="R5" s="0">
+        <v>0.048593749999999998</v>
+      </c>
+      <c r="S5" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T5" s="0">
+        <v>0.010507812500000005</v>
+      </c>
+      <c r="U5" s="0">
+        <v>0.014609375000000001</v>
+      </c>
+      <c r="V5" s="0">
+        <v>-0.0001171874999999975</v>
+      </c>
+      <c r="W5" s="0">
+        <v>0.28900100000000001</v>
+      </c>
+      <c r="X5" s="0">
+        <v>384.52800000000002</v>
+      </c>
+      <c r="Y5" s="0">
+        <v>757.87909787499939</v>
+      </c>
+      <c r="Z5" s="0">
+        <v>0.016419739620687341</v>
       </c>
     </row>
     <row r="6">
@@ -472,7 +643,34 @@
         <v>0.046601562499999999</v>
       </c>
       <c r="Q6" s="0">
+        <v>0.021523437499999999</v>
+      </c>
+      <c r="R6" s="0">
+        <v>0.045156250000000002</v>
+      </c>
+      <c r="S6" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T6" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U6" s="0">
+        <v>0.017148437500000002</v>
+      </c>
+      <c r="V6" s="0">
+        <v>0.025078125</v>
+      </c>
+      <c r="W6" s="0">
+        <v>0.26946999999999999</v>
+      </c>
+      <c r="X6" s="0">
+        <v>366.22899999999981</v>
+      </c>
+      <c r="Y6" s="0">
+        <v>746.46685336799965</v>
+      </c>
+      <c r="Z6" s="0">
+        <v>0.018483989905611911</v>
       </c>
     </row>
     <row r="7">
@@ -523,7 +721,34 @@
         <v>0.063125000000000001</v>
       </c>
       <c r="Q7" s="0">
+        <v>0.037617187500000003</v>
+      </c>
+      <c r="R7" s="0">
+        <v>0.061757812500000002</v>
+      </c>
+      <c r="S7" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T7" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U7" s="0">
+        <v>0.017109374999999996</v>
+      </c>
+      <c r="V7" s="0">
+        <v>0.025507812499999998</v>
+      </c>
+      <c r="W7" s="0">
+        <v>0.28961099999999995</v>
+      </c>
+      <c r="X7" s="0">
+        <v>402.86900000000014</v>
+      </c>
+      <c r="Y7" s="0">
+        <v>763.99617609100005</v>
+      </c>
+      <c r="Z7" s="0">
+        <v>0.0096110953460419798</v>
       </c>
     </row>
     <row r="8">
@@ -574,7 +799,34 @@
         <v>0.052656250000000002</v>
       </c>
       <c r="Q8" s="0">
+        <v>0.027148437500000001</v>
+      </c>
+      <c r="R8" s="0">
+        <v>0.051289062500000003</v>
+      </c>
+      <c r="S8" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T8" s="0">
+        <v>0.010507812500000002</v>
+      </c>
+      <c r="U8" s="0">
+        <v>0.0151171875</v>
+      </c>
+      <c r="V8" s="0">
+        <v>0.025507812500000001</v>
+      </c>
+      <c r="W8" s="0">
+        <v>0.28686500000000004</v>
+      </c>
+      <c r="X8" s="0">
+        <v>384.54700000000003</v>
+      </c>
+      <c r="Y8" s="0">
+        <v>749.72822682599963</v>
+      </c>
+      <c r="Z8" s="0">
+        <v>0.03761440230284975</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +877,34 @@
         <v>0.049218749999999999</v>
       </c>
       <c r="Q9" s="0">
+        <v>0.02375</v>
+      </c>
+      <c r="R9" s="0">
+        <v>0.047890624999999999</v>
+      </c>
+      <c r="S9" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T9" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U9" s="0">
+        <v>0.014609375000000001</v>
+      </c>
+      <c r="V9" s="0">
+        <v>0.025468749999999998</v>
+      </c>
+      <c r="W9" s="0">
+        <v>0.27191100000000001</v>
+      </c>
+      <c r="X9" s="0">
+        <v>366.23500000000013</v>
+      </c>
+      <c r="Y9" s="0">
+        <v>777.45598713800018</v>
+      </c>
+      <c r="Z9" s="0">
+        <v>0.0097580344680125355</v>
       </c>
     </row>
     <row r="10">
@@ -676,7 +955,34 @@
         <v>0.065000000000000002</v>
       </c>
       <c r="Q10" s="0">
+        <v>0.039804687499999998</v>
+      </c>
+      <c r="R10" s="0">
+        <v>0.063437500000000008</v>
+      </c>
+      <c r="S10" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T10" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U10" s="0">
+        <v>0.018164062500000001</v>
+      </c>
+      <c r="V10" s="0">
+        <v>0.025195312500000004</v>
+      </c>
+      <c r="W10" s="0">
+        <v>0.28320299999999998</v>
+      </c>
+      <c r="X10" s="0">
+        <v>366.23500000000013</v>
+      </c>
+      <c r="Y10" s="0">
+        <v>781.71107254800063</v>
+      </c>
+      <c r="Z10" s="0">
+        <v>0.012291018334008953</v>
       </c>
     </row>
     <row r="11">
@@ -727,7 +1033,34 @@
         <v>0.062031250000000003</v>
       </c>
       <c r="Q11" s="0">
+        <v>0.036757812500000001</v>
+      </c>
+      <c r="R11" s="0">
+        <v>0.060390625000000003</v>
+      </c>
+      <c r="S11" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T11" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U11" s="0">
+        <v>0.014609375000000001</v>
+      </c>
+      <c r="V11" s="0">
+        <v>0.025273437500000002</v>
+      </c>
+      <c r="W11" s="0">
+        <v>0.28350799999999998</v>
+      </c>
+      <c r="X11" s="0">
+        <v>366.22200000000009</v>
+      </c>
+      <c r="Y11" s="0">
+        <v>754.26571249300014</v>
+      </c>
+      <c r="Z11" s="0">
+        <v>0.010593886982163493</v>
       </c>
     </row>
     <row r="12">
@@ -778,7 +1111,34 @@
         <v>0.064023437500000002</v>
       </c>
       <c r="Q12" s="0">
+        <v>0.038984375000000002</v>
+      </c>
+      <c r="R12" s="0">
+        <v>0.062656249999999997</v>
+      </c>
+      <c r="S12" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T12" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U12" s="0">
+        <v>0.013124999999999998</v>
+      </c>
+      <c r="V12" s="0">
+        <v>0.025039062500000001</v>
+      </c>
+      <c r="W12" s="0">
+        <v>0.26824899999999996</v>
+      </c>
+      <c r="X12" s="0">
+        <v>384.53300000000013</v>
+      </c>
+      <c r="Y12" s="0">
+        <v>781.6211288720001</v>
+      </c>
+      <c r="Z12" s="0">
+        <v>0.017043374180892055</v>
       </c>
     </row>
     <row r="13">
@@ -829,7 +1189,34 @@
         <v>0.053515625000000004</v>
       </c>
       <c r="Q13" s="0">
+        <v>0.028554687500000002</v>
+      </c>
+      <c r="R13" s="0">
+        <v>0.052226562500000004</v>
+      </c>
+      <c r="S13" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T13" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U13" s="0">
+        <v>0.013593750000000002</v>
+      </c>
+      <c r="V13" s="0">
+        <v>0.024960937500000002</v>
+      </c>
+      <c r="W13" s="0">
+        <v>0.27282699999999999</v>
+      </c>
+      <c r="X13" s="0">
+        <v>402.84299999999996</v>
+      </c>
+      <c r="Y13" s="0">
+        <v>729.24586604700016</v>
+      </c>
+      <c r="Z13" s="0">
+        <v>0.012332799070084222</v>
       </c>
     </row>
     <row r="14">
@@ -880,7 +1267,34 @@
         <v>0.037890625000000004</v>
       </c>
       <c r="Q14" s="0">
+        <v>0.038515624999999998</v>
+      </c>
+      <c r="R14" s="0">
+        <v>0.062226562499999999</v>
+      </c>
+      <c r="S14" s="0">
         <v>0.023710937500000001</v>
+      </c>
+      <c r="T14" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U14" s="0">
+        <v>0.013632812500000001</v>
+      </c>
+      <c r="V14" s="0">
+        <v>-0.00062499999999999362</v>
+      </c>
+      <c r="W14" s="0">
+        <v>0.28747599999999995</v>
+      </c>
+      <c r="X14" s="0">
+        <v>366.23599999999988</v>
+      </c>
+      <c r="Y14" s="0">
+        <v>716.50680113599992</v>
+      </c>
+      <c r="Z14" s="0">
+        <v>0.033380564733293296</v>
       </c>
     </row>
     <row r="15">
@@ -931,7 +1345,34 @@
         <v>0.048554687499999999</v>
       </c>
       <c r="Q15" s="0">
+        <v>0.02359375</v>
+      </c>
+      <c r="R15" s="0">
+        <v>0.047265624999999999</v>
+      </c>
+      <c r="S15" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T15" s="0">
+        <v>0.010039062499999998</v>
+      </c>
+      <c r="U15" s="0">
+        <v>0.015664062500000003</v>
+      </c>
+      <c r="V15" s="0">
+        <v>0.024960937499999999</v>
+      </c>
+      <c r="W15" s="0">
+        <v>0.28472900000000001</v>
+      </c>
+      <c r="X15" s="0">
+        <v>384.53199999999993</v>
+      </c>
+      <c r="Y15" s="0">
+        <v>781.65203279599973</v>
+      </c>
+      <c r="Z15" s="0">
+        <v>0.031412170597581113</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +1423,34 @@
         <v>0.061328125000000004</v>
       </c>
       <c r="Q16" s="0">
+        <v>0.036210937499999998</v>
+      </c>
+      <c r="R16" s="0">
+        <v>0.0598828125</v>
+      </c>
+      <c r="S16" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T16" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U16" s="0">
+        <v>0.015664062500000006</v>
+      </c>
+      <c r="V16" s="0">
+        <v>0.025117187500000006</v>
+      </c>
+      <c r="W16" s="0">
+        <v>0.28533999999999998</v>
+      </c>
+      <c r="X16" s="0">
+        <v>384.54600000000028</v>
+      </c>
+      <c r="Y16" s="0">
+        <v>755.4165667240004</v>
+      </c>
+      <c r="Z16" s="0">
+        <v>0.040713163392491918</v>
       </c>
     </row>
     <row r="17">
@@ -1033,7 +1501,34 @@
         <v>0.055468750000000004</v>
       </c>
       <c r="Q17" s="0">
+        <v>0.030468749999999999</v>
+      </c>
+      <c r="R17" s="0">
+        <v>0.054140624999999998</v>
+      </c>
+      <c r="S17" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T17" s="0">
+        <v>0.010039062500000005</v>
+      </c>
+      <c r="U17" s="0">
+        <v>0.013632812500000004</v>
+      </c>
+      <c r="V17" s="0">
+        <v>0.025000000000000005</v>
+      </c>
+      <c r="W17" s="0">
+        <v>0.28289800000000004</v>
+      </c>
+      <c r="X17" s="0">
+        <v>384.54700000000003</v>
+      </c>
+      <c r="Y17" s="0">
+        <v>765.46309170899985</v>
+      </c>
+      <c r="Z17" s="0">
+        <v>0.28104861919430668</v>
       </c>
     </row>
     <row r="18">
@@ -1084,7 +1579,34 @@
         <v>0.0621875</v>
       </c>
       <c r="Q18" s="0">
+        <v>0.037226562499999998</v>
+      </c>
+      <c r="R18" s="0">
+        <v>0.060898437499999999</v>
+      </c>
+      <c r="S18" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T18" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U18" s="0">
+        <v>0.014648437500000007</v>
+      </c>
+      <c r="V18" s="0">
+        <v>0.024960937500000002</v>
+      </c>
+      <c r="W18" s="0">
+        <v>0.26092499999999996</v>
+      </c>
+      <c r="X18" s="0">
+        <v>421.14899999999994</v>
+      </c>
+      <c r="Y18" s="0">
+        <v>716.85607173200015</v>
+      </c>
+      <c r="Z18" s="0">
+        <v>0.015681650531139624</v>
       </c>
     </row>
     <row r="19">
@@ -1135,7 +1657,34 @@
         <v>0.056835937500000003</v>
       </c>
       <c r="Q19" s="0">
+        <v>0.031796875000000002</v>
+      </c>
+      <c r="R19" s="0">
+        <v>0.055468750000000004</v>
+      </c>
+      <c r="S19" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T19" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U19" s="0">
+        <v>0.013124999999999998</v>
+      </c>
+      <c r="V19" s="0">
+        <v>0.025039062500000001</v>
+      </c>
+      <c r="W19" s="0">
+        <v>0.26184000000000007</v>
+      </c>
+      <c r="X19" s="0">
+        <v>439.49199999999973</v>
+      </c>
+      <c r="Y19" s="0">
+        <v>752.06999235600051</v>
+      </c>
+      <c r="Z19" s="0">
+        <v>0.048615084512761607</v>
       </c>
     </row>
     <row r="20">
@@ -1186,7 +1735,34 @@
         <v>0.0287890625</v>
       </c>
       <c r="Q20" s="0">
+        <v>0.029375000000000002</v>
+      </c>
+      <c r="R20" s="0">
+        <v>0.053046875</v>
+      </c>
+      <c r="S20" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T20" s="0">
+        <v>0.010039062499999998</v>
+      </c>
+      <c r="U20" s="0">
+        <v>0.014140625</v>
+      </c>
+      <c r="V20" s="0">
+        <v>-0.00058593750000000139</v>
+      </c>
+      <c r="W20" s="0">
+        <v>0.26916500000000004</v>
+      </c>
+      <c r="X20" s="0">
+        <v>366.24999999999955</v>
+      </c>
+      <c r="Y20" s="0">
+        <v>762.42194301300015</v>
+      </c>
+      <c r="Z20" s="0">
+        <v>0.027094176268970142</v>
       </c>
     </row>
     <row r="21">
@@ -1237,7 +1813,34 @@
         <v>0.046015624999999998</v>
       </c>
       <c r="Q21" s="0">
+        <v>0.020937500000000001</v>
+      </c>
+      <c r="R21" s="0">
+        <v>0.044609375</v>
+      </c>
+      <c r="S21" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T21" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U21" s="0">
+        <v>0.0161328125</v>
+      </c>
+      <c r="V21" s="0">
+        <v>0.025078124999999996</v>
+      </c>
+      <c r="W21" s="0">
+        <v>0.25970400000000005</v>
+      </c>
+      <c r="X21" s="0">
+        <v>347.9399999999996</v>
+      </c>
+      <c r="Y21" s="0">
+        <v>717.63404893300003</v>
+      </c>
+      <c r="Z21" s="0">
+        <v>0.024278985037541671</v>
       </c>
     </row>
     <row r="22">
@@ -1288,7 +1891,34 @@
         <v>0.060624999999999998</v>
       </c>
       <c r="Q22" s="0">
+        <v>0.035507812499999999</v>
+      </c>
+      <c r="R22" s="0">
+        <v>0.059179687500000001</v>
+      </c>
+      <c r="S22" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T22" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U22" s="0">
+        <v>0.017148437500000002</v>
+      </c>
+      <c r="V22" s="0">
+        <v>0.025117187499999999</v>
+      </c>
+      <c r="W22" s="0">
+        <v>0.26122999999999996</v>
+      </c>
+      <c r="X22" s="0">
+        <v>366.22700000000009</v>
+      </c>
+      <c r="Y22" s="0">
+        <v>746.41148292000025</v>
+      </c>
+      <c r="Z22" s="0">
+        <v>0.0082443675337928977</v>
       </c>
     </row>
     <row r="23">
@@ -1339,7 +1969,34 @@
         <v>0.0592578125</v>
       </c>
       <c r="Q23" s="0">
+        <v>0.034101562500000002</v>
+      </c>
+      <c r="R23" s="0">
+        <v>0.057773437500000004</v>
+      </c>
+      <c r="S23" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T23" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U23" s="0">
+        <v>0.015117187499999997</v>
+      </c>
+      <c r="V23" s="0">
+        <v>0.025156249999999998</v>
+      </c>
+      <c r="W23" s="0">
+        <v>0.26336599999999999</v>
+      </c>
+      <c r="X23" s="0">
+        <v>384.54599999999982</v>
+      </c>
+      <c r="Y23" s="0">
+        <v>762.07675161999987</v>
+      </c>
+      <c r="Z23" s="0">
+        <v>0.013624533568407215</v>
       </c>
     </row>
     <row r="24">
@@ -1390,7 +2047,34 @@
         <v>0.050585937500000004</v>
       </c>
       <c r="Q24" s="0">
+        <v>0.025625000000000002</v>
+      </c>
+      <c r="R24" s="0">
+        <v>0.049335937500000003</v>
+      </c>
+      <c r="S24" s="0">
         <v>0.023710937500000001</v>
+      </c>
+      <c r="T24" s="0">
+        <v>0.010078125</v>
+      </c>
+      <c r="U24" s="0">
+        <v>0.016171875000000002</v>
+      </c>
+      <c r="V24" s="0">
+        <v>0.024960937500000002</v>
+      </c>
+      <c r="W24" s="0">
+        <v>0.26489299999999999</v>
+      </c>
+      <c r="X24" s="0">
+        <v>366.22500000000014</v>
+      </c>
+      <c r="Y24" s="0">
+        <v>745.99390835400027</v>
+      </c>
+      <c r="Z24" s="0">
+        <v>0.02138741506694735</v>
       </c>
     </row>
     <row r="25">
@@ -1441,7 +2125,34 @@
         <v>0.065273437500000003</v>
       </c>
       <c r="Q25" s="0">
+        <v>0.040312500000000001</v>
+      </c>
+      <c r="R25" s="0">
+        <v>0.063984374999999996</v>
+      </c>
+      <c r="S25" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T25" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U25" s="0">
+        <v>0.014140624999999997</v>
+      </c>
+      <c r="V25" s="0">
+        <v>0.024960937500000002</v>
+      </c>
+      <c r="W25" s="0">
+        <v>0.25848400000000005</v>
+      </c>
+      <c r="X25" s="0">
+        <v>402.85500000000002</v>
+      </c>
+      <c r="Y25" s="0">
+        <v>756.56952619599952</v>
+      </c>
+      <c r="Z25" s="0">
+        <v>0.012610403831727962</v>
       </c>
     </row>
     <row r="26">
@@ -1492,7 +2203,34 @@
         <v>0.036640625000000003</v>
       </c>
       <c r="Q26" s="0">
+        <v>0.037265625000000004</v>
+      </c>
+      <c r="R26" s="0">
+        <v>0.060937499999999999</v>
+      </c>
+      <c r="S26" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T26" s="0">
+        <v>0.010039062499999994</v>
+      </c>
+      <c r="U26" s="0">
+        <v>0.016132812499999996</v>
+      </c>
+      <c r="V26" s="0">
+        <v>-0.00062500000000000056</v>
+      </c>
+      <c r="W26" s="0">
+        <v>0.25940000000000002</v>
+      </c>
+      <c r="X26" s="0">
+        <v>402.85800000000017</v>
+      </c>
+      <c r="Y26" s="0">
+        <v>746.36185411299994</v>
+      </c>
+      <c r="Z26" s="0">
+        <v>0.01357836961871055</v>
       </c>
     </row>
     <row r="27">
@@ -1543,7 +2281,34 @@
         <v>0.063203124999999999</v>
       </c>
       <c r="Q27" s="0">
+        <v>0.038203124999999998</v>
+      </c>
+      <c r="R27" s="0">
+        <v>0.061874999999999999</v>
+      </c>
+      <c r="S27" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T27" s="0">
+        <v>0.010078125</v>
+      </c>
+      <c r="U27" s="0">
+        <v>0.015156250000000003</v>
+      </c>
+      <c r="V27" s="0">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="W27" s="0">
+        <v>0.26519800000000004</v>
+      </c>
+      <c r="X27" s="0">
+        <v>421.16699999999992</v>
+      </c>
+      <c r="Y27" s="0">
+        <v>737.47307665599919</v>
+      </c>
+      <c r="Z27" s="0">
+        <v>0.064223986029312702</v>
       </c>
     </row>
     <row r="28">
@@ -1594,7 +2359,34 @@
         <v>0.056835937500000003</v>
       </c>
       <c r="Q28" s="0">
+        <v>0.031796875000000002</v>
+      </c>
+      <c r="R28" s="0">
+        <v>0.055468750000000004</v>
+      </c>
+      <c r="S28" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T28" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U28" s="0">
+        <v>0.014140624999999997</v>
+      </c>
+      <c r="V28" s="0">
+        <v>0.025039062500000001</v>
+      </c>
+      <c r="W28" s="0">
+        <v>0.25970399999999999</v>
+      </c>
+      <c r="X28" s="0">
+        <v>347.92899999999963</v>
+      </c>
+      <c r="Y28" s="0">
+        <v>743.62532328400039</v>
+      </c>
+      <c r="Z28" s="0">
+        <v>0.27804046229685558</v>
       </c>
     </row>
     <row r="29">
@@ -1645,7 +2437,34 @@
         <v>0.064453125</v>
       </c>
       <c r="Q29" s="0">
+        <v>0.039414062499999999</v>
+      </c>
+      <c r="R29" s="0">
+        <v>0.063046875000000002</v>
+      </c>
+      <c r="S29" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T29" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U29" s="0">
+        <v>0.015117187500000004</v>
+      </c>
+      <c r="V29" s="0">
+        <v>0.025039062500000001</v>
+      </c>
+      <c r="W29" s="0">
+        <v>0.26123099999999999</v>
+      </c>
+      <c r="X29" s="0">
+        <v>384.54299999999989</v>
+      </c>
+      <c r="Y29" s="0">
+        <v>722.37816185599922</v>
+      </c>
+      <c r="Z29" s="0">
+        <v>0.015470825954359037</v>
       </c>
     </row>
     <row r="30">
@@ -1696,7 +2515,34 @@
         <v>0.065625000000000003</v>
       </c>
       <c r="Q30" s="0">
+        <v>0.040078124999999999</v>
+      </c>
+      <c r="R30" s="0">
+        <v>0.064218750000000005</v>
+      </c>
+      <c r="S30" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T30" s="0">
+        <v>0.010507812500000005</v>
+      </c>
+      <c r="U30" s="0">
+        <v>0.014609375000000001</v>
+      </c>
+      <c r="V30" s="0">
+        <v>0.025546875000000004</v>
+      </c>
+      <c r="W30" s="0">
+        <v>0.27862599999999998</v>
+      </c>
+      <c r="X30" s="0">
+        <v>384.54100000000017</v>
+      </c>
+      <c r="Y30" s="0">
+        <v>728.474148530001</v>
+      </c>
+      <c r="Z30" s="0">
+        <v>0.016965575763407813</v>
       </c>
     </row>
     <row r="31">
@@ -1747,7 +2593,34 @@
         <v>0.063984374999999996</v>
       </c>
       <c r="Q31" s="0">
+        <v>0.038789062499999999</v>
+      </c>
+      <c r="R31" s="0">
+        <v>0.062421875000000002</v>
+      </c>
+      <c r="S31" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T31" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U31" s="0">
+        <v>0.014609375000000001</v>
+      </c>
+      <c r="V31" s="0">
+        <v>0.025195312499999997</v>
+      </c>
+      <c r="W31" s="0">
+        <v>0.26458699999999996</v>
+      </c>
+      <c r="X31" s="0">
+        <v>384.54600000000028</v>
+      </c>
+      <c r="Y31" s="0">
+        <v>775.88260679800032</v>
+      </c>
+      <c r="Z31" s="0">
+        <v>0.0092834259815561156</v>
       </c>
     </row>
     <row r="32">
@@ -1798,7 +2671,34 @@
         <v>0.054609375000000002</v>
       </c>
       <c r="Q32" s="0">
+        <v>0.029257812500000001</v>
+      </c>
+      <c r="R32" s="0">
+        <v>0.052929687500000003</v>
+      </c>
+      <c r="S32" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T32" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U32" s="0">
+        <v>0.013124999999999998</v>
+      </c>
+      <c r="V32" s="0">
+        <v>0.025351562500000001</v>
+      </c>
+      <c r="W32" s="0">
+        <v>0.27099600000000001</v>
+      </c>
+      <c r="X32" s="0">
+        <v>384.54400000000032</v>
+      </c>
+      <c r="Y32" s="0">
+        <v>754.71795018300099</v>
+      </c>
+      <c r="Z32" s="0">
+        <v>0.0089829724693345908</v>
       </c>
     </row>
     <row r="33">
@@ -1849,7 +2749,34 @@
         <v>0.027773437500000001</v>
       </c>
       <c r="Q33" s="0">
+        <v>0.028398437500000002</v>
+      </c>
+      <c r="R33" s="0">
+        <v>0.0520703125</v>
+      </c>
+      <c r="S33" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T33" s="0">
+        <v>0.010039062499999998</v>
+      </c>
+      <c r="U33" s="0">
+        <v>0.016640624999999996</v>
+      </c>
+      <c r="V33" s="0">
+        <v>-0.00062500000000000056</v>
+      </c>
+      <c r="W33" s="0">
+        <v>0.26031499999999996</v>
+      </c>
+      <c r="X33" s="0">
+        <v>347.93899999999985</v>
+      </c>
+      <c r="Y33" s="0">
+        <v>730.61244253199993</v>
+      </c>
+      <c r="Z33" s="0">
+        <v>0.018272505842049064</v>
       </c>
     </row>
     <row r="34">
@@ -1900,7 +2827,34 @@
         <v>0.065039062499999994</v>
       </c>
       <c r="Q34" s="0">
+        <v>0.039960937500000002</v>
+      </c>
+      <c r="R34" s="0">
+        <v>0.063593750000000004</v>
+      </c>
+      <c r="S34" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T34" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U34" s="0">
+        <v>0.014609375000000001</v>
+      </c>
+      <c r="V34" s="0">
+        <v>0.025078124999999993</v>
+      </c>
+      <c r="W34" s="0">
+        <v>0.26092499999999996</v>
+      </c>
+      <c r="X34" s="0">
+        <v>384.54500000000007</v>
+      </c>
+      <c r="Y34" s="0">
+        <v>732.08106725299967</v>
+      </c>
+      <c r="Z34" s="0">
+        <v>0.025541614941425945</v>
       </c>
     </row>
     <row r="35">
@@ -1951,7 +2905,34 @@
         <v>0.057539062500000002</v>
       </c>
       <c r="Q35" s="0">
+        <v>0.032500000000000001</v>
+      </c>
+      <c r="R35" s="0">
+        <v>0.056171875000000003</v>
+      </c>
+      <c r="S35" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T35" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U35" s="0">
+        <v>0.018164062500000001</v>
+      </c>
+      <c r="V35" s="0">
+        <v>0.025039062500000001</v>
+      </c>
+      <c r="W35" s="0">
+        <v>0.26580799999999999</v>
+      </c>
+      <c r="X35" s="0">
+        <v>347.92600000000039</v>
+      </c>
+      <c r="Y35" s="0">
+        <v>731.66969813700007</v>
+      </c>
+      <c r="Z35" s="0">
+        <v>0.018984037549254939</v>
       </c>
     </row>
     <row r="36">
@@ -2002,7 +2983,34 @@
         <v>0.028437500000000001</v>
       </c>
       <c r="Q36" s="0">
+        <v>0.029101562500000001</v>
+      </c>
+      <c r="R36" s="0">
+        <v>0.052773437499999999</v>
+      </c>
+      <c r="S36" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T36" s="0">
+        <v>0.010039062499999998</v>
+      </c>
+      <c r="U36" s="0">
+        <v>0.013593749999999998</v>
+      </c>
+      <c r="V36" s="0">
+        <v>-0.00066406249999999972</v>
+      </c>
+      <c r="W36" s="0">
+        <v>0.25695799999999996</v>
+      </c>
+      <c r="X36" s="0">
+        <v>384.54700000000003</v>
+      </c>
+      <c r="Y36" s="0">
+        <v>772.43099211199933</v>
+      </c>
+      <c r="Z36" s="0">
+        <v>0.618327235266242</v>
       </c>
     </row>
     <row r="37">
@@ -2053,7 +3061,34 @@
         <v>0.048750000000000002</v>
       </c>
       <c r="Q37" s="0">
+        <v>0.023671875000000002</v>
+      </c>
+      <c r="R37" s="0">
+        <v>0.047304687499999998</v>
+      </c>
+      <c r="S37" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T37" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U37" s="0">
+        <v>0.018632812499999998</v>
+      </c>
+      <c r="V37" s="0">
+        <v>0.025078125</v>
+      </c>
+      <c r="W37" s="0">
+        <v>0.25848399999999999</v>
+      </c>
+      <c r="X37" s="0">
+        <v>366.23000000000002</v>
+      </c>
+      <c r="Y37" s="0">
+        <v>757.78058648200022</v>
+      </c>
+      <c r="Z37" s="0">
+        <v>0.008708629074975438</v>
       </c>
     </row>
     <row r="38">
@@ -2104,7 +3139,34 @@
         <v>0.058437500000000003</v>
       </c>
       <c r="Q38" s="0">
+        <v>0.032734375000000003</v>
+      </c>
+      <c r="R38" s="0">
+        <v>0.056875000000000002</v>
+      </c>
+      <c r="S38" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T38" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U38" s="0">
+        <v>0.015585937500000001</v>
+      </c>
+      <c r="V38" s="0">
+        <v>0.025703125</v>
+      </c>
+      <c r="W38" s="0">
+        <v>0.26031500000000007</v>
+      </c>
+      <c r="X38" s="0">
+        <v>421.16600000000017</v>
+      </c>
+      <c r="Y38" s="0">
+        <v>746.00790017899953</v>
+      </c>
+      <c r="Z38" s="0">
+        <v>0.036415334461045994</v>
       </c>
     </row>
     <row r="39">
@@ -2155,7 +3217,34 @@
         <v>0.051679687500000002</v>
       </c>
       <c r="Q39" s="0">
+        <v>0.026757812500000002</v>
+      </c>
+      <c r="R39" s="0">
+        <v>0.050429687500000001</v>
+      </c>
+      <c r="S39" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T39" s="0">
+        <v>0.010039062499999998</v>
+      </c>
+      <c r="U39" s="0">
+        <v>0.014140625</v>
+      </c>
+      <c r="V39" s="0">
+        <v>0.024921875</v>
+      </c>
+      <c r="W39" s="0">
+        <v>0.25817899999999994</v>
+      </c>
+      <c r="X39" s="0">
+        <v>402.86199999999963</v>
+      </c>
+      <c r="Y39" s="0">
+        <v>829.67610923500024</v>
+      </c>
+      <c r="Z39" s="0">
+        <v>0.010492761192709716</v>
       </c>
     </row>
     <row r="40">
@@ -2206,7 +3295,34 @@
         <v>0.0247265625</v>
       </c>
       <c r="Q40" s="0">
+        <v>0.025351562500000001</v>
+      </c>
+      <c r="R40" s="0">
+        <v>0.049023437500000003</v>
+      </c>
+      <c r="S40" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T40" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U40" s="0">
+        <v>0.0146484375</v>
+      </c>
+      <c r="V40" s="0">
+        <v>-0.00062500000000000056</v>
+      </c>
+      <c r="W40" s="0">
+        <v>0.26001000000000002</v>
+      </c>
+      <c r="X40" s="0">
+        <v>366.23099999999977</v>
+      </c>
+      <c r="Y40" s="0">
+        <v>746.88071933299989</v>
+      </c>
+      <c r="Z40" s="0">
+        <v>0.10816085455433164</v>
       </c>
     </row>
     <row r="41">
@@ -2257,7 +3373,34 @@
         <v>0.0592578125</v>
       </c>
       <c r="Q41" s="0">
+        <v>0.033906249999999999</v>
+      </c>
+      <c r="R41" s="0">
+        <v>0.057539062500000002</v>
+      </c>
+      <c r="S41" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T41" s="0">
+        <v>0.011523437500000004</v>
+      </c>
+      <c r="U41" s="0">
+        <v>0.015117187500000004</v>
+      </c>
+      <c r="V41" s="0">
+        <v>0.025351562500000001</v>
+      </c>
+      <c r="W41" s="0">
+        <v>0.26275700000000002</v>
+      </c>
+      <c r="X41" s="0">
+        <v>347.94100000000071</v>
+      </c>
+      <c r="Y41" s="0">
+        <v>737.55778786199971</v>
+      </c>
+      <c r="Z41" s="0">
+        <v>0.033467324152458913</v>
       </c>
     </row>
     <row r="42">
@@ -2308,7 +3451,34 @@
         <v>0.036328125000000003</v>
       </c>
       <c r="Q42" s="0">
+        <v>0.036953125000000003</v>
+      </c>
+      <c r="R42" s="0">
+        <v>0.060624999999999998</v>
+      </c>
+      <c r="S42" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T42" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U42" s="0">
+        <v>0.013632812500000001</v>
+      </c>
+      <c r="V42" s="0">
+        <v>-0.00062500000000000056</v>
+      </c>
+      <c r="W42" s="0">
+        <v>0.25512699999999999</v>
+      </c>
+      <c r="X42" s="0">
+        <v>384.53100000000006</v>
+      </c>
+      <c r="Y42" s="0">
+        <v>734.644000409</v>
+      </c>
+      <c r="Z42" s="0">
+        <v>0.012518938745498734</v>
       </c>
     </row>
     <row r="43">
@@ -2359,7 +3529,34 @@
         <v>0.0579296875</v>
       </c>
       <c r="Q43" s="0">
+        <v>0.0325390625</v>
+      </c>
+      <c r="R43" s="0">
+        <v>0.056210937500000002</v>
+      </c>
+      <c r="S43" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T43" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U43" s="0">
+        <v>0.014140625000000004</v>
+      </c>
+      <c r="V43" s="0">
+        <v>0.025390625</v>
+      </c>
+      <c r="W43" s="0">
+        <v>0.25787399999999999</v>
+      </c>
+      <c r="X43" s="0">
+        <v>366.25099999999975</v>
+      </c>
+      <c r="Y43" s="0">
+        <v>751.28459976000022</v>
+      </c>
+      <c r="Z43" s="0">
+        <v>0.011323204219852466</v>
       </c>
     </row>
     <row r="44">
@@ -2410,7 +3607,34 @@
         <v>0.055468750000000004</v>
       </c>
       <c r="Q44" s="0">
+        <v>0.030507812500000002</v>
+      </c>
+      <c r="R44" s="0">
+        <v>0.054179687500000004</v>
+      </c>
+      <c r="S44" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T44" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U44" s="0">
+        <v>0.013124999999999998</v>
+      </c>
+      <c r="V44" s="0">
+        <v>0.024960937500000002</v>
+      </c>
+      <c r="W44" s="0">
+        <v>0.25665200000000005</v>
+      </c>
+      <c r="X44" s="0">
+        <v>384.52900000000011</v>
+      </c>
+      <c r="Y44" s="0">
+        <v>736.60681184000032</v>
+      </c>
+      <c r="Z44" s="0">
+        <v>0.0082890658663892103</v>
       </c>
     </row>
     <row r="45">
@@ -2461,7 +3685,34 @@
         <v>0.0229296875</v>
       </c>
       <c r="Q45" s="0">
+        <v>0.023554687500000001</v>
+      </c>
+      <c r="R45" s="0">
+        <v>0.0471875</v>
+      </c>
+      <c r="S45" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T45" s="0">
+        <v>0.0099999999999999985</v>
+      </c>
+      <c r="U45" s="0">
+        <v>0.0151171875</v>
+      </c>
+      <c r="V45" s="0">
+        <v>-0.00062500000000000056</v>
+      </c>
+      <c r="W45" s="0">
+        <v>0.26946999999999999</v>
+      </c>
+      <c r="X45" s="0">
+        <v>347.94100000000026</v>
+      </c>
+      <c r="Y45" s="0">
+        <v>712.08404835100009</v>
+      </c>
+      <c r="Z45" s="0">
+        <v>0.004750314617670089</v>
       </c>
     </row>
     <row r="46">
@@ -2512,7 +3763,34 @@
         <v>0.060039062500000004</v>
       </c>
       <c r="Q46" s="0">
+        <v>0.035000000000000003</v>
+      </c>
+      <c r="R46" s="0">
+        <v>0.058671874999999998</v>
+      </c>
+      <c r="S46" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T46" s="0">
+        <v>0.010039062499999994</v>
+      </c>
+      <c r="U46" s="0">
+        <v>0.015664062499999999</v>
+      </c>
+      <c r="V46" s="0">
+        <v>0.025039062500000001</v>
+      </c>
+      <c r="W46" s="0">
+        <v>0.27160699999999999</v>
+      </c>
+      <c r="X46" s="0">
+        <v>366.23399999999992</v>
+      </c>
+      <c r="Y46" s="0">
+        <v>743.47298025200007</v>
+      </c>
+      <c r="Z46" s="0">
+        <v>0.011193520107729955</v>
       </c>
     </row>
     <row r="47">
@@ -2563,7 +3841,34 @@
         <v>0.063710937499999995</v>
       </c>
       <c r="Q47" s="0">
+        <v>0.038671875000000001</v>
+      </c>
+      <c r="R47" s="0">
+        <v>0.062343750000000003</v>
+      </c>
+      <c r="S47" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T47" s="0">
+        <v>0.011562499999999996</v>
+      </c>
+      <c r="U47" s="0">
+        <v>0.018671874999999998</v>
+      </c>
+      <c r="V47" s="0">
+        <v>0.025039062499999994</v>
+      </c>
+      <c r="W47" s="0">
+        <v>0.26672299999999999</v>
+      </c>
+      <c r="X47" s="0">
+        <v>347.92500000000018</v>
+      </c>
+      <c r="Y47" s="0">
+        <v>761.25944484399997</v>
+      </c>
+      <c r="Z47" s="0">
+        <v>0.013689159536472213</v>
       </c>
     </row>
     <row r="48">
@@ -2614,7 +3919,34 @@
         <v>0.0498046875</v>
       </c>
       <c r="Q48" s="0">
+        <v>0.024804687500000002</v>
+      </c>
+      <c r="R48" s="0">
+        <v>0.048476562500000001</v>
+      </c>
+      <c r="S48" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T48" s="0">
+        <v>0.010039062499999998</v>
+      </c>
+      <c r="U48" s="0">
+        <v>0.019179687499999997</v>
+      </c>
+      <c r="V48" s="0">
+        <v>0.024999999999999998</v>
+      </c>
+      <c r="W48" s="0">
+        <v>0.25665299999999996</v>
+      </c>
+      <c r="X48" s="0">
+        <v>402.85399999999936</v>
+      </c>
+      <c r="Y48" s="0">
+        <v>739.99588085400046</v>
+      </c>
+      <c r="Z48" s="0">
+        <v>0.12516664405036068</v>
       </c>
     </row>
     <row r="49">
@@ -2665,7 +3997,34 @@
         <v>0.059335937499999998</v>
       </c>
       <c r="Q49" s="0">
+        <v>0.034335937500000004</v>
+      </c>
+      <c r="R49" s="0">
+        <v>0.058007812499999999</v>
+      </c>
+      <c r="S49" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T49" s="0">
+        <v>0.011562499999999996</v>
+      </c>
+      <c r="U49" s="0">
+        <v>0.022695312499999995</v>
+      </c>
+      <c r="V49" s="0">
+        <v>0.024999999999999994</v>
+      </c>
+      <c r="W49" s="0">
+        <v>0.26428200000000002</v>
+      </c>
+      <c r="X49" s="0">
+        <v>366.24099999999999</v>
+      </c>
+      <c r="Y49" s="0">
+        <v>749.62124667499984</v>
+      </c>
+      <c r="Z49" s="0">
+        <v>0.038919884302220542</v>
       </c>
     </row>
     <row r="50">
@@ -2716,7 +4075,34 @@
         <v>0.064023437500000002</v>
       </c>
       <c r="Q50" s="0">
+        <v>0.038984375000000002</v>
+      </c>
+      <c r="R50" s="0">
+        <v>0.062656249999999997</v>
+      </c>
+      <c r="S50" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T50" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U50" s="0">
+        <v>0.013632812500000001</v>
+      </c>
+      <c r="V50" s="0">
+        <v>0.025039062500000001</v>
+      </c>
+      <c r="W50" s="0">
+        <v>0.25512699999999999</v>
+      </c>
+      <c r="X50" s="0">
+        <v>366.24099999999999</v>
+      </c>
+      <c r="Y50" s="0">
+        <v>742.37547657100004</v>
+      </c>
+      <c r="Z50" s="0">
+        <v>0.016476308624736397</v>
       </c>
     </row>
     <row r="51">
@@ -2767,7 +4153,34 @@
         <v>0.022890625000000001</v>
       </c>
       <c r="Q51" s="0">
+        <v>0.023476562499999999</v>
+      </c>
+      <c r="R51" s="0">
+        <v>0.047148437500000001</v>
+      </c>
+      <c r="S51" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T51" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U51" s="0">
+        <v>0.015156250000000003</v>
+      </c>
+      <c r="V51" s="0">
+        <v>-0.00058593749999999792</v>
+      </c>
+      <c r="W51" s="0">
+        <v>0.26397700000000002</v>
+      </c>
+      <c r="X51" s="0">
+        <v>366.23700000000008</v>
+      </c>
+      <c r="Y51" s="0">
+        <v>761.68895046000034</v>
+      </c>
+      <c r="Z51" s="0">
+        <v>0.10932905191095892</v>
       </c>
     </row>
     <row r="52">
@@ -2818,7 +4231,34 @@
         <v>0.064179687499999999</v>
       </c>
       <c r="Q52" s="0">
+        <v>0.0390625</v>
+      </c>
+      <c r="R52" s="0">
+        <v>0.062734374999999995</v>
+      </c>
+      <c r="S52" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T52" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U52" s="0">
+        <v>0.022187499999999999</v>
+      </c>
+      <c r="V52" s="0">
+        <v>0.025117187499999999</v>
+      </c>
+      <c r="W52" s="0">
+        <v>0.24993900000000002</v>
+      </c>
+      <c r="X52" s="0">
+        <v>366.23399999999992</v>
+      </c>
+      <c r="Y52" s="0">
+        <v>729.00366836199964</v>
+      </c>
+      <c r="Z52" s="0">
+        <v>0.030047681117144287</v>
       </c>
     </row>
     <row r="53">
@@ -2869,7 +4309,34 @@
         <v>0.054726562499999999</v>
       </c>
       <c r="Q53" s="0">
+        <v>0.029609375</v>
+      </c>
+      <c r="R53" s="0">
+        <v>0.053281250000000002</v>
+      </c>
+      <c r="S53" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T53" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U53" s="0">
+        <v>0.013632812500000001</v>
+      </c>
+      <c r="V53" s="0">
+        <v>0.025117187499999999</v>
+      </c>
+      <c r="W53" s="0">
+        <v>0.25634800000000002</v>
+      </c>
+      <c r="X53" s="0">
+        <v>384.54500000000007</v>
+      </c>
+      <c r="Y53" s="0">
+        <v>723.47852119200024</v>
+      </c>
+      <c r="Z53" s="0">
+        <v>0.048783629450088975</v>
       </c>
     </row>
     <row r="54">
@@ -2920,7 +4387,34 @@
         <v>0.051210937499999998</v>
       </c>
       <c r="Q54" s="0">
+        <v>0.0262109375</v>
+      </c>
+      <c r="R54" s="0">
+        <v>0.049882812499999998</v>
+      </c>
+      <c r="S54" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T54" s="0">
+        <v>0.010039062499999998</v>
+      </c>
+      <c r="U54" s="0">
+        <v>0.016640625000000003</v>
+      </c>
+      <c r="V54" s="0">
+        <v>0.024999999999999998</v>
+      </c>
+      <c r="W54" s="0">
+        <v>0.26458800000000005</v>
+      </c>
+      <c r="X54" s="0">
+        <v>402.83800000000008</v>
+      </c>
+      <c r="Y54" s="0">
+        <v>733.67678460299976</v>
+      </c>
+      <c r="Z54" s="0">
+        <v>0.50384886561648845</v>
       </c>
     </row>
     <row r="55">
@@ -2971,7 +4465,34 @@
         <v>0.047773437500000002</v>
       </c>
       <c r="Q55" s="0">
+        <v>0.0227734375</v>
+      </c>
+      <c r="R55" s="0">
+        <v>0.046445312500000002</v>
+      </c>
+      <c r="S55" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T55" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U55" s="0">
+        <v>0.015625</v>
+      </c>
+      <c r="V55" s="0">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="W55" s="0">
+        <v>0.25299100000000002</v>
+      </c>
+      <c r="X55" s="0">
+        <v>347.92700000000013</v>
+      </c>
+      <c r="Y55" s="0">
+        <v>718.42527437799981</v>
+      </c>
+      <c r="Z55" s="0">
+        <v>0.014298935507951046</v>
       </c>
     </row>
     <row r="56">
@@ -3022,7 +4543,34 @@
         <v>0.057812500000000003</v>
       </c>
       <c r="Q56" s="0">
+        <v>0.032812500000000001</v>
+      </c>
+      <c r="R56" s="0">
+        <v>0.056445312500000004</v>
+      </c>
+      <c r="S56" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T56" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U56" s="0">
+        <v>0.017656249999999998</v>
+      </c>
+      <c r="V56" s="0">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="W56" s="0">
+        <v>0.25787399999999999</v>
+      </c>
+      <c r="X56" s="0">
+        <v>421.16600000000017</v>
+      </c>
+      <c r="Y56" s="0">
+        <v>726.07420716600063</v>
+      </c>
+      <c r="Z56" s="0">
+        <v>0.012353405506153469</v>
       </c>
     </row>
     <row r="57">
@@ -3073,7 +4621,34 @@
         <v>0.050625000000000003</v>
       </c>
       <c r="Q57" s="0">
+        <v>0.025664062500000001</v>
+      </c>
+      <c r="R57" s="0">
+        <v>0.049335937500000003</v>
+      </c>
+      <c r="S57" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T57" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U57" s="0">
+        <v>0.0146484375</v>
+      </c>
+      <c r="V57" s="0">
+        <v>0.024960937500000002</v>
+      </c>
+      <c r="W57" s="0">
+        <v>0.25817800000000002</v>
+      </c>
+      <c r="X57" s="0">
+        <v>402.8420000000001</v>
+      </c>
+      <c r="Y57" s="0">
+        <v>735.4052472479998</v>
+      </c>
+      <c r="Z57" s="0">
+        <v>0.016392720038089306</v>
       </c>
     </row>
     <row r="58">
@@ -3124,7 +4699,34 @@
         <v>0.048671875000000003</v>
       </c>
       <c r="Q58" s="0">
+        <v>0.023710937500000001</v>
+      </c>
+      <c r="R58" s="0">
+        <v>0.047343750000000004</v>
+      </c>
+      <c r="S58" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T58" s="0">
+        <v>0.011523437499999997</v>
+      </c>
+      <c r="U58" s="0">
+        <v>0.015625</v>
+      </c>
+      <c r="V58" s="0">
+        <v>0.024960937500000002</v>
+      </c>
+      <c r="W58" s="0">
+        <v>0.26275599999999999</v>
+      </c>
+      <c r="X58" s="0">
+        <v>366.2510000000002</v>
+      </c>
+      <c r="Y58" s="0">
+        <v>753.99520271599977</v>
+      </c>
+      <c r="Z58" s="0">
+        <v>0.023552406989464845</v>
       </c>
     </row>
     <row r="59">
@@ -3175,7 +4777,34 @@
         <v>0.056250000000000001</v>
       </c>
       <c r="Q59" s="0">
+        <v>0.03078125</v>
+      </c>
+      <c r="R59" s="0">
+        <v>0.054921875000000002</v>
+      </c>
+      <c r="S59" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T59" s="0">
+        <v>0.010507812500000002</v>
+      </c>
+      <c r="U59" s="0">
+        <v>0.014101562500000001</v>
+      </c>
+      <c r="V59" s="0">
+        <v>0.025468750000000002</v>
+      </c>
+      <c r="W59" s="0">
+        <v>0.26794399999999996</v>
+      </c>
+      <c r="X59" s="0">
+        <v>347.93899999999985</v>
+      </c>
+      <c r="Y59" s="0">
+        <v>733.916996036</v>
+      </c>
+      <c r="Z59" s="0">
+        <v>0.02517055129395868</v>
       </c>
     </row>
     <row r="60">
@@ -3226,7 +4855,34 @@
         <v>0.047968750000000004</v>
       </c>
       <c r="Q60" s="0">
+        <v>0.023007812499999999</v>
+      </c>
+      <c r="R60" s="0">
+        <v>0.046679687500000004</v>
+      </c>
+      <c r="S60" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T60" s="0">
+        <v>0.010039062500000005</v>
+      </c>
+      <c r="U60" s="0">
+        <v>0.013632812500000004</v>
+      </c>
+      <c r="V60" s="0">
+        <v>0.024960937500000006</v>
+      </c>
+      <c r="W60" s="0">
+        <v>0.25787399999999999</v>
+      </c>
+      <c r="X60" s="0">
+        <v>384.54600000000028</v>
+      </c>
+      <c r="Y60" s="0">
+        <v>731.98239384999988</v>
+      </c>
+      <c r="Z60" s="0">
+        <v>0.01928476818921248</v>
       </c>
     </row>
     <row r="61">
@@ -3277,7 +4933,34 @@
         <v>0.051875000000000004</v>
       </c>
       <c r="Q61" s="0">
+        <v>0.026953125000000001</v>
+      </c>
+      <c r="R61" s="0">
+        <v>0.050625000000000003</v>
+      </c>
+      <c r="S61" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T61" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U61" s="0">
+        <v>0.015625</v>
+      </c>
+      <c r="V61" s="0">
+        <v>0.024921875000000003</v>
+      </c>
+      <c r="W61" s="0">
+        <v>0.26184099999999993</v>
+      </c>
+      <c r="X61" s="0">
+        <v>366.25</v>
+      </c>
+      <c r="Y61" s="0">
+        <v>745.68198171699987</v>
+      </c>
+      <c r="Z61" s="0">
+        <v>0.014711706390466369</v>
       </c>
     </row>
     <row r="62">
@@ -3328,7 +5011,34 @@
         <v>0.049101562500000001</v>
       </c>
       <c r="Q62" s="0">
+        <v>0.023789062499999999</v>
+      </c>
+      <c r="R62" s="0">
+        <v>0.047460937500000001</v>
+      </c>
+      <c r="S62" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T62" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U62" s="0">
+        <v>0.014140625000000004</v>
+      </c>
+      <c r="V62" s="0">
+        <v>0.025312500000000002</v>
+      </c>
+      <c r="W62" s="0">
+        <v>0.25451699999999999</v>
+      </c>
+      <c r="X62" s="0">
+        <v>366.2510000000002</v>
+      </c>
+      <c r="Y62" s="0">
+        <v>754.13704986500034</v>
+      </c>
+      <c r="Z62" s="0">
+        <v>0.011761954626477118</v>
       </c>
     </row>
     <row r="63">
@@ -3379,7 +5089,34 @@
         <v>0.054062499999999999</v>
       </c>
       <c r="Q63" s="0">
+        <v>0.028242187500000002</v>
+      </c>
+      <c r="R63" s="0">
+        <v>0.051914062500000004</v>
+      </c>
+      <c r="S63" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T63" s="0">
+        <v>0.011562499999999996</v>
+      </c>
+      <c r="U63" s="0">
+        <v>0.015156249999999996</v>
+      </c>
+      <c r="V63" s="0">
+        <v>0.025820312499999998</v>
+      </c>
+      <c r="W63" s="0">
+        <v>0.26153599999999999</v>
+      </c>
+      <c r="X63" s="0">
+        <v>384.54600000000028</v>
+      </c>
+      <c r="Y63" s="0">
+        <v>751.88176572900056</v>
+      </c>
+      <c r="Z63" s="0">
+        <v>0.0075494637098274982</v>
       </c>
     </row>
     <row r="64">
@@ -3430,7 +5167,34 @@
         <v>0.063945312500000004</v>
       </c>
       <c r="Q64" s="0">
+        <v>0.038789062499999999</v>
+      </c>
+      <c r="R64" s="0">
+        <v>0.0625</v>
+      </c>
+      <c r="S64" s="0">
         <v>0.023710937500000001</v>
+      </c>
+      <c r="T64" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U64" s="0">
+        <v>0.016679687500000005</v>
+      </c>
+      <c r="V64" s="0">
+        <v>0.025156250000000005</v>
+      </c>
+      <c r="W64" s="0">
+        <v>0.27038600000000002</v>
+      </c>
+      <c r="X64" s="0">
+        <v>421.16799999999967</v>
+      </c>
+      <c r="Y64" s="0">
+        <v>726.92442340799971</v>
+      </c>
+      <c r="Z64" s="0">
+        <v>0.0097072079952605691</v>
       </c>
     </row>
     <row r="65">
@@ -3481,7 +5245,34 @@
         <v>0.057382812499999998</v>
       </c>
       <c r="Q65" s="0">
+        <v>0.032343749999999998</v>
+      </c>
+      <c r="R65" s="0">
+        <v>0.056054687499999999</v>
+      </c>
+      <c r="S65" s="0">
         <v>0.023710937500000001</v>
+      </c>
+      <c r="T65" s="0">
+        <v>0.010078125</v>
+      </c>
+      <c r="U65" s="0">
+        <v>0.015156250000000003</v>
+      </c>
+      <c r="V65" s="0">
+        <v>0.025039062500000001</v>
+      </c>
+      <c r="W65" s="0">
+        <v>0.25787300000000002</v>
+      </c>
+      <c r="X65" s="0">
+        <v>421.17999999999984</v>
+      </c>
+      <c r="Y65" s="0">
+        <v>770.54745349099994</v>
+      </c>
+      <c r="Z65" s="0">
+        <v>0.018918103037330335</v>
       </c>
     </row>
     <row r="66">
@@ -3532,7 +5323,34 @@
         <v>0.028359374999999999</v>
       </c>
       <c r="Q66" s="0">
+        <v>0.028945312500000001</v>
+      </c>
+      <c r="R66" s="0">
+        <v>0.052617187500000002</v>
+      </c>
+      <c r="S66" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T66" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U66" s="0">
+        <v>0.013632812500000001</v>
+      </c>
+      <c r="V66" s="0">
+        <v>-0.00058593750000000139</v>
+      </c>
+      <c r="W66" s="0">
+        <v>0.25939999999999996</v>
+      </c>
+      <c r="X66" s="0">
+        <v>384.53100000000018</v>
+      </c>
+      <c r="Y66" s="0">
+        <v>740.65069248599957</v>
+      </c>
+      <c r="Z66" s="0">
+        <v>0.15282319254503551</v>
       </c>
     </row>
     <row r="67">
@@ -3583,7 +5401,34 @@
         <v>0.058515625000000002</v>
       </c>
       <c r="Q67" s="0">
+        <v>0.033476562500000001</v>
+      </c>
+      <c r="R67" s="0">
+        <v>0.057109375000000004</v>
+      </c>
+      <c r="S67" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T67" s="0">
+        <v>0.011523437499999997</v>
+      </c>
+      <c r="U67" s="0">
+        <v>0.015117187499999997</v>
+      </c>
+      <c r="V67" s="0">
+        <v>0.025039062500000001</v>
+      </c>
+      <c r="W67" s="0">
+        <v>0.26245099999999999</v>
+      </c>
+      <c r="X67" s="0">
+        <v>366.23499999999967</v>
+      </c>
+      <c r="Y67" s="0">
+        <v>727.7388446609998</v>
+      </c>
+      <c r="Z67" s="0">
+        <v>0.019980443158404686</v>
       </c>
     </row>
     <row r="68">
@@ -3634,7 +5479,34 @@
         <v>0.050078125000000001</v>
       </c>
       <c r="Q68" s="0">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="R68" s="0">
+        <v>0.048671875000000003</v>
+      </c>
+      <c r="S68" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T68" s="0">
+        <v>0.011562499999999996</v>
+      </c>
+      <c r="U68" s="0">
+        <v>0.015664062499999999</v>
+      </c>
+      <c r="V68" s="0">
+        <v>0.025078125</v>
+      </c>
+      <c r="W68" s="0">
+        <v>0.26123000000000002</v>
+      </c>
+      <c r="X68" s="0">
+        <v>366.23399999999992</v>
+      </c>
+      <c r="Y68" s="0">
+        <v>738.07963893099986</v>
+      </c>
+      <c r="Z68" s="0">
+        <v>0.012369923190529774</v>
       </c>
     </row>
     <row r="69">
@@ -3685,7 +5557,34 @@
         <v>0.064101562500000001</v>
       </c>
       <c r="Q69" s="0">
+        <v>0.038554687500000004</v>
+      </c>
+      <c r="R69" s="0">
+        <v>0.062226562499999999</v>
+      </c>
+      <c r="S69" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T69" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U69" s="0">
+        <v>0.014140624999999997</v>
+      </c>
+      <c r="V69" s="0">
+        <v>0.025546874999999997</v>
+      </c>
+      <c r="W69" s="0">
+        <v>0.26245099999999999</v>
+      </c>
+      <c r="X69" s="0">
+        <v>402.85699999999997</v>
+      </c>
+      <c r="Y69" s="0">
+        <v>727.0604948199998</v>
+      </c>
+      <c r="Z69" s="0">
+        <v>0.030849088714244639</v>
       </c>
     </row>
     <row r="70">
@@ -3736,7 +5635,34 @@
         <v>0.033554687499999999</v>
       </c>
       <c r="Q70" s="0">
+        <v>0.034140625000000001</v>
+      </c>
+      <c r="R70" s="0">
+        <v>0.057812500000000003</v>
+      </c>
+      <c r="S70" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T70" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U70" s="0">
+        <v>0.014140624999999997</v>
+      </c>
+      <c r="V70" s="0">
+        <v>-0.00058593750000000139</v>
+      </c>
+      <c r="W70" s="0">
+        <v>0.26458800000000005</v>
+      </c>
+      <c r="X70" s="0">
+        <v>402.85800000000017</v>
+      </c>
+      <c r="Y70" s="0">
+        <v>758.63588306800011</v>
+      </c>
+      <c r="Z70" s="0">
+        <v>0.0064271919491618781</v>
       </c>
     </row>
     <row r="71">
@@ -3789,6 +5715,33 @@
       <c r="Q71" s="0">
         <v>0</v>
       </c>
+      <c r="R71" s="0">
+        <v>0</v>
+      </c>
+      <c r="S71" s="0">
+        <v>0</v>
+      </c>
+      <c r="T71" s="0">
+        <v>0</v>
+      </c>
+      <c r="U71" s="0">
+        <v>0</v>
+      </c>
+      <c r="V71" s="0">
+        <v>0</v>
+      </c>
+      <c r="W71" s="0">
+        <v>0</v>
+      </c>
+      <c r="X71" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
@@ -3838,7 +5791,34 @@
         <v>0.062734374999999995</v>
       </c>
       <c r="Q72" s="0">
+        <v>0.037539062499999998</v>
+      </c>
+      <c r="R72" s="0">
+        <v>0.0612109375</v>
+      </c>
+      <c r="S72" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T72" s="0">
+        <v>0.012070312500000006</v>
+      </c>
+      <c r="U72" s="0">
+        <v>0.016171875000000002</v>
+      </c>
+      <c r="V72" s="0">
+        <v>0.025195312499999997</v>
+      </c>
+      <c r="W72" s="0">
+        <v>0.26611299999999999</v>
+      </c>
+      <c r="X72" s="0">
+        <v>402.85799999999927</v>
+      </c>
+      <c r="Y72" s="0">
+        <v>772.47514400399996</v>
+      </c>
+      <c r="Z72" s="0">
+        <v>0.0069362390003434738</v>
       </c>
     </row>
     <row r="73">
@@ -3889,7 +5869,34 @@
         <v>0.035195312499999999</v>
       </c>
       <c r="Q73" s="0">
+        <v>0.0358203125</v>
+      </c>
+      <c r="R73" s="0">
+        <v>0.059453125000000002</v>
+      </c>
+      <c r="S73" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T73" s="0">
+        <v>0.011523437500000004</v>
+      </c>
+      <c r="U73" s="0">
+        <v>0.014609375000000001</v>
+      </c>
+      <c r="V73" s="0">
+        <v>-0.00062500000000000056</v>
+      </c>
+      <c r="W73" s="0">
+        <v>0.25482199999999999</v>
+      </c>
+      <c r="X73" s="0">
+        <v>384.5600000000004</v>
+      </c>
+      <c r="Y73" s="0">
+        <v>789.35447118000002</v>
+      </c>
+      <c r="Z73" s="0">
+        <v>0.014101971549877431</v>
       </c>
     </row>
     <row r="74">
@@ -3942,6 +5949,33 @@
       <c r="Q74" s="0">
         <v>0</v>
       </c>
+      <c r="R74" s="0">
+        <v>0</v>
+      </c>
+      <c r="S74" s="0">
+        <v>0</v>
+      </c>
+      <c r="T74" s="0">
+        <v>0</v>
+      </c>
+      <c r="U74" s="0">
+        <v>0</v>
+      </c>
+      <c r="V74" s="0">
+        <v>0</v>
+      </c>
+      <c r="W74" s="0">
+        <v>0</v>
+      </c>
+      <c r="X74" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
@@ -3991,7 +6025,34 @@
         <v>0.059179687500000001</v>
       </c>
       <c r="Q75" s="0">
+        <v>0.032968749999999998</v>
+      </c>
+      <c r="R75" s="0">
+        <v>0.057109375000000004</v>
+      </c>
+      <c r="S75" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T75" s="0">
+        <v>0.01203125</v>
+      </c>
+      <c r="U75" s="0">
+        <v>0.015117187500000004</v>
+      </c>
+      <c r="V75" s="0">
+        <v>0.026210937500000003</v>
+      </c>
+      <c r="W75" s="0">
+        <v>0.26763900000000002</v>
+      </c>
+      <c r="X75" s="0">
+        <v>347.9409999999998</v>
+      </c>
+      <c r="Y75" s="0">
+        <v>738.62743393600022</v>
+      </c>
+      <c r="Z75" s="0">
+        <v>0.0079770599961925467</v>
       </c>
     </row>
     <row r="76">
@@ -4042,7 +6103,34 @@
         <v>0.050234374999999998</v>
       </c>
       <c r="Q76" s="0">
+        <v>0.025156250000000002</v>
+      </c>
+      <c r="R76" s="0">
+        <v>0.048789062500000001</v>
+      </c>
+      <c r="S76" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T76" s="0">
+        <v>0.0099999999999999985</v>
+      </c>
+      <c r="U76" s="0">
+        <v>0.014609374999999997</v>
+      </c>
+      <c r="V76" s="0">
+        <v>0.025078124999999996</v>
+      </c>
+      <c r="W76" s="0">
+        <v>0.26611299999999999</v>
+      </c>
+      <c r="X76" s="0">
+        <v>366.23599999999988</v>
+      </c>
+      <c r="Y76" s="0">
+        <v>735.36465871100017</v>
+      </c>
+      <c r="Z76" s="0">
+        <v>0.014960847882173951</v>
       </c>
     </row>
     <row r="77">
@@ -4093,7 +6181,34 @@
         <v>0.035039062500000002</v>
       </c>
       <c r="Q77" s="0">
+        <v>0.03515625</v>
+      </c>
+      <c r="R77" s="0">
+        <v>0.059296874999999999</v>
+      </c>
+      <c r="S77" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T77" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U77" s="0">
+        <v>0.016093750000000004</v>
+      </c>
+      <c r="V77" s="0">
+        <v>-0.0001171874999999975</v>
+      </c>
+      <c r="W77" s="0">
+        <v>0.30364999999999998</v>
+      </c>
+      <c r="X77" s="0">
+        <v>366.24199999999973</v>
+      </c>
+      <c r="Y77" s="0">
+        <v>792.71665446799898</v>
+      </c>
+      <c r="Z77" s="0">
+        <v>0.010874233964609339</v>
       </c>
     </row>
     <row r="78">
@@ -4144,7 +6259,34 @@
         <v>0.055546875000000002</v>
       </c>
       <c r="Q78" s="0">
+        <v>0.0301171875</v>
+      </c>
+      <c r="R78" s="0">
+        <v>0.054257812500000002</v>
+      </c>
+      <c r="S78" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T78" s="0">
+        <v>0.010507812500000002</v>
+      </c>
+      <c r="U78" s="0">
+        <v>0.022148437500000003</v>
+      </c>
+      <c r="V78" s="0">
+        <v>0.025429687500000003</v>
+      </c>
+      <c r="W78" s="0">
+        <v>0.28747600000000001</v>
+      </c>
+      <c r="X78" s="0">
+        <v>347.92700000000013</v>
+      </c>
+      <c r="Y78" s="0">
+        <v>746.72947993499929</v>
+      </c>
+      <c r="Z78" s="0">
+        <v>0.014931676809117719</v>
       </c>
     </row>
     <row r="79">
@@ -4195,7 +6337,34 @@
         <v>0.0634765625</v>
       </c>
       <c r="Q79" s="0">
+        <v>0.037617187500000003</v>
+      </c>
+      <c r="R79" s="0">
+        <v>0.061757812500000002</v>
+      </c>
+      <c r="S79" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T79" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U79" s="0">
+        <v>0.014101562499999998</v>
+      </c>
+      <c r="V79" s="0">
+        <v>0.025859374999999997</v>
+      </c>
+      <c r="W79" s="0">
+        <v>0.299072</v>
+      </c>
+      <c r="X79" s="0">
+        <v>384.54399999999987</v>
+      </c>
+      <c r="Y79" s="0">
+        <v>802.68463631100076</v>
+      </c>
+      <c r="Z79" s="0">
+        <v>0.0094809917157249561</v>
       </c>
     </row>
     <row r="80">
@@ -4246,7 +6415,34 @@
         <v>0.02703125</v>
       </c>
       <c r="Q80" s="0">
+        <v>0.027148437500000001</v>
+      </c>
+      <c r="R80" s="0">
+        <v>0.051289062500000003</v>
+      </c>
+      <c r="S80" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T80" s="0">
+        <v>0.010546875000000001</v>
+      </c>
+      <c r="U80" s="0">
+        <v>0.014140625</v>
+      </c>
+      <c r="V80" s="0">
+        <v>-0.00011718750000000097</v>
+      </c>
+      <c r="W80" s="0">
+        <v>0.28198299999999998</v>
+      </c>
+      <c r="X80" s="0">
+        <v>366.22099999999989</v>
+      </c>
+      <c r="Y80" s="0">
+        <v>753.70649844399941</v>
+      </c>
+      <c r="Z80" s="0">
+        <v>0.9817552281580687</v>
       </c>
     </row>
     <row r="81">
@@ -4297,7 +6493,34 @@
         <v>0.064375000000000002</v>
       </c>
       <c r="Q81" s="0">
+        <v>0.038710937500000001</v>
+      </c>
+      <c r="R81" s="0">
+        <v>0.062851562499999999</v>
+      </c>
+      <c r="S81" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T81" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U81" s="0">
+        <v>0.016640624999999999</v>
+      </c>
+      <c r="V81" s="0">
+        <v>0.025664062500000001</v>
+      </c>
+      <c r="W81" s="0">
+        <v>0.299682</v>
+      </c>
+      <c r="X81" s="0">
+        <v>366.25200000000041</v>
+      </c>
+      <c r="Y81" s="0">
+        <v>801.63876873599929</v>
+      </c>
+      <c r="Z81" s="0">
+        <v>0.0085442290311940061</v>
       </c>
     </row>
     <row r="82">
@@ -4348,7 +6571,34 @@
         <v>0.057070312499999998</v>
       </c>
       <c r="Q82" s="0">
+        <v>0.031601562499999999</v>
+      </c>
+      <c r="R82" s="0">
+        <v>0.055742187499999998</v>
+      </c>
+      <c r="S82" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T82" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U82" s="0">
+        <v>0.016640624999999999</v>
+      </c>
+      <c r="V82" s="0">
+        <v>0.025468749999999998</v>
+      </c>
+      <c r="W82" s="0">
+        <v>0.30120900000000006</v>
+      </c>
+      <c r="X82" s="0">
+        <v>366.23900000000049</v>
+      </c>
+      <c r="Y82" s="0">
+        <v>779.06416463000096</v>
+      </c>
+      <c r="Z82" s="0">
+        <v>0.020408048443440227</v>
       </c>
     </row>
     <row r="83">
@@ -4399,7 +6649,34 @@
         <v>0.049765625000000001</v>
       </c>
       <c r="Q83" s="0">
+        <v>0.024648437500000002</v>
+      </c>
+      <c r="R83" s="0">
+        <v>0.048320312500000004</v>
+      </c>
+      <c r="S83" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T83" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U83" s="0">
+        <v>0.016640624999999999</v>
+      </c>
+      <c r="V83" s="0">
+        <v>0.025117187499999999</v>
+      </c>
+      <c r="W83" s="0">
+        <v>0.27526899999999993</v>
+      </c>
+      <c r="X83" s="0">
+        <v>402.85300000000007</v>
+      </c>
+      <c r="Y83" s="0">
+        <v>774.26637868000012</v>
+      </c>
+      <c r="Z83" s="0">
+        <v>0.038587309549868838</v>
       </c>
     </row>
     <row r="84">
@@ -4450,7 +6727,34 @@
         <v>0.059843750000000001</v>
       </c>
       <c r="Q84" s="0">
+        <v>0.0341796875</v>
+      </c>
+      <c r="R84" s="0">
+        <v>0.058359374999999998</v>
+      </c>
+      <c r="S84" s="0">
         <v>0.024179687500000002</v>
+      </c>
+      <c r="T84" s="0">
+        <v>0.010546875000000004</v>
+      </c>
+      <c r="U84" s="0">
+        <v>0.017656249999999998</v>
+      </c>
+      <c r="V84" s="0">
+        <v>0.025664062500000001</v>
+      </c>
+      <c r="W84" s="0">
+        <v>0.28045599999999998</v>
+      </c>
+      <c r="X84" s="0">
+        <v>366.24499999999989</v>
+      </c>
+      <c r="Y84" s="0">
+        <v>789.7259802450003</v>
+      </c>
+      <c r="Z84" s="0">
+        <v>0.010523618932390493</v>
       </c>
     </row>
     <row r="85">
@@ -4501,7 +6805,34 @@
         <v>0.047031250000000004</v>
       </c>
       <c r="Q85" s="0">
+        <v>0.021953125</v>
+      </c>
+      <c r="R85" s="0">
+        <v>0.045624999999999999</v>
+      </c>
+      <c r="S85" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T85" s="0">
+        <v>0.010039062499999998</v>
+      </c>
+      <c r="U85" s="0">
+        <v>0.013125000000000001</v>
+      </c>
+      <c r="V85" s="0">
+        <v>0.025078125000000003</v>
+      </c>
+      <c r="W85" s="0">
+        <v>0.27496299999999996</v>
+      </c>
+      <c r="X85" s="0">
+        <v>366.23500000000013</v>
+      </c>
+      <c r="Y85" s="0">
+        <v>809.21138656199992</v>
+      </c>
+      <c r="Z85" s="0">
+        <v>0.015345463704147111</v>
       </c>
     </row>
     <row r="86">
@@ -4552,7 +6883,34 @@
         <v>0.058554687500000001</v>
       </c>
       <c r="Q86" s="0">
+        <v>0.033476562500000001</v>
+      </c>
+      <c r="R86" s="0">
+        <v>0.057109375000000004</v>
+      </c>
+      <c r="S86" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T86" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U86" s="0">
+        <v>0.021679687500000003</v>
+      </c>
+      <c r="V86" s="0">
+        <v>0.025078125</v>
+      </c>
+      <c r="W86" s="0">
+        <v>0.27435300000000007</v>
+      </c>
+      <c r="X86" s="0">
+        <v>384.54800000000023</v>
+      </c>
+      <c r="Y86" s="0">
+        <v>762.16940937499976</v>
+      </c>
+      <c r="Z86" s="0">
+        <v>0.027553390362777607</v>
       </c>
     </row>
     <row r="87">
@@ -4603,7 +6961,34 @@
         <v>0.052265625000000003</v>
       </c>
       <c r="Q87" s="0">
+        <v>0.026562499999999999</v>
+      </c>
+      <c r="R87" s="0">
+        <v>0.050703125000000002</v>
+      </c>
+      <c r="S87" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T87" s="0">
+        <v>0.010507812500000002</v>
+      </c>
+      <c r="U87" s="0">
+        <v>0.015625000000000003</v>
+      </c>
+      <c r="V87" s="0">
+        <v>0.025703125000000004</v>
+      </c>
+      <c r="W87" s="0">
+        <v>0.27099600000000001</v>
+      </c>
+      <c r="X87" s="0">
+        <v>384.54799999999977</v>
+      </c>
+      <c r="Y87" s="0">
+        <v>794.95579135499975</v>
+      </c>
+      <c r="Z87" s="0">
+        <v>0.15475482649457264</v>
       </c>
     </row>
     <row r="88">
@@ -4654,7 +7039,34 @@
         <v>0.056054687499999999</v>
       </c>
       <c r="Q88" s="0">
+        <v>0.029921875000000001</v>
+      </c>
+      <c r="R88" s="0">
+        <v>0.0540234375</v>
+      </c>
+      <c r="S88" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T88" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U88" s="0">
+        <v>0.015117187499999997</v>
+      </c>
+      <c r="V88" s="0">
+        <v>0.026132812499999998</v>
+      </c>
+      <c r="W88" s="0">
+        <v>0.27465800000000007</v>
+      </c>
+      <c r="X88" s="0">
+        <v>366.23399999999992</v>
+      </c>
+      <c r="Y88" s="0">
+        <v>750.12447237600054</v>
+      </c>
+      <c r="Z88" s="0">
+        <v>0.0086480064744080994</v>
       </c>
     </row>
     <row r="89">
@@ -4705,7 +7117,34 @@
         <v>0.0014062499999999999</v>
       </c>
       <c r="Q89" s="0">
+        <v>0.024453124999999999</v>
+      </c>
+      <c r="R89" s="0">
+        <v>0.048593749999999998</v>
+      </c>
+      <c r="S89" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T89" s="0">
+        <v>0.010507812500000005</v>
+      </c>
+      <c r="U89" s="0">
+        <v>0.017656249999999998</v>
+      </c>
+      <c r="V89" s="0">
+        <v>-0.023046874999999998</v>
+      </c>
+      <c r="W89" s="0">
+        <v>0.29571600000000003</v>
+      </c>
+      <c r="X89" s="0">
+        <v>384.53700000000026</v>
+      </c>
+      <c r="Y89" s="0">
+        <v>758.39944805299956</v>
+      </c>
+      <c r="Z89" s="0">
+        <v>65535</v>
       </c>
     </row>
     <row r="90">
@@ -4756,7 +7195,34 @@
         <v>0.065156249999999999</v>
       </c>
       <c r="Q90" s="0">
+        <v>0.0397265625</v>
+      </c>
+      <c r="R90" s="0">
+        <v>0.063867187500000006</v>
+      </c>
+      <c r="S90" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T90" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U90" s="0">
+        <v>0.015117187500000004</v>
+      </c>
+      <c r="V90" s="0">
+        <v>0.025429687499999999</v>
+      </c>
+      <c r="W90" s="0">
+        <v>0.28594999999999998</v>
+      </c>
+      <c r="X90" s="0">
+        <v>366.22500000000014</v>
+      </c>
+      <c r="Y90" s="0">
+        <v>777.87883524600056</v>
+      </c>
+      <c r="Z90" s="0">
+        <v>0.015774938487874035</v>
       </c>
     </row>
     <row r="91">
@@ -4807,7 +7273,34 @@
         <v>0.062304687500000004</v>
       </c>
       <c r="Q91" s="0">
+        <v>0.036601562500000004</v>
+      </c>
+      <c r="R91" s="0">
+        <v>0.060742187500000003</v>
+      </c>
+      <c r="S91" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T91" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U91" s="0">
+        <v>0.014101562499999998</v>
+      </c>
+      <c r="V91" s="0">
+        <v>0.025703125</v>
+      </c>
+      <c r="W91" s="0">
+        <v>0.29022200000000004</v>
+      </c>
+      <c r="X91" s="0">
+        <v>402.87100000000055</v>
+      </c>
+      <c r="Y91" s="0">
+        <v>788.20580638399952</v>
+      </c>
+      <c r="Z91" s="0">
+        <v>0.0086518865563162423</v>
       </c>
     </row>
     <row r="92">
@@ -4858,7 +7351,34 @@
         <v>0.048359375000000003</v>
       </c>
       <c r="Q92" s="0">
+        <v>0.0227734375</v>
+      </c>
+      <c r="R92" s="0">
+        <v>0.046914062499999999</v>
+      </c>
+      <c r="S92" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T92" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U92" s="0">
+        <v>0.014609375000000001</v>
+      </c>
+      <c r="V92" s="0">
+        <v>0.025585937500000003</v>
+      </c>
+      <c r="W92" s="0">
+        <v>0.28656000000000004</v>
+      </c>
+      <c r="X92" s="0">
+        <v>384.53199999999993</v>
+      </c>
+      <c r="Y92" s="0">
+        <v>778.30052447000025</v>
+      </c>
+      <c r="Z92" s="0">
+        <v>0.0099155299133470189</v>
       </c>
     </row>
     <row r="93">
@@ -4909,7 +7429,34 @@
         <v>0.060156250000000001</v>
       </c>
       <c r="Q93" s="0">
+        <v>0.034609374999999998</v>
+      </c>
+      <c r="R93" s="0">
+        <v>0.058750000000000004</v>
+      </c>
+      <c r="S93" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T93" s="0">
+        <v>0.010507812500000005</v>
+      </c>
+      <c r="U93" s="0">
+        <v>0.014101562500000005</v>
+      </c>
+      <c r="V93" s="0">
+        <v>0.025546875000000004</v>
+      </c>
+      <c r="W93" s="0">
+        <v>0.27526900000000004</v>
+      </c>
+      <c r="X93" s="0">
+        <v>384.5590000000002</v>
+      </c>
+      <c r="Y93" s="0">
+        <v>768.70619796599931</v>
+      </c>
+      <c r="Z93" s="0">
+        <v>0.02251870471588234</v>
       </c>
     </row>
     <row r="94">
@@ -4960,7 +7507,34 @@
         <v>0.052929687500000003</v>
       </c>
       <c r="Q94" s="0">
+        <v>0.027148437500000001</v>
+      </c>
+      <c r="R94" s="0">
+        <v>0.051289062500000003</v>
+      </c>
+      <c r="S94" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T94" s="0">
+        <v>0.010507812500000002</v>
+      </c>
+      <c r="U94" s="0">
+        <v>0.017617187500000003</v>
+      </c>
+      <c r="V94" s="0">
+        <v>0.025781250000000002</v>
+      </c>
+      <c r="W94" s="0">
+        <v>0.29388500000000001</v>
+      </c>
+      <c r="X94" s="0">
+        <v>366.24699999999984</v>
+      </c>
+      <c r="Y94" s="0">
+        <v>759.50327456399964</v>
+      </c>
+      <c r="Z94" s="0">
+        <v>0.03647091538938195</v>
       </c>
     </row>
     <row r="95">
@@ -5011,7 +7585,34 @@
         <v>0.048242187499999999</v>
       </c>
       <c r="Q95" s="0">
+        <v>0.023203125000000002</v>
+      </c>
+      <c r="R95" s="0">
+        <v>0.046875</v>
+      </c>
+      <c r="S95" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T95" s="0">
+        <v>0.010039062499999998</v>
+      </c>
+      <c r="U95" s="0">
+        <v>0.01515625</v>
+      </c>
+      <c r="V95" s="0">
+        <v>0.025039062499999997</v>
+      </c>
+      <c r="W95" s="0">
+        <v>0.28869599999999995</v>
+      </c>
+      <c r="X95" s="0">
+        <v>347.94000000000096</v>
+      </c>
+      <c r="Y95" s="0">
+        <v>736.39523087199905</v>
+      </c>
+      <c r="Z95" s="0">
+        <v>0.14199181993355364</v>
       </c>
     </row>
     <row r="96">
@@ -5062,7 +7663,34 @@
         <v>0.062851562499999999</v>
       </c>
       <c r="Q96" s="0">
+        <v>0.037304687500000003</v>
+      </c>
+      <c r="R96" s="0">
+        <v>0.061445312500000002</v>
+      </c>
+      <c r="S96" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T96" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U96" s="0">
+        <v>0.019140625000000001</v>
+      </c>
+      <c r="V96" s="0">
+        <v>0.025546874999999997</v>
+      </c>
+      <c r="W96" s="0">
+        <v>0.28564499999999998</v>
+      </c>
+      <c r="X96" s="0">
+        <v>366.24600000000009</v>
+      </c>
+      <c r="Y96" s="0">
+        <v>813.04806762099997</v>
+      </c>
+      <c r="Z96" s="0">
+        <v>0.0086836202384553696</v>
       </c>
     </row>
     <row r="97">
@@ -5113,7 +7741,34 @@
         <v>0.053671875000000001</v>
       </c>
       <c r="Q97" s="0">
+        <v>0.0278515625</v>
+      </c>
+      <c r="R97" s="0">
+        <v>0.051992187500000002</v>
+      </c>
+      <c r="S97" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T97" s="0">
+        <v>0.010507812500000002</v>
+      </c>
+      <c r="U97" s="0">
+        <v>0.0151171875</v>
+      </c>
+      <c r="V97" s="0">
+        <v>0.025820312500000001</v>
+      </c>
+      <c r="W97" s="0">
+        <v>0.28686499999999998</v>
+      </c>
+      <c r="X97" s="0">
+        <v>421.16799999999967</v>
+      </c>
+      <c r="Y97" s="0">
+        <v>793.84675204799987</v>
+      </c>
+      <c r="Z97" s="0">
+        <v>0.01253265797911029</v>
       </c>
     </row>
     <row r="98">
@@ -5164,7 +7819,34 @@
         <v>0.046953124999999998</v>
       </c>
       <c r="Q98" s="0">
+        <v>0.021406250000000002</v>
+      </c>
+      <c r="R98" s="0">
+        <v>0.045546875000000001</v>
+      </c>
+      <c r="S98" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T98" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U98" s="0">
+        <v>0.018125000000000002</v>
+      </c>
+      <c r="V98" s="0">
+        <v>0.025546874999999997</v>
+      </c>
+      <c r="W98" s="0">
+        <v>0.29052799999999995</v>
+      </c>
+      <c r="X98" s="0">
+        <v>384.53999999999996</v>
+      </c>
+      <c r="Y98" s="0">
+        <v>782.55865873199946</v>
+      </c>
+      <c r="Z98" s="0">
+        <v>0.013696323168722078</v>
       </c>
     </row>
     <row r="99">
@@ -5215,7 +7897,34 @@
         <v>0.036835937499999999</v>
       </c>
       <c r="Q99" s="0">
+        <v>0.036992187500000002</v>
+      </c>
+      <c r="R99" s="0">
+        <v>0.061132812500000001</v>
+      </c>
+      <c r="S99" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T99" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U99" s="0">
+        <v>0.013085937499999999</v>
+      </c>
+      <c r="V99" s="0">
+        <v>-0.00015625000000000361</v>
+      </c>
+      <c r="W99" s="0">
+        <v>0.27710000000000001</v>
+      </c>
+      <c r="X99" s="0">
+        <v>366.2470000000003</v>
+      </c>
+      <c r="Y99" s="0">
+        <v>797.35576210800036</v>
+      </c>
+      <c r="Z99" s="0">
+        <v>0.060618303159083183</v>
       </c>
     </row>
     <row r="100">
@@ -5266,7 +7975,34 @@
         <v>0.053906250000000003</v>
       </c>
       <c r="Q100" s="0">
+        <v>0.028554687500000002</v>
+      </c>
+      <c r="R100" s="0">
+        <v>0.052656250000000002</v>
+      </c>
+      <c r="S100" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T100" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U100" s="0">
+        <v>0.018632812499999998</v>
+      </c>
+      <c r="V100" s="0">
+        <v>0.025351562500000001</v>
+      </c>
+      <c r="W100" s="0">
+        <v>0.27435300000000001</v>
+      </c>
+      <c r="X100" s="0">
+        <v>384.54499999999962</v>
+      </c>
+      <c r="Y100" s="0">
+        <v>792.92796399600047</v>
+      </c>
+      <c r="Z100" s="0">
+        <v>0.014694271856666016</v>
       </c>
     </row>
     <row r="101">
@@ -5317,7 +8053,34 @@
         <v>0.0501171875</v>
       </c>
       <c r="Q101" s="0">
+        <v>0.024687500000000001</v>
+      </c>
+      <c r="R101" s="0">
+        <v>0.048867187499999999</v>
+      </c>
+      <c r="S101" s="0">
         <v>0.024179687500000002</v>
+      </c>
+      <c r="T101" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U101" s="0">
+        <v>0.023203124999999998</v>
+      </c>
+      <c r="V101" s="0">
+        <v>0.025429687499999999</v>
+      </c>
+      <c r="W101" s="0">
+        <v>0.28625499999999998</v>
+      </c>
+      <c r="X101" s="0">
+        <v>366.22999999999979</v>
+      </c>
+      <c r="Y101" s="0">
+        <v>744.02768904400091</v>
+      </c>
+      <c r="Z101" s="0">
+        <v>0.016257079844450018</v>
       </c>
     </row>
     <row r="102">
@@ -5368,7 +8131,34 @@
         <v>0.065234374999999997</v>
       </c>
       <c r="Q102" s="0">
+        <v>0.039296875000000002</v>
+      </c>
+      <c r="R102" s="0">
+        <v>0.063398437500000002</v>
+      </c>
+      <c r="S102" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T102" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U102" s="0">
+        <v>0.015625</v>
+      </c>
+      <c r="V102" s="0">
+        <v>0.025937499999999995</v>
+      </c>
+      <c r="W102" s="0">
+        <v>0.27862600000000004</v>
+      </c>
+      <c r="X102" s="0">
+        <v>384.54399999999987</v>
+      </c>
+      <c r="Y102" s="0">
+        <v>793.4668152029999</v>
+      </c>
+      <c r="Z102" s="0">
+        <v>0.010868643839754975</v>
       </c>
     </row>
     <row r="103">
@@ -5419,7 +8209,34 @@
         <v>0.058007812499999999</v>
       </c>
       <c r="Q103" s="0">
+        <v>0.032578124999999999</v>
+      </c>
+      <c r="R103" s="0">
+        <v>0.056718749999999998</v>
+      </c>
+      <c r="S103" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T103" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U103" s="0">
+        <v>0.013593750000000002</v>
+      </c>
+      <c r="V103" s="0">
+        <v>0.025429687499999999</v>
+      </c>
+      <c r="W103" s="0">
+        <v>0.29327400000000003</v>
+      </c>
+      <c r="X103" s="0">
+        <v>402.85400000000004</v>
+      </c>
+      <c r="Y103" s="0">
+        <v>816.36639124300018</v>
+      </c>
+      <c r="Z103" s="0">
+        <v>0.052533471829798853</v>
       </c>
     </row>
     <row r="104">
@@ -5470,7 +8287,34 @@
         <v>0.058710937500000004</v>
       </c>
       <c r="Q104" s="0">
+        <v>0.032031249999999997</v>
+      </c>
+      <c r="R104" s="0">
+        <v>0.056171875000000003</v>
+      </c>
+      <c r="S104" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T104" s="0">
+        <v>0.010507812500000005</v>
+      </c>
+      <c r="U104" s="0">
+        <v>0.019140625000000001</v>
+      </c>
+      <c r="V104" s="0">
+        <v>0.026679687500000007</v>
+      </c>
+      <c r="W104" s="0">
+        <v>0.28564500000000004</v>
+      </c>
+      <c r="X104" s="0">
+        <v>402.85699999999997</v>
+      </c>
+      <c r="Y104" s="0">
+        <v>765.58647761900056</v>
+      </c>
+      <c r="Z104" s="0">
+        <v>0.018444362915176708</v>
       </c>
     </row>
     <row r="105">
@@ -5521,7 +8365,34 @@
         <v>0.050156249999999999</v>
       </c>
       <c r="Q105" s="0">
+        <v>0.024179687500000002</v>
+      </c>
+      <c r="R105" s="0">
+        <v>0.048281249999999998</v>
+      </c>
+      <c r="S105" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T105" s="0">
+        <v>0.010507812500000002</v>
+      </c>
+      <c r="U105" s="0">
+        <v>0.014609374999999997</v>
+      </c>
+      <c r="V105" s="0">
+        <v>0.025976562499999998</v>
+      </c>
+      <c r="W105" s="0">
+        <v>0.27923499999999996</v>
+      </c>
+      <c r="X105" s="0">
+        <v>384.55899999999974</v>
+      </c>
+      <c r="Y105" s="0">
+        <v>762.73463533999939</v>
+      </c>
+      <c r="Z105" s="0">
+        <v>0.01348152811350747</v>
       </c>
     </row>
     <row r="106">
@@ -5572,7 +8443,34 @@
         <v>0.056445312500000004</v>
       </c>
       <c r="Q106" s="0">
+        <v>0.031054687500000001</v>
+      </c>
+      <c r="R106" s="0">
+        <v>0.055195312500000003</v>
+      </c>
+      <c r="S106" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T106" s="0">
+        <v>0.010507812500000002</v>
+      </c>
+      <c r="U106" s="0">
+        <v>0.015625000000000003</v>
+      </c>
+      <c r="V106" s="0">
+        <v>0.025390625000000003</v>
+      </c>
+      <c r="W106" s="0">
+        <v>0.29419000000000006</v>
+      </c>
+      <c r="X106" s="0">
+        <v>402.85300000000007</v>
+      </c>
+      <c r="Y106" s="0">
+        <v>784.22670872499998</v>
+      </c>
+      <c r="Z106" s="0">
+        <v>0.014163463823815902</v>
       </c>
     </row>
     <row r="107">
@@ -5623,7 +8521,34 @@
         <v>0.064609374999999997</v>
       </c>
       <c r="Q107" s="0">
+        <v>0.039335937500000001</v>
+      </c>
+      <c r="R107" s="0">
+        <v>0.0634765625</v>
+      </c>
+      <c r="S107" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T107" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U107" s="0">
+        <v>0.013124999999999998</v>
+      </c>
+      <c r="V107" s="0">
+        <v>0.025273437499999996</v>
+      </c>
+      <c r="W107" s="0">
+        <v>0.27404799999999996</v>
+      </c>
+      <c r="X107" s="0">
+        <v>384.54099999999994</v>
+      </c>
+      <c r="Y107" s="0">
+        <v>734.68423502600035</v>
+      </c>
+      <c r="Z107" s="0">
+        <v>0.0099896934176602926</v>
       </c>
     </row>
     <row r="108">
@@ -5674,7 +8599,34 @@
         <v>0.064101562500000001</v>
       </c>
       <c r="Q108" s="0">
+        <v>0.038789062499999999</v>
+      </c>
+      <c r="R108" s="0">
+        <v>0.062929687499999998</v>
+      </c>
+      <c r="S108" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T108" s="0">
+        <v>0.010546875000000004</v>
+      </c>
+      <c r="U108" s="0">
+        <v>0.016640624999999999</v>
+      </c>
+      <c r="V108" s="0">
+        <v>0.025312500000000002</v>
+      </c>
+      <c r="W108" s="0">
+        <v>0.28045599999999998</v>
+      </c>
+      <c r="X108" s="0">
+        <v>402.86300000000028</v>
+      </c>
+      <c r="Y108" s="0">
+        <v>724.16656560599995</v>
+      </c>
+      <c r="Z108" s="0">
+        <v>0.018826320490913682</v>
       </c>
     </row>
     <row r="109">
@@ -5725,7 +8677,34 @@
         <v>0.056718749999999998</v>
       </c>
       <c r="Q109" s="0">
+        <v>0.031367187499999998</v>
+      </c>
+      <c r="R109" s="0">
+        <v>0.055507812500000003</v>
+      </c>
+      <c r="S109" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T109" s="0">
+        <v>0.010507812500000005</v>
+      </c>
+      <c r="U109" s="0">
+        <v>0.013593750000000002</v>
+      </c>
+      <c r="V109" s="0">
+        <v>0.025351562500000001</v>
+      </c>
+      <c r="W109" s="0">
+        <v>0.30792200000000003</v>
+      </c>
+      <c r="X109" s="0">
+        <v>366.24500000000035</v>
+      </c>
+      <c r="Y109" s="0">
+        <v>747.75323997199985</v>
+      </c>
+      <c r="Z109" s="0">
+        <v>0.016639113503238406</v>
       </c>
     </row>
     <row r="110">
@@ -5776,7 +8755,34 @@
         <v>0.052226562500000004</v>
       </c>
       <c r="Q110" s="0">
+        <v>0.026914062500000002</v>
+      </c>
+      <c r="R110" s="0">
+        <v>0.051054687500000001</v>
+      </c>
+      <c r="S110" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T110" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U110" s="0">
+        <v>0.014140624999999997</v>
+      </c>
+      <c r="V110" s="0">
+        <v>0.025312500000000002</v>
+      </c>
+      <c r="W110" s="0">
+        <v>0.28930699999999998</v>
+      </c>
+      <c r="X110" s="0">
+        <v>384.55600000000004</v>
+      </c>
+      <c r="Y110" s="0">
+        <v>745.15109156800008</v>
+      </c>
+      <c r="Z110" s="0">
+        <v>0.070155039506364203</v>
       </c>
     </row>
     <row r="111">
@@ -5827,7 +8833,34 @@
         <v>0.057890625000000001</v>
       </c>
       <c r="Q111" s="0">
+        <v>0.032460937500000002</v>
+      </c>
+      <c r="R111" s="0">
+        <v>0.056562500000000002</v>
+      </c>
+      <c r="S111" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T111" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U111" s="0">
+        <v>0.014101562499999998</v>
+      </c>
+      <c r="V111" s="0">
+        <v>0.025429687499999999</v>
+      </c>
+      <c r="W111" s="0">
+        <v>0.29388400000000003</v>
+      </c>
+      <c r="X111" s="0">
+        <v>366.24699999999984</v>
+      </c>
+      <c r="Y111" s="0">
+        <v>725.81049146199939</v>
+      </c>
+      <c r="Z111" s="0">
+        <v>0.1303086588871977</v>
       </c>
     </row>
     <row r="112">
@@ -5878,7 +8911,34 @@
         <v>0.049531249999999999</v>
       </c>
       <c r="Q112" s="0">
+        <v>0.023984375000000002</v>
+      </c>
+      <c r="R112" s="0">
+        <v>0.048125000000000001</v>
+      </c>
+      <c r="S112" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T112" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U112" s="0">
+        <v>0.013124999999999998</v>
+      </c>
+      <c r="V112" s="0">
+        <v>0.025546874999999997</v>
+      </c>
+      <c r="W112" s="0">
+        <v>0.27710000000000001</v>
+      </c>
+      <c r="X112" s="0">
+        <v>366.22500000000014</v>
+      </c>
+      <c r="Y112" s="0">
+        <v>753.6667988690001</v>
+      </c>
+      <c r="Z112" s="0">
+        <v>0.012763706276738722</v>
       </c>
     </row>
     <row r="113">
@@ -5929,7 +8989,34 @@
         <v>0.061992187500000004</v>
       </c>
       <c r="Q113" s="0">
+        <v>0.036562499999999998</v>
+      </c>
+      <c r="R113" s="0">
+        <v>0.060664062500000004</v>
+      </c>
+      <c r="S113" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T113" s="0">
+        <v>0.010507812500000005</v>
+      </c>
+      <c r="U113" s="0">
+        <v>0.013085937500000006</v>
+      </c>
+      <c r="V113" s="0">
+        <v>0.025429687500000006</v>
+      </c>
+      <c r="W113" s="0">
+        <v>0.30517599999999995</v>
+      </c>
+      <c r="X113" s="0">
+        <v>347.9360000000006</v>
+      </c>
+      <c r="Y113" s="0">
+        <v>707.17625731599992</v>
+      </c>
+      <c r="Z113" s="0">
+        <v>0.025459919326703787</v>
       </c>
     </row>
     <row r="114">
@@ -5980,7 +9067,34 @@
         <v>0.057460937500000003</v>
       </c>
       <c r="Q114" s="0">
+        <v>0.032109375000000002</v>
+      </c>
+      <c r="R114" s="0">
+        <v>0.056289062500000001</v>
+      </c>
+      <c r="S114" s="0">
         <v>0.024179687500000002</v>
+      </c>
+      <c r="T114" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U114" s="0">
+        <v>0.014140624999999997</v>
+      </c>
+      <c r="V114" s="0">
+        <v>0.025351562500000001</v>
+      </c>
+      <c r="W114" s="0">
+        <v>0.28381299999999993</v>
+      </c>
+      <c r="X114" s="0">
+        <v>366.21800000000002</v>
+      </c>
+      <c r="Y114" s="0">
+        <v>723.87446550599998</v>
+      </c>
+      <c r="Z114" s="0">
+        <v>0.01547610389704703</v>
       </c>
     </row>
     <row r="115">
@@ -6031,7 +9145,34 @@
         <v>0.061289062499999998</v>
       </c>
       <c r="Q115" s="0">
+        <v>0.035976562500000003</v>
+      </c>
+      <c r="R115" s="0">
+        <v>0.060117187500000002</v>
+      </c>
+      <c r="S115" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T115" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U115" s="0">
+        <v>0.013124999999999998</v>
+      </c>
+      <c r="V115" s="0">
+        <v>0.025312499999999995</v>
+      </c>
+      <c r="W115" s="0">
+        <v>0.28198200000000001</v>
+      </c>
+      <c r="X115" s="0">
+        <v>384.55400000000009</v>
+      </c>
+      <c r="Y115" s="0">
+        <v>736.10710382499974</v>
+      </c>
+      <c r="Z115" s="0">
+        <v>0.043446494514099689</v>
       </c>
     </row>
     <row r="116">
@@ -6082,7 +9223,34 @@
         <v>0.054179687500000004</v>
       </c>
       <c r="Q116" s="0">
+        <v>0.028750000000000001</v>
+      </c>
+      <c r="R116" s="0">
+        <v>0.052890625000000004</v>
+      </c>
+      <c r="S116" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T116" s="0">
+        <v>0.010546875000000001</v>
+      </c>
+      <c r="U116" s="0">
+        <v>0.0161328125</v>
+      </c>
+      <c r="V116" s="0">
+        <v>0.025429687500000003</v>
+      </c>
+      <c r="W116" s="0">
+        <v>0.27801599999999999</v>
+      </c>
+      <c r="X116" s="0">
+        <v>384.54300000000035</v>
+      </c>
+      <c r="Y116" s="0">
+        <v>742.01055461600026</v>
+      </c>
+      <c r="Z116" s="0">
+        <v>0.94836003540360192</v>
       </c>
     </row>
     <row r="117">
@@ -6133,7 +9301,34 @@
         <v>0.052656250000000002</v>
       </c>
       <c r="Q117" s="0">
+        <v>0.027226562499999999</v>
+      </c>
+      <c r="R117" s="0">
+        <v>0.051367187500000001</v>
+      </c>
+      <c r="S117" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T117" s="0">
+        <v>0.010546875000000001</v>
+      </c>
+      <c r="U117" s="0">
+        <v>0.014101562500000001</v>
+      </c>
+      <c r="V117" s="0">
+        <v>0.025429687500000003</v>
+      </c>
+      <c r="W117" s="0">
+        <v>0.299987</v>
+      </c>
+      <c r="X117" s="0">
+        <v>402.85500000000002</v>
+      </c>
+      <c r="Y117" s="0">
+        <v>781.6274462299998</v>
+      </c>
+      <c r="Z117" s="0">
+        <v>0.0097111506382658117</v>
       </c>
     </row>
     <row r="118">
@@ -6184,7 +9379,34 @@
         <v>0.046132812500000002</v>
       </c>
       <c r="Q118" s="0">
+        <v>0.0206640625</v>
+      </c>
+      <c r="R118" s="0">
+        <v>0.044804687500000002</v>
+      </c>
+      <c r="S118" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T118" s="0">
+        <v>0.010546875000000001</v>
+      </c>
+      <c r="U118" s="0">
+        <v>0.013632812499999997</v>
+      </c>
+      <c r="V118" s="0">
+        <v>0.025468750000000002</v>
+      </c>
+      <c r="W118" s="0">
+        <v>0.28930599999999995</v>
+      </c>
+      <c r="X118" s="0">
+        <v>366.23799999999983</v>
+      </c>
+      <c r="Y118" s="0">
+        <v>812.62321501400038</v>
+      </c>
+      <c r="Z118" s="0">
+        <v>0.011003561250024586</v>
       </c>
     </row>
     <row r="119">
@@ -6235,7 +9457,34 @@
         <v>0.063437500000000008</v>
       </c>
       <c r="Q119" s="0">
+        <v>0.038046875000000001</v>
+      </c>
+      <c r="R119" s="0">
+        <v>0.0621875</v>
+      </c>
+      <c r="S119" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T119" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U119" s="0">
+        <v>0.015625</v>
+      </c>
+      <c r="V119" s="0">
+        <v>0.025390625000000007</v>
+      </c>
+      <c r="W119" s="0">
+        <v>0.27648900000000004</v>
+      </c>
+      <c r="X119" s="0">
+        <v>384.55500000000029</v>
+      </c>
+      <c r="Y119" s="0">
+        <v>732.64742016399941</v>
+      </c>
+      <c r="Z119" s="0">
+        <v>0.057778124548887977</v>
       </c>
     </row>
     <row r="120">
@@ -6286,7 +9535,34 @@
         <v>0.056992187499999999</v>
       </c>
       <c r="Q120" s="0">
+        <v>0.0315625</v>
+      </c>
+      <c r="R120" s="0">
+        <v>0.055703124999999999</v>
+      </c>
+      <c r="S120" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T120" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U120" s="0">
+        <v>0.015156250000000003</v>
+      </c>
+      <c r="V120" s="0">
+        <v>0.025429687499999999</v>
+      </c>
+      <c r="W120" s="0">
+        <v>0.305481</v>
+      </c>
+      <c r="X120" s="0">
+        <v>384.54799999999977</v>
+      </c>
+      <c r="Y120" s="0">
+        <v>708.70132928999965</v>
+      </c>
+      <c r="Z120" s="0">
+        <v>0.0091849248273608158</v>
       </c>
     </row>
     <row r="121">
@@ -6337,7 +9613,34 @@
         <v>0.057773437500000004</v>
       </c>
       <c r="Q121" s="0">
+        <v>0.032421875000000003</v>
+      </c>
+      <c r="R121" s="0">
+        <v>0.056562500000000002</v>
+      </c>
+      <c r="S121" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T121" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U121" s="0">
+        <v>0.012617187499999995</v>
+      </c>
+      <c r="V121" s="0">
+        <v>0.025351562500000001</v>
+      </c>
+      <c r="W121" s="0">
+        <v>0.29998799999999998</v>
+      </c>
+      <c r="X121" s="0">
+        <v>384.55699999999933</v>
+      </c>
+      <c r="Y121" s="0">
+        <v>733.27513670200028</v>
+      </c>
+      <c r="Z121" s="0">
+        <v>0.037133907890297947</v>
       </c>
     </row>
     <row r="122">
@@ -6390,6 +9693,33 @@
       <c r="Q122" s="0">
         <v>0</v>
       </c>
+      <c r="R122" s="0">
+        <v>0</v>
+      </c>
+      <c r="S122" s="0">
+        <v>0</v>
+      </c>
+      <c r="T122" s="0">
+        <v>0</v>
+      </c>
+      <c r="U122" s="0">
+        <v>0</v>
+      </c>
+      <c r="V122" s="0">
+        <v>0</v>
+      </c>
+      <c r="W122" s="0">
+        <v>0</v>
+      </c>
+      <c r="X122" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y122" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z122" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="0">
@@ -6439,7 +9769,34 @@
         <v>0.059218750000000001</v>
       </c>
       <c r="Q123" s="0">
+        <v>0.033632812499999998</v>
+      </c>
+      <c r="R123" s="0">
+        <v>0.057773437500000004</v>
+      </c>
+      <c r="S123" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T123" s="0">
+        <v>0.010546875000000004</v>
+      </c>
+      <c r="U123" s="0">
+        <v>0.016171875000000002</v>
+      </c>
+      <c r="V123" s="0">
+        <v>0.025585937500000003</v>
+      </c>
+      <c r="W123" s="0">
+        <v>0.28991700000000004</v>
+      </c>
+      <c r="X123" s="0">
+        <v>402.85800000000017</v>
+      </c>
+      <c r="Y123" s="0">
+        <v>745.89313692399992</v>
+      </c>
+      <c r="Z123" s="0">
+        <v>0.0096491743042743418</v>
       </c>
     </row>
     <row r="124">
@@ -6490,7 +9847,34 @@
         <v>0.048515625</v>
       </c>
       <c r="Q124" s="0">
+        <v>0.023164062499999999</v>
+      </c>
+      <c r="R124" s="0">
+        <v>0.047304687499999998</v>
+      </c>
+      <c r="S124" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T124" s="0">
+        <v>0.010546875000000004</v>
+      </c>
+      <c r="U124" s="0">
+        <v>0.014140625000000004</v>
+      </c>
+      <c r="V124" s="0">
+        <v>0.025351562500000001</v>
+      </c>
+      <c r="W124" s="0">
+        <v>0.307923</v>
+      </c>
+      <c r="X124" s="0">
+        <v>384.55099999999993</v>
+      </c>
+      <c r="Y124" s="0">
+        <v>729.66691682199962</v>
+      </c>
+      <c r="Z124" s="0">
+        <v>0.011298765351603814</v>
       </c>
     </row>
     <row r="125">
@@ -6541,7 +9925,34 @@
         <v>0.059179687500000001</v>
       </c>
       <c r="Q125" s="0">
+        <v>0.033710937500000003</v>
+      </c>
+      <c r="R125" s="0">
+        <v>0.057851562500000002</v>
+      </c>
+      <c r="S125" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T125" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U125" s="0">
+        <v>0.023203124999999998</v>
+      </c>
+      <c r="V125" s="0">
+        <v>0.025468749999999998</v>
+      </c>
+      <c r="W125" s="0">
+        <v>0.30029300000000003</v>
+      </c>
+      <c r="X125" s="0">
+        <v>384.53400000000033</v>
+      </c>
+      <c r="Y125" s="0">
+        <v>679.85497962000022</v>
+      </c>
+      <c r="Z125" s="0">
+        <v>0.018351348413293923</v>
       </c>
     </row>
     <row r="126">
@@ -6592,7 +10003,34 @@
         <v>0.057656249999999999</v>
       </c>
       <c r="Q126" s="0">
+        <v>0.032304687499999998</v>
+      </c>
+      <c r="R126" s="0">
+        <v>0.056445312500000004</v>
+      </c>
+      <c r="S126" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T126" s="0">
+        <v>0.010546875000000004</v>
+      </c>
+      <c r="U126" s="0">
+        <v>0.017695312500000004</v>
+      </c>
+      <c r="V126" s="0">
+        <v>0.025351562500000001</v>
+      </c>
+      <c r="W126" s="0">
+        <v>0.29724099999999998</v>
+      </c>
+      <c r="X126" s="0">
+        <v>366.23599999999988</v>
+      </c>
+      <c r="Y126" s="0">
+        <v>716.82524858800025</v>
+      </c>
+      <c r="Z126" s="0">
+        <v>0.043629467965429561</v>
       </c>
     </row>
     <row r="127">
@@ -6643,7 +10081,34 @@
         <v>0.052187499999999998</v>
       </c>
       <c r="Q127" s="0">
+        <v>0.026875</v>
+      </c>
+      <c r="R127" s="0">
+        <v>0.051015625000000002</v>
+      </c>
+      <c r="S127" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T127" s="0">
+        <v>0.010546875000000001</v>
+      </c>
+      <c r="U127" s="0">
+        <v>0.013125000000000001</v>
+      </c>
+      <c r="V127" s="0">
+        <v>0.025312499999999998</v>
+      </c>
+      <c r="W127" s="0">
+        <v>0.29357900000000003</v>
+      </c>
+      <c r="X127" s="0">
+        <v>366.22900000000004</v>
+      </c>
+      <c r="Y127" s="0">
+        <v>710.47975285400025</v>
+      </c>
+      <c r="Z127" s="0">
+        <v>0.010232568807211328</v>
       </c>
     </row>
     <row r="128">
@@ -6694,7 +10159,34 @@
         <v>0.062968750000000004</v>
       </c>
       <c r="Q128" s="0">
+        <v>0.037421875</v>
+      </c>
+      <c r="R128" s="0">
+        <v>0.061562499999999999</v>
+      </c>
+      <c r="S128" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T128" s="0">
+        <v>0.010546875000000004</v>
+      </c>
+      <c r="U128" s="0">
+        <v>0.022695312500000002</v>
+      </c>
+      <c r="V128" s="0">
+        <v>0.025546875000000004</v>
+      </c>
+      <c r="W128" s="0">
+        <v>0.29266399999999998</v>
+      </c>
+      <c r="X128" s="0">
+        <v>384.54200000000014</v>
+      </c>
+      <c r="Y128" s="0">
+        <v>707.62847548500031</v>
+      </c>
+      <c r="Z128" s="0">
+        <v>0.021125170323416629</v>
       </c>
     </row>
     <row r="129">
@@ -6745,7 +10237,34 @@
         <v>0.059179687500000001</v>
       </c>
       <c r="Q129" s="0">
+        <v>0.034023437500000003</v>
+      </c>
+      <c r="R129" s="0">
+        <v>0.058125000000000003</v>
+      </c>
+      <c r="S129" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T129" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U129" s="0">
+        <v>0.016132812499999996</v>
+      </c>
+      <c r="V129" s="0">
+        <v>0.025156249999999998</v>
+      </c>
+      <c r="W129" s="0">
+        <v>0.29144300000000001</v>
+      </c>
+      <c r="X129" s="0">
+        <v>366.2320000000002</v>
+      </c>
+      <c r="Y129" s="0">
+        <v>702.6828867820002</v>
+      </c>
+      <c r="Z129" s="0">
+        <v>0.055725082663506904</v>
       </c>
     </row>
     <row r="130">
@@ -6796,7 +10315,34 @@
         <v>0.056796875000000004</v>
       </c>
       <c r="Q130" s="0">
+        <v>0.031601562499999999</v>
+      </c>
+      <c r="R130" s="0">
+        <v>0.055703124999999999</v>
+      </c>
+      <c r="S130" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T130" s="0">
+        <v>0.010546875000000004</v>
+      </c>
+      <c r="U130" s="0">
+        <v>0.018164062500000001</v>
+      </c>
+      <c r="V130" s="0">
+        <v>0.025195312500000004</v>
+      </c>
+      <c r="W130" s="0">
+        <v>0.28137200000000007</v>
+      </c>
+      <c r="X130" s="0">
+        <v>402.85400000000027</v>
+      </c>
+      <c r="Y130" s="0">
+        <v>697.61508150699956</v>
+      </c>
+      <c r="Z130" s="0">
+        <v>0.0099740387131242707</v>
       </c>
     </row>
     <row r="131">
@@ -6847,7 +10393,34 @@
         <v>0.060468750000000002</v>
       </c>
       <c r="Q131" s="0">
+        <v>0.035273437499999998</v>
+      </c>
+      <c r="R131" s="0">
+        <v>0.059414062500000003</v>
+      </c>
+      <c r="S131" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T131" s="0">
+        <v>0.010546875000000004</v>
+      </c>
+      <c r="U131" s="0">
+        <v>0.013632812500000001</v>
+      </c>
+      <c r="V131" s="0">
+        <v>0.025195312500000004</v>
+      </c>
+      <c r="W131" s="0">
+        <v>0.29968299999999998</v>
+      </c>
+      <c r="X131" s="0">
+        <v>384.55100000000039</v>
+      </c>
+      <c r="Y131" s="0">
+        <v>678.52602174899948</v>
+      </c>
+      <c r="Z131" s="0">
+        <v>0.66560718798719931</v>
       </c>
     </row>
     <row r="132">
@@ -6898,7 +10471,34 @@
         <v>0.059609374999999999</v>
       </c>
       <c r="Q132" s="0">
+        <v>0.034453125000000001</v>
+      </c>
+      <c r="R132" s="0">
+        <v>0.058554687500000001</v>
+      </c>
+      <c r="S132" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T132" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U132" s="0">
+        <v>0.019687499999999997</v>
+      </c>
+      <c r="V132" s="0">
+        <v>0.025156249999999998</v>
+      </c>
+      <c r="W132" s="0">
+        <v>0.30090299999999998</v>
+      </c>
+      <c r="X132" s="0">
+        <v>366.22599999999989</v>
+      </c>
+      <c r="Y132" s="0">
+        <v>710.91262964800012</v>
+      </c>
+      <c r="Z132" s="0">
+        <v>0.07245190467771187</v>
       </c>
     </row>
     <row r="133">
@@ -6949,7 +10549,34 @@
         <v>0.021289062500000001</v>
       </c>
       <c r="Q133" s="0">
+        <v>0.021406250000000002</v>
+      </c>
+      <c r="R133" s="0">
+        <v>0.045546875000000001</v>
+      </c>
+      <c r="S133" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T133" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U133" s="0">
+        <v>0.015664062499999999</v>
+      </c>
+      <c r="V133" s="0">
+        <v>-0.00011718750000000097</v>
+      </c>
+      <c r="W133" s="0">
+        <v>0.30548099999999995</v>
+      </c>
+      <c r="X133" s="0">
+        <v>384.55200000000013</v>
+      </c>
+      <c r="Y133" s="0">
+        <v>680.46452201700026</v>
+      </c>
+      <c r="Z133" s="0">
+        <v>0.06069375812314616</v>
       </c>
     </row>
     <row r="134">
@@ -7000,7 +10627,34 @@
         <v>0.023359375000000002</v>
       </c>
       <c r="Q134" s="0">
+        <v>0.023476562499999999</v>
+      </c>
+      <c r="R134" s="0">
+        <v>0.047617187499999998</v>
+      </c>
+      <c r="S134" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T134" s="0">
+        <v>0.010585937500000003</v>
+      </c>
+      <c r="U134" s="0">
+        <v>0.0146484375</v>
+      </c>
+      <c r="V134" s="0">
+        <v>-0.0001171874999999975</v>
+      </c>
+      <c r="W134" s="0">
+        <v>0.30456599999999995</v>
+      </c>
+      <c r="X134" s="0">
+        <v>402.85300000000007</v>
+      </c>
+      <c r="Y134" s="0">
+        <v>727.80334976999984</v>
+      </c>
+      <c r="Z134" s="0">
+        <v>0.022727475170461562</v>
       </c>
     </row>
     <row r="135">
@@ -7051,7 +10705,34 @@
         <v>0.050742187500000001</v>
       </c>
       <c r="Q135" s="0">
+        <v>0.0248828125</v>
+      </c>
+      <c r="R135" s="0">
+        <v>0.049023437500000003</v>
+      </c>
+      <c r="S135" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T135" s="0">
+        <v>0.010546875000000001</v>
+      </c>
+      <c r="U135" s="0">
+        <v>0.01515625</v>
+      </c>
+      <c r="V135" s="0">
+        <v>0.025859375</v>
+      </c>
+      <c r="W135" s="0">
+        <v>0.30731199999999997</v>
+      </c>
+      <c r="X135" s="0">
+        <v>347.92500000000018</v>
+      </c>
+      <c r="Y135" s="0">
+        <v>712.14767293500063</v>
+      </c>
+      <c r="Z135" s="0">
+        <v>0.020184037359716644</v>
       </c>
     </row>
     <row r="136">
@@ -7102,7 +10783,34 @@
         <v>0.061093750000000002</v>
       </c>
       <c r="Q136" s="0">
+        <v>0.035625000000000004</v>
+      </c>
+      <c r="R136" s="0">
+        <v>0.059765625000000003</v>
+      </c>
+      <c r="S136" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T136" s="0">
+        <v>0.010585937499999996</v>
+      </c>
+      <c r="U136" s="0">
+        <v>0.015156249999999996</v>
+      </c>
+      <c r="V136" s="0">
+        <v>0.025468749999999998</v>
+      </c>
+      <c r="W136" s="0">
+        <v>0.30700699999999997</v>
+      </c>
+      <c r="X136" s="0">
+        <v>384.53800000000001</v>
+      </c>
+      <c r="Y136" s="0">
+        <v>683.66710691499998</v>
+      </c>
+      <c r="Z136" s="0">
+        <v>0.020942531019178597</v>
       </c>
     </row>
     <row r="137">
@@ -7153,7 +10861,34 @@
         <v>0.035390625000000002</v>
       </c>
       <c r="Q137" s="0">
+        <v>0.035429687500000001</v>
+      </c>
+      <c r="R137" s="0">
+        <v>0.0595703125</v>
+      </c>
+      <c r="S137" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T137" s="0">
+        <v>0.010585937499999996</v>
+      </c>
+      <c r="U137" s="0">
+        <v>0.021718750000000002</v>
+      </c>
+      <c r="V137" s="0">
+        <v>-3.9062499999999167e-05</v>
+      </c>
+      <c r="W137" s="0">
+        <v>0.30975399999999997</v>
+      </c>
+      <c r="X137" s="0">
+        <v>366.22600000000011</v>
+      </c>
+      <c r="Y137" s="0">
+        <v>755.00282345999995</v>
+      </c>
+      <c r="Z137" s="0">
+        <v>0.00069563903064194521</v>
       </c>
     </row>
     <row r="138">
@@ -7204,7 +10939,34 @@
         <v>0.059296874999999999</v>
       </c>
       <c r="Q138" s="0">
+        <v>0.033984375000000004</v>
+      </c>
+      <c r="R138" s="0">
+        <v>0.058085937500000004</v>
+      </c>
+      <c r="S138" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T138" s="0">
+        <v>0.012578124999999996</v>
+      </c>
+      <c r="U138" s="0">
+        <v>0.016679687499999998</v>
+      </c>
+      <c r="V138" s="0">
+        <v>0.025312499999999995</v>
+      </c>
+      <c r="W138" s="0">
+        <v>0.31555199999999994</v>
+      </c>
+      <c r="X138" s="0">
+        <v>366.23600000000033</v>
+      </c>
+      <c r="Y138" s="0">
+        <v>645.53378498800043</v>
+      </c>
+      <c r="Z138" s="0">
+        <v>0.011493266250460878</v>
       </c>
     </row>
     <row r="139">
@@ -7255,7 +11017,34 @@
         <v>0.059843750000000001</v>
       </c>
       <c r="Q139" s="0">
+        <v>0.034453125000000001</v>
+      </c>
+      <c r="R139" s="0">
+        <v>0.05859375</v>
+      </c>
+      <c r="S139" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T139" s="0">
+        <v>0.010585937499999996</v>
+      </c>
+      <c r="U139" s="0">
+        <v>0.023203124999999998</v>
+      </c>
+      <c r="V139" s="0">
+        <v>0.025390625</v>
+      </c>
+      <c r="W139" s="0">
+        <v>0.30670100000000006</v>
+      </c>
+      <c r="X139" s="0">
+        <v>366.23199999999997</v>
+      </c>
+      <c r="Y139" s="0">
+        <v>655.63257050000038</v>
+      </c>
+      <c r="Z139" s="0">
+        <v>0.0057309972640560095</v>
       </c>
     </row>
     <row r="140">
@@ -7306,7 +11095,34 @@
         <v>0.057109375000000004</v>
       </c>
       <c r="Q140" s="0">
+        <v>0.032070312500000003</v>
+      </c>
+      <c r="R140" s="0">
+        <v>0.056171875000000003</v>
+      </c>
+      <c r="S140" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T140" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U140" s="0">
+        <v>0.018671874999999998</v>
+      </c>
+      <c r="V140" s="0">
+        <v>0.025039062500000001</v>
+      </c>
+      <c r="W140" s="0">
+        <v>0.28625499999999998</v>
+      </c>
+      <c r="X140" s="0">
+        <v>347.92699999999968</v>
+      </c>
+      <c r="Y140" s="0">
+        <v>634.00747185599971</v>
+      </c>
+      <c r="Z140" s="0">
+        <v>0.01756240935165625</v>
       </c>
     </row>
     <row r="141">
@@ -7357,7 +11173,34 @@
         <v>0.051992187500000002</v>
       </c>
       <c r="Q141" s="0">
+        <v>0.026601562500000002</v>
+      </c>
+      <c r="R141" s="0">
+        <v>0.050742187500000001</v>
+      </c>
+      <c r="S141" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T141" s="0">
+        <v>0.010585937499999996</v>
+      </c>
+      <c r="U141" s="0">
+        <v>0.020703124999999996</v>
+      </c>
+      <c r="V141" s="0">
+        <v>0.025390625</v>
+      </c>
+      <c r="W141" s="0">
+        <v>0.28747599999999995</v>
+      </c>
+      <c r="X141" s="0">
+        <v>366.23299999999972</v>
+      </c>
+      <c r="Y141" s="0">
+        <v>644.94106126199995</v>
+      </c>
+      <c r="Z141" s="0">
+        <v>0.019267939781813511</v>
       </c>
     </row>
     <row r="142">
@@ -7408,7 +11251,34 @@
         <v>0.037070312500000001</v>
       </c>
       <c r="Q142" s="0">
+        <v>0.037148437499999999</v>
+      </c>
+      <c r="R142" s="0">
+        <v>0.061249999999999999</v>
+      </c>
+      <c r="S142" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T142" s="0">
+        <v>0.010585937500000003</v>
+      </c>
+      <c r="U142" s="0">
+        <v>0.014687499999999999</v>
+      </c>
+      <c r="V142" s="0">
+        <v>-7.8124999999998335e-05</v>
+      </c>
+      <c r="W142" s="0">
+        <v>0.29540999999999995</v>
+      </c>
+      <c r="X142" s="0">
+        <v>402.84699999999998</v>
+      </c>
+      <c r="Y142" s="0">
+        <v>639.15544587699992</v>
+      </c>
+      <c r="Z142" s="0">
+        <v>0.16362607624492459</v>
       </c>
     </row>
     <row r="143">
@@ -7459,7 +11329,34 @@
         <v>0.058828125000000002</v>
       </c>
       <c r="Q143" s="0">
+        <v>0.033750000000000002</v>
+      </c>
+      <c r="R143" s="0">
+        <v>0.057851562500000002</v>
+      </c>
+      <c r="S143" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T143" s="0">
+        <v>0.010585937499999996</v>
+      </c>
+      <c r="U143" s="0">
+        <v>0.015156249999999996</v>
+      </c>
+      <c r="V143" s="0">
+        <v>0.025078125</v>
+      </c>
+      <c r="W143" s="0">
+        <v>0.30395499999999992</v>
+      </c>
+      <c r="X143" s="0">
+        <v>366.23300000000017</v>
+      </c>
+      <c r="Y143" s="0">
+        <v>662.23106811700018</v>
+      </c>
+      <c r="Z143" s="0">
+        <v>0.0098008269608397328</v>
       </c>
     </row>
     <row r="144">
@@ -7510,7 +11407,34 @@
         <v>0.053515625000000004</v>
       </c>
       <c r="Q144" s="0">
+        <v>0.0283203125</v>
+      </c>
+      <c r="R144" s="0">
+        <v>0.052421875</v>
+      </c>
+      <c r="S144" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T144" s="0">
+        <v>0.010585937500000003</v>
+      </c>
+      <c r="U144" s="0">
+        <v>0.014140625000000004</v>
+      </c>
+      <c r="V144" s="0">
+        <v>0.025195312500000004</v>
+      </c>
+      <c r="W144" s="0">
+        <v>0.30456499999999997</v>
+      </c>
+      <c r="X144" s="0">
+        <v>384.54299999999989</v>
+      </c>
+      <c r="Y144" s="0">
+        <v>660.46933675499986</v>
+      </c>
+      <c r="Z144" s="0">
+        <v>0.013567862268514723</v>
       </c>
     </row>
     <row r="145">
@@ -7561,7 +11485,34 @@
         <v>0.030820312500000002</v>
       </c>
       <c r="Q145" s="0">
+        <v>0.0309375</v>
+      </c>
+      <c r="R145" s="0">
+        <v>0.055078124999999999</v>
+      </c>
+      <c r="S145" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T145" s="0">
+        <v>0.010585937500000003</v>
+      </c>
+      <c r="U145" s="0">
+        <v>0.015703124999999998</v>
+      </c>
+      <c r="V145" s="0">
+        <v>-0.0001171874999999975</v>
+      </c>
+      <c r="W145" s="0">
+        <v>0.28747600000000001</v>
+      </c>
+      <c r="X145" s="0">
+        <v>366.23599999999988</v>
+      </c>
+      <c r="Y145" s="0">
+        <v>693.73330657200017</v>
+      </c>
+      <c r="Z145" s="0">
+        <v>0.014501551450256455</v>
       </c>
     </row>
     <row r="146">
@@ -7612,7 +11563,34 @@
         <v>0.027460937500000001</v>
       </c>
       <c r="Q146" s="0">
+        <v>0.027539062499999999</v>
+      </c>
+      <c r="R146" s="0">
+        <v>0.051679687500000002</v>
+      </c>
+      <c r="S146" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T146" s="0">
+        <v>0.0105859375</v>
+      </c>
+      <c r="U146" s="0">
+        <v>0.016679687500000002</v>
+      </c>
+      <c r="V146" s="0">
+        <v>-7.8124999999998335e-05</v>
+      </c>
+      <c r="W146" s="0">
+        <v>0.31250000000000006</v>
+      </c>
+      <c r="X146" s="0">
+        <v>366.23700000000008</v>
+      </c>
+      <c r="Y146" s="0">
+        <v>629.09889157599969</v>
+      </c>
+      <c r="Z146" s="0">
+        <v>0.0087039991488844972</v>
       </c>
     </row>
     <row r="147">
@@ -7663,7 +11641,34 @@
         <v>0.057187500000000002</v>
       </c>
       <c r="Q147" s="0">
+        <v>0.032109375000000002</v>
+      </c>
+      <c r="R147" s="0">
+        <v>0.056210937500000002</v>
+      </c>
+      <c r="S147" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T147" s="0">
+        <v>0.012578124999999996</v>
+      </c>
+      <c r="U147" s="0">
+        <v>0.013124999999999998</v>
+      </c>
+      <c r="V147" s="0">
+        <v>0.025078125</v>
+      </c>
+      <c r="W147" s="0">
+        <v>0.31372100000000003</v>
+      </c>
+      <c r="X147" s="0">
+        <v>384.53299999999979</v>
+      </c>
+      <c r="Y147" s="0">
+        <v>700.89633763799998</v>
+      </c>
+      <c r="Z147" s="0">
+        <v>0.018554812685121023</v>
       </c>
     </row>
     <row r="148">
@@ -7714,7 +11719,34 @@
         <v>0.02375</v>
       </c>
       <c r="Q148" s="0">
+        <v>0.023828125000000002</v>
+      </c>
+      <c r="R148" s="0">
+        <v>0.047929687499999998</v>
+      </c>
+      <c r="S148" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T148" s="0">
+        <v>0.010546875000000001</v>
+      </c>
+      <c r="U148" s="0">
+        <v>0.015664062499999996</v>
+      </c>
+      <c r="V148" s="0">
+        <v>-7.8125000000001804e-05</v>
+      </c>
+      <c r="W148" s="0">
+        <v>0.28625499999999993</v>
+      </c>
+      <c r="X148" s="0">
+        <v>366.22300000000007</v>
+      </c>
+      <c r="Y148" s="0">
+        <v>639.47901014399986</v>
+      </c>
+      <c r="Z148" s="0">
+        <v>0.059258741832732921</v>
       </c>
     </row>
     <row r="149">
@@ -7765,7 +11797,34 @@
         <v>0.048984375000000004</v>
       </c>
       <c r="Q149" s="0">
+        <v>0.023789062499999999</v>
+      </c>
+      <c r="R149" s="0">
+        <v>0.047890624999999999</v>
+      </c>
+      <c r="S149" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T149" s="0">
+        <v>0.013085937499999999</v>
+      </c>
+      <c r="U149" s="0">
+        <v>0.016171875000000002</v>
+      </c>
+      <c r="V149" s="0">
+        <v>0.025195312500000004</v>
+      </c>
+      <c r="W149" s="0">
+        <v>0.319519</v>
+      </c>
+      <c r="X149" s="0">
+        <v>347.92699999999968</v>
+      </c>
+      <c r="Y149" s="0">
+        <v>631.9134256079999</v>
+      </c>
+      <c r="Z149" s="0">
+        <v>0.00970230820100558</v>
       </c>
     </row>
     <row r="150">
@@ -7816,7 +11875,34 @@
         <v>0.064453125</v>
       </c>
       <c r="Q150" s="0">
+        <v>0.039218750000000004</v>
+      </c>
+      <c r="R150" s="0">
+        <v>0.063320312500000003</v>
+      </c>
+      <c r="S150" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T150" s="0">
+        <v>0.010585937499999996</v>
+      </c>
+      <c r="U150" s="0">
+        <v>0.019687499999999997</v>
+      </c>
+      <c r="V150" s="0">
+        <v>0.025234374999999996</v>
+      </c>
+      <c r="W150" s="0">
+        <v>0.32440200000000002</v>
+      </c>
+      <c r="X150" s="0">
+        <v>366.23900000000003</v>
+      </c>
+      <c r="Y150" s="0">
+        <v>624.53860832000009</v>
+      </c>
+      <c r="Z150" s="0">
+        <v>0.011064309563483936</v>
       </c>
     </row>
     <row r="151">
@@ -7867,7 +11953,34 @@
         <v>0.058789062500000003</v>
       </c>
       <c r="Q151" s="0">
+        <v>0.033750000000000002</v>
+      </c>
+      <c r="R151" s="0">
+        <v>0.057851562500000002</v>
+      </c>
+      <c r="S151" s="0">
         <v>0.0241015625</v>
+      </c>
+      <c r="T151" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U151" s="0">
+        <v>0.017656249999999998</v>
+      </c>
+      <c r="V151" s="0">
+        <v>0.025039062500000001</v>
+      </c>
+      <c r="W151" s="0">
+        <v>0.30365000000000003</v>
+      </c>
+      <c r="X151" s="0">
+        <v>384.52800000000002</v>
+      </c>
+      <c r="Y151" s="0">
+        <v>629.70787661899976</v>
+      </c>
+      <c r="Z151" s="0">
+        <v>0.023014836393544812</v>
       </c>
     </row>
     <row r="152">
@@ -7918,7 +12031,34 @@
         <v>0.057148437500000003</v>
       </c>
       <c r="Q152" s="0">
+        <v>0.032187500000000001</v>
+      </c>
+      <c r="R152" s="0">
+        <v>0.055859375000000003</v>
+      </c>
+      <c r="S152" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T152" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U152" s="0">
+        <v>0.015664062499999999</v>
+      </c>
+      <c r="V152" s="0">
+        <v>0.024960937500000002</v>
+      </c>
+      <c r="W152" s="0">
+        <v>0.28656000000000004</v>
+      </c>
+      <c r="X152" s="0">
+        <v>366.23799999999983</v>
+      </c>
+      <c r="Y152" s="0">
+        <v>766.14324562799948</v>
+      </c>
+      <c r="Z152" s="0">
+        <v>0.011505649862313958</v>
       </c>
     </row>
     <row r="153">
@@ -7969,7 +12109,34 @@
         <v>0.035742187500000001</v>
       </c>
       <c r="Q153" s="0">
+        <v>0.036328125000000003</v>
+      </c>
+      <c r="R153" s="0">
+        <v>0.059999999999999998</v>
+      </c>
+      <c r="S153" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T153" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U153" s="0">
+        <v>0.013124999999999998</v>
+      </c>
+      <c r="V153" s="0">
+        <v>-0.00058593750000000139</v>
+      </c>
+      <c r="W153" s="0">
+        <v>0.29266300000000006</v>
+      </c>
+      <c r="X153" s="0">
+        <v>347.92700000000013</v>
+      </c>
+      <c r="Y153" s="0">
+        <v>736.87725172399996</v>
+      </c>
+      <c r="Z153" s="0">
+        <v>0.075273378762968218</v>
       </c>
     </row>
     <row r="154">
@@ -8020,7 +12187,34 @@
         <v>0.05890625</v>
       </c>
       <c r="Q154" s="0">
+        <v>0.033437500000000002</v>
+      </c>
+      <c r="R154" s="0">
+        <v>0.057578125000000001</v>
+      </c>
+      <c r="S154" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T154" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U154" s="0">
+        <v>0.019648437499999998</v>
+      </c>
+      <c r="V154" s="0">
+        <v>0.025468749999999998</v>
+      </c>
+      <c r="W154" s="0">
+        <v>0.30364999999999998</v>
+      </c>
+      <c r="X154" s="0">
+        <v>366.23099999999977</v>
+      </c>
+      <c r="Y154" s="0">
+        <v>775.48225824000019</v>
+      </c>
+      <c r="Z154" s="0">
+        <v>0.011158934590394005</v>
       </c>
     </row>
     <row r="155">
@@ -8071,7 +12265,34 @@
         <v>0.063437500000000008</v>
       </c>
       <c r="Q155" s="0">
+        <v>0.037929687500000003</v>
+      </c>
+      <c r="R155" s="0">
+        <v>0.062070312500000002</v>
+      </c>
+      <c r="S155" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T155" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U155" s="0">
+        <v>0.014609375000000001</v>
+      </c>
+      <c r="V155" s="0">
+        <v>0.025507812500000004</v>
+      </c>
+      <c r="W155" s="0">
+        <v>0.28533900000000001</v>
+      </c>
+      <c r="X155" s="0">
+        <v>366.23699999999963</v>
+      </c>
+      <c r="Y155" s="0">
+        <v>771.82706610600007</v>
+      </c>
+      <c r="Z155" s="0">
+        <v>0.012135875055505055</v>
       </c>
     </row>
     <row r="156">
@@ -8122,7 +12343,34 @@
         <v>0.029335937499999999</v>
       </c>
       <c r="Q156" s="0">
+        <v>0.0299609375</v>
+      </c>
+      <c r="R156" s="0">
+        <v>0.053632812500000002</v>
+      </c>
+      <c r="S156" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T156" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U156" s="0">
+        <v>0.015664062499999999</v>
+      </c>
+      <c r="V156" s="0">
+        <v>-0.00062500000000000056</v>
+      </c>
+      <c r="W156" s="0">
+        <v>0.28686499999999993</v>
+      </c>
+      <c r="X156" s="0">
+        <v>366.21600000000001</v>
+      </c>
+      <c r="Y156" s="0">
+        <v>738.23681899200028</v>
+      </c>
+      <c r="Z156" s="0">
+        <v>0.013255068991891902</v>
       </c>
     </row>
     <row r="157">
@@ -8173,7 +12421,34 @@
         <v>0.050664062500000002</v>
       </c>
       <c r="Q157" s="0">
+        <v>0.025078125</v>
+      </c>
+      <c r="R157" s="0">
+        <v>0.049218749999999999</v>
+      </c>
+      <c r="S157" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T157" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U157" s="0">
+        <v>0.014609375000000001</v>
+      </c>
+      <c r="V157" s="0">
+        <v>0.025585937500000003</v>
+      </c>
+      <c r="W157" s="0">
+        <v>0.28076200000000007</v>
+      </c>
+      <c r="X157" s="0">
+        <v>366.25099999999884</v>
+      </c>
+      <c r="Y157" s="0">
+        <v>770.73513108400039</v>
+      </c>
+      <c r="Z157" s="0">
+        <v>0.0099726669859082785</v>
       </c>
     </row>
     <row r="158">
@@ -8224,7 +12499,34 @@
         <v>0.023554687500000001</v>
       </c>
       <c r="Q158" s="0">
+        <v>0.023671875000000002</v>
+      </c>
+      <c r="R158" s="0">
+        <v>0.047812500000000001</v>
+      </c>
+      <c r="S158" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T158" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U158" s="0">
+        <v>0.015625</v>
+      </c>
+      <c r="V158" s="0">
+        <v>-0.00011718750000000097</v>
+      </c>
+      <c r="W158" s="0">
+        <v>0.29083300000000006</v>
+      </c>
+      <c r="X158" s="0">
+        <v>366.2510000000002</v>
+      </c>
+      <c r="Y158" s="0">
+        <v>789.20617362999974</v>
+      </c>
+      <c r="Z158" s="0">
+        <v>0.012765750920770784</v>
       </c>
     </row>
     <row r="159">
@@ -8275,7 +12577,34 @@
         <v>0.033085937500000002</v>
       </c>
       <c r="Q159" s="0">
+        <v>0.033203125</v>
+      </c>
+      <c r="R159" s="0">
+        <v>0.057343749999999999</v>
+      </c>
+      <c r="S159" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T159" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U159" s="0">
+        <v>0.016640624999999999</v>
+      </c>
+      <c r="V159" s="0">
+        <v>-0.0001171874999999975</v>
+      </c>
+      <c r="W159" s="0">
+        <v>0.29388500000000006</v>
+      </c>
+      <c r="X159" s="0">
+        <v>384.54800000000023</v>
+      </c>
+      <c r="Y159" s="0">
+        <v>802.34633303999999</v>
+      </c>
+      <c r="Z159" s="0">
+        <v>0.076387534867366241</v>
       </c>
     </row>
     <row r="160">
@@ -8326,7 +12655,34 @@
         <v>0.051484374999999999</v>
       </c>
       <c r="Q160" s="0">
+        <v>0.0262109375</v>
+      </c>
+      <c r="R160" s="0">
+        <v>0.049882812499999998</v>
+      </c>
+      <c r="S160" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T160" s="0">
+        <v>0.010039062499999998</v>
+      </c>
+      <c r="U160" s="0">
+        <v>0.017148437499999999</v>
+      </c>
+      <c r="V160" s="0">
+        <v>0.025273437499999999</v>
+      </c>
+      <c r="W160" s="0">
+        <v>0.27130100000000001</v>
+      </c>
+      <c r="X160" s="0">
+        <v>384.54600000000028</v>
+      </c>
+      <c r="Y160" s="0">
+        <v>771.56380865700066</v>
+      </c>
+      <c r="Z160" s="0">
+        <v>0.057041211523089233</v>
       </c>
     </row>
     <row r="161">
@@ -8377,7 +12733,34 @@
         <v>0.018359375000000001</v>
       </c>
       <c r="Q161" s="0">
+        <v>0.020781250000000001</v>
+      </c>
+      <c r="R161" s="0">
+        <v>0.044453125000000003</v>
+      </c>
+      <c r="S161" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T161" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U161" s="0">
+        <v>0.016132812500000003</v>
+      </c>
+      <c r="V161" s="0">
+        <v>-0.0024218750000000004</v>
+      </c>
+      <c r="W161" s="0">
+        <v>0.27038599999999996</v>
+      </c>
+      <c r="X161" s="0">
+        <v>384.54200000000014</v>
+      </c>
+      <c r="Y161" s="0">
+        <v>740.95682859399994</v>
+      </c>
+      <c r="Z161" s="0">
+        <v>65535</v>
       </c>
     </row>
     <row r="162">
@@ -8428,7 +12811,34 @@
         <v>0.059531250000000001</v>
       </c>
       <c r="Q162" s="0">
+        <v>0.034531249999999999</v>
+      </c>
+      <c r="R162" s="0">
+        <v>0.058203125000000001</v>
+      </c>
+      <c r="S162" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T162" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U162" s="0">
+        <v>0.012617187500000002</v>
+      </c>
+      <c r="V162" s="0">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="W162" s="0">
+        <v>0.27465800000000001</v>
+      </c>
+      <c r="X162" s="0">
+        <v>366.2320000000002</v>
+      </c>
+      <c r="Y162" s="0">
+        <v>747.68902880799988</v>
+      </c>
+      <c r="Z162" s="0">
+        <v>0.024538573411139877</v>
       </c>
     </row>
     <row r="163">
@@ -8479,7 +12889,34 @@
         <v>0.052031250000000001</v>
       </c>
       <c r="Q163" s="0">
+        <v>0.026484375000000001</v>
+      </c>
+      <c r="R163" s="0">
+        <v>0.050625000000000003</v>
+      </c>
+      <c r="S163" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T163" s="0">
+        <v>0.010507812500000002</v>
+      </c>
+      <c r="U163" s="0">
+        <v>0.014609374999999997</v>
+      </c>
+      <c r="V163" s="0">
+        <v>0.025546875</v>
+      </c>
+      <c r="W163" s="0">
+        <v>0.29327400000000003</v>
+      </c>
+      <c r="X163" s="0">
+        <v>347.91800000000012</v>
+      </c>
+      <c r="Y163" s="0">
+        <v>759.20126282400088</v>
+      </c>
+      <c r="Z163" s="0">
+        <v>0.018403095524141759</v>
       </c>
     </row>
     <row r="164">
@@ -8530,7 +12967,34 @@
         <v>0.0283203125</v>
       </c>
       <c r="Q164" s="0">
+        <v>0.028945312500000001</v>
+      </c>
+      <c r="R164" s="0">
+        <v>0.052617187500000002</v>
+      </c>
+      <c r="S164" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T164" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U164" s="0">
+        <v>0.016132812500000003</v>
+      </c>
+      <c r="V164" s="0">
+        <v>-0.00062500000000000056</v>
+      </c>
+      <c r="W164" s="0">
+        <v>0.27709899999999998</v>
+      </c>
+      <c r="X164" s="0">
+        <v>476.09900000000016</v>
+      </c>
+      <c r="Y164" s="0">
+        <v>856.48199940899985</v>
+      </c>
+      <c r="Z164" s="0">
+        <v>0.016201918937447945</v>
       </c>
     </row>
     <row r="165">
@@ -8581,7 +13045,34 @@
         <v>0.065390625000000008</v>
       </c>
       <c r="Q165" s="0">
+        <v>0.039960937500000002</v>
+      </c>
+      <c r="R165" s="0">
+        <v>0.064101562500000001</v>
+      </c>
+      <c r="S165" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T165" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U165" s="0">
+        <v>0.015156249999999996</v>
+      </c>
+      <c r="V165" s="0">
+        <v>0.025429687500000006</v>
+      </c>
+      <c r="W165" s="0">
+        <v>0.29083300000000001</v>
+      </c>
+      <c r="X165" s="0">
+        <v>366.23599999999988</v>
+      </c>
+      <c r="Y165" s="0">
+        <v>736.23874284600015</v>
+      </c>
+      <c r="Z165" s="0">
+        <v>0.072225844156897881</v>
       </c>
     </row>
     <row r="166">
@@ -8632,7 +13123,34 @@
         <v>0.048007812500000004</v>
       </c>
       <c r="Q166" s="0">
+        <v>0.022539062500000002</v>
+      </c>
+      <c r="R166" s="0">
+        <v>0.046679687500000004</v>
+      </c>
+      <c r="S166" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T166" s="0">
+        <v>0.010507812500000002</v>
+      </c>
+      <c r="U166" s="0">
+        <v>0.0161328125</v>
+      </c>
+      <c r="V166" s="0">
+        <v>0.025468750000000002</v>
+      </c>
+      <c r="W166" s="0">
+        <v>0.29510499999999995</v>
+      </c>
+      <c r="X166" s="0">
+        <v>384.55000000000018</v>
+      </c>
+      <c r="Y166" s="0">
+        <v>792.68024440500039</v>
+      </c>
+      <c r="Z166" s="0">
+        <v>0.071867784102531543</v>
       </c>
     </row>
     <row r="167">
@@ -8683,7 +13201,34 @@
         <v>0.0462109375</v>
       </c>
       <c r="Q167" s="0">
+        <v>0.020937500000000001</v>
+      </c>
+      <c r="R167" s="0">
+        <v>0.044609375</v>
+      </c>
+      <c r="S167" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T167" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U167" s="0">
+        <v>0.014648437499999997</v>
+      </c>
+      <c r="V167" s="0">
+        <v>0.025273437499999999</v>
+      </c>
+      <c r="W167" s="0">
+        <v>0.28472899999999995</v>
+      </c>
+      <c r="X167" s="0">
+        <v>384.53599999999983</v>
+      </c>
+      <c r="Y167" s="0">
+        <v>802.57997476100081</v>
+      </c>
+      <c r="Z167" s="0">
+        <v>0.006537762746350863</v>
       </c>
     </row>
     <row r="168">
@@ -8734,7 +13279,34 @@
         <v>0.037578125000000004</v>
       </c>
       <c r="Q168" s="0">
+        <v>0.037734375000000001</v>
+      </c>
+      <c r="R168" s="0">
+        <v>0.061874999999999999</v>
+      </c>
+      <c r="S168" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T168" s="0">
+        <v>0.011015625000000001</v>
+      </c>
+      <c r="U168" s="0">
+        <v>0.016132812500000003</v>
+      </c>
+      <c r="V168" s="0">
+        <v>-0.00015624999999999667</v>
+      </c>
+      <c r="W168" s="0">
+        <v>0.27648899999999998</v>
+      </c>
+      <c r="X168" s="0">
+        <v>384.54500000000007</v>
+      </c>
+      <c r="Y168" s="0">
+        <v>748.56491840099989</v>
+      </c>
+      <c r="Z168" s="0">
+        <v>0.018642596251451017</v>
       </c>
     </row>
     <row r="169">
@@ -8785,7 +13357,34 @@
         <v>0.059765625000000003</v>
       </c>
       <c r="Q169" s="0">
+        <v>0.034804687500000001</v>
+      </c>
+      <c r="R169" s="0">
+        <v>0.058476562500000002</v>
+      </c>
+      <c r="S169" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T169" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U169" s="0">
+        <v>0.013124999999999998</v>
+      </c>
+      <c r="V169" s="0">
+        <v>0.024960937500000002</v>
+      </c>
+      <c r="W169" s="0">
+        <v>0.28076199999999996</v>
+      </c>
+      <c r="X169" s="0">
+        <v>439.47600000000011</v>
+      </c>
+      <c r="Y169" s="0">
+        <v>780.62105847899966</v>
+      </c>
+      <c r="Z169" s="0">
+        <v>0.011817389949868078</v>
       </c>
     </row>
     <row r="170">
@@ -8836,7 +13435,34 @@
         <v>0.027773437500000001</v>
       </c>
       <c r="Q170" s="0">
+        <v>0.028359374999999999</v>
+      </c>
+      <c r="R170" s="0">
+        <v>0.052031250000000001</v>
+      </c>
+      <c r="S170" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T170" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U170" s="0">
+        <v>0.016640624999999999</v>
+      </c>
+      <c r="V170" s="0">
+        <v>-0.00058593749999999792</v>
+      </c>
+      <c r="W170" s="0">
+        <v>0.28625499999999998</v>
+      </c>
+      <c r="X170" s="0">
+        <v>347.9369999999999</v>
+      </c>
+      <c r="Y170" s="0">
+        <v>775.56799715199941</v>
+      </c>
+      <c r="Z170" s="0">
+        <v>0.024579577834804262</v>
       </c>
     </row>
     <row r="171">
@@ -8887,7 +13513,34 @@
         <v>0.048359375000000003</v>
       </c>
       <c r="Q171" s="0">
+        <v>0.0224609375</v>
+      </c>
+      <c r="R171" s="0">
+        <v>0.046601562499999999</v>
+      </c>
+      <c r="S171" s="0">
         <v>0.024140624999999999</v>
+      </c>
+      <c r="T171" s="0">
+        <v>0.010507812499999998</v>
+      </c>
+      <c r="U171" s="0">
+        <v>0.020156250000000001</v>
+      </c>
+      <c r="V171" s="0">
+        <v>0.025898437500000003</v>
+      </c>
+      <c r="W171" s="0">
+        <v>0.28717000000000004</v>
+      </c>
+      <c r="X171" s="0">
+        <v>384.55099999999948</v>
+      </c>
+      <c r="Y171" s="0">
+        <v>798.80456352800002</v>
+      </c>
+      <c r="Z171" s="0">
+        <v>0.021521417450744481</v>
       </c>
     </row>
     <row r="172">
@@ -8938,7 +13591,34 @@
         <v>0.065468750000000006</v>
       </c>
       <c r="Q172" s="0">
+        <v>0.040546875000000003</v>
+      </c>
+      <c r="R172" s="0">
+        <v>0.064179687499999999</v>
+      </c>
+      <c r="S172" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T172" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U172" s="0">
+        <v>0.016132812499999996</v>
+      </c>
+      <c r="V172" s="0">
+        <v>0.024921875000000003</v>
+      </c>
+      <c r="W172" s="0">
+        <v>0.28503400000000001</v>
+      </c>
+      <c r="X172" s="0">
+        <v>366.23599999999988</v>
+      </c>
+      <c r="Y172" s="0">
+        <v>811.41687603399987</v>
+      </c>
+      <c r="Z172" s="0">
+        <v>0.03512889371997719</v>
       </c>
     </row>
     <row r="173">
@@ -8989,7 +13669,34 @@
         <v>0.059062500000000004</v>
       </c>
       <c r="Q173" s="0">
+        <v>0.034101562500000002</v>
+      </c>
+      <c r="R173" s="0">
+        <v>0.057773437500000004</v>
+      </c>
+      <c r="S173" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T173" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U173" s="0">
+        <v>0.013124999999999998</v>
+      </c>
+      <c r="V173" s="0">
+        <v>0.024960937500000002</v>
+      </c>
+      <c r="W173" s="0">
+        <v>0.27313200000000004</v>
+      </c>
+      <c r="X173" s="0">
+        <v>402.86999999999989</v>
+      </c>
+      <c r="Y173" s="0">
+        <v>856.08216733999961</v>
+      </c>
+      <c r="Z173" s="0">
+        <v>0.018712476122874695</v>
       </c>
     </row>
     <row r="174">
@@ -9040,7 +13747,34 @@
         <v>0.050625000000000003</v>
       </c>
       <c r="Q174" s="0">
+        <v>0.025625000000000002</v>
+      </c>
+      <c r="R174" s="0">
+        <v>0.049296875000000004</v>
+      </c>
+      <c r="S174" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T174" s="0">
+        <v>0.010078125</v>
+      </c>
+      <c r="U174" s="0">
+        <v>0.019179687500000001</v>
+      </c>
+      <c r="V174" s="0">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="W174" s="0">
+        <v>0.28625500000000004</v>
+      </c>
+      <c r="X174" s="0">
+        <v>366.23000000000002</v>
+      </c>
+      <c r="Y174" s="0">
+        <v>736.07882939400042</v>
+      </c>
+      <c r="Z174" s="0">
+        <v>0.013074751575192237</v>
       </c>
     </row>
     <row r="175">
@@ -9091,7 +13825,34 @@
         <v>0.021601562500000001</v>
       </c>
       <c r="Q175" s="0">
+        <v>0.022226562500000002</v>
+      </c>
+      <c r="R175" s="0">
+        <v>0.0458984375</v>
+      </c>
+      <c r="S175" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T175" s="0">
+        <v>0.010039062499999998</v>
+      </c>
+      <c r="U175" s="0">
+        <v>0.0161328125</v>
+      </c>
+      <c r="V175" s="0">
+        <v>-0.00062500000000000056</v>
+      </c>
+      <c r="W175" s="0">
+        <v>0.27862600000000004</v>
+      </c>
+      <c r="X175" s="0">
+        <v>402.85599999999977</v>
+      </c>
+      <c r="Y175" s="0">
+        <v>750.01436617799936</v>
+      </c>
+      <c r="Z175" s="0">
+        <v>0.011951520628348585</v>
       </c>
     </row>
     <row r="176">
@@ -9142,7 +13903,34 @@
         <v>0.0341796875</v>
       </c>
       <c r="Q176" s="0">
+        <v>0.034765625000000001</v>
+      </c>
+      <c r="R176" s="0">
+        <v>0.058437500000000003</v>
+      </c>
+      <c r="S176" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T176" s="0">
+        <v>0.010078125</v>
+      </c>
+      <c r="U176" s="0">
+        <v>0.015156250000000003</v>
+      </c>
+      <c r="V176" s="0">
+        <v>-0.00058593750000000139</v>
+      </c>
+      <c r="W176" s="0">
+        <v>0.28045700000000001</v>
+      </c>
+      <c r="X176" s="0">
+        <v>366.23300000000017</v>
+      </c>
+      <c r="Y176" s="0">
+        <v>749.9308855940003</v>
+      </c>
+      <c r="Z176" s="0">
+        <v>0.017980454172642199</v>
       </c>
     </row>
     <row r="177">
@@ -9193,7 +13981,34 @@
         <v>0.047890624999999999</v>
       </c>
       <c r="Q177" s="0">
+        <v>0.022812499999999999</v>
+      </c>
+      <c r="R177" s="0">
+        <v>0.046484375000000001</v>
+      </c>
+      <c r="S177" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T177" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U177" s="0">
+        <v>0.018671875000000004</v>
+      </c>
+      <c r="V177" s="0">
+        <v>0.025078125</v>
+      </c>
+      <c r="W177" s="0">
+        <v>0.29052700000000004</v>
+      </c>
+      <c r="X177" s="0">
+        <v>366.22500000000014</v>
+      </c>
+      <c r="Y177" s="0">
+        <v>775.63654182999926</v>
+      </c>
+      <c r="Z177" s="0">
+        <v>0.010324959983939088</v>
       </c>
     </row>
     <row r="178">
@@ -9244,7 +14059,34 @@
         <v>0.0579296875</v>
       </c>
       <c r="Q178" s="0">
+        <v>0.032851562500000001</v>
+      </c>
+      <c r="R178" s="0">
+        <v>0.056523437500000002</v>
+      </c>
+      <c r="S178" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T178" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U178" s="0">
+        <v>0.017148437500000002</v>
+      </c>
+      <c r="V178" s="0">
+        <v>0.025078125</v>
+      </c>
+      <c r="W178" s="0">
+        <v>0.28686600000000007</v>
+      </c>
+      <c r="X178" s="0">
+        <v>402.8449999999998</v>
+      </c>
+      <c r="Y178" s="0">
+        <v>763.94262415399999</v>
+      </c>
+      <c r="Z178" s="0">
+        <v>0.018054627764152405</v>
       </c>
     </row>
     <row r="179">
@@ -9295,7 +14137,34 @@
         <v>0.036601562500000004</v>
       </c>
       <c r="Q179" s="0">
+        <v>0.037187499999999998</v>
+      </c>
+      <c r="R179" s="0">
+        <v>0.060859375</v>
+      </c>
+      <c r="S179" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T179" s="0">
+        <v>0.010546875000000004</v>
+      </c>
+      <c r="U179" s="0">
+        <v>0.0146484375</v>
+      </c>
+      <c r="V179" s="0">
+        <v>-0.00058593749999999445</v>
+      </c>
+      <c r="W179" s="0">
+        <v>0.27557399999999999</v>
+      </c>
+      <c r="X179" s="0">
+        <v>384.55400000000009</v>
+      </c>
+      <c r="Y179" s="0">
+        <v>752.43618235199983</v>
+      </c>
+      <c r="Z179" s="0">
+        <v>0.1892171906001259</v>
       </c>
     </row>
     <row r="180">
@@ -9346,7 +14215,34 @@
         <v>0.046484375000000001</v>
       </c>
       <c r="Q180" s="0">
+        <v>0.021523437499999999</v>
+      </c>
+      <c r="R180" s="0">
+        <v>0.045195312500000001</v>
+      </c>
+      <c r="S180" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T180" s="0">
+        <v>0.010546875000000004</v>
+      </c>
+      <c r="U180" s="0">
+        <v>0.020703125000000003</v>
+      </c>
+      <c r="V180" s="0">
+        <v>0.024960937500000002</v>
+      </c>
+      <c r="W180" s="0">
+        <v>0.28137200000000001</v>
+      </c>
+      <c r="X180" s="0">
+        <v>347.94000000000051</v>
+      </c>
+      <c r="Y180" s="0">
+        <v>713.31033940700036</v>
+      </c>
+      <c r="Z180" s="0">
+        <v>0.024100934177414428</v>
       </c>
     </row>
     <row r="181">
@@ -9397,7 +14293,34 @@
         <v>0.062851562499999999</v>
       </c>
       <c r="Q181" s="0">
+        <v>0.037812499999999999</v>
+      </c>
+      <c r="R181" s="0">
+        <v>0.061445312500000002</v>
+      </c>
+      <c r="S181" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T181" s="0">
+        <v>0.0110546875</v>
+      </c>
+      <c r="U181" s="0">
+        <v>0.018164062500000001</v>
+      </c>
+      <c r="V181" s="0">
+        <v>0.025039062500000001</v>
+      </c>
+      <c r="W181" s="0">
+        <v>0.27709900000000004</v>
+      </c>
+      <c r="X181" s="0">
+        <v>384.54799999999977</v>
+      </c>
+      <c r="Y181" s="0">
+        <v>773.46342153000023</v>
+      </c>
+      <c r="Z181" s="0">
+        <v>0.015779551548791664</v>
       </c>
     </row>
     <row r="182">
@@ -9448,7 +14371,34 @@
         <v>0.061406250000000002</v>
       </c>
       <c r="Q182" s="0">
+        <v>0.0364453125</v>
+      </c>
+      <c r="R182" s="0">
+        <v>0.060117187500000002</v>
+      </c>
+      <c r="S182" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T182" s="0">
+        <v>0.010039062500000001</v>
+      </c>
+      <c r="U182" s="0">
+        <v>0.015664062499999999</v>
+      </c>
+      <c r="V182" s="0">
+        <v>0.024960937500000002</v>
+      </c>
+      <c r="W182" s="0">
+        <v>0.28533900000000001</v>
+      </c>
+      <c r="X182" s="0">
+        <v>366.24699999999984</v>
+      </c>
+      <c r="Y182" s="0">
+        <v>746.74724689599952</v>
+      </c>
+      <c r="Z182" s="0">
+        <v>0.019866601694951518</v>
       </c>
     </row>
     <row r="183">
@@ -9499,7 +14449,34 @@
         <v>0.037304687500000003</v>
       </c>
       <c r="Q183" s="0">
+        <v>0.037890625000000004</v>
+      </c>
+      <c r="R183" s="0">
+        <v>0.061562499999999999</v>
+      </c>
+      <c r="S183" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T183" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U183" s="0">
+        <v>0.014140624999999997</v>
+      </c>
+      <c r="V183" s="0">
+        <v>-0.00058593750000000139</v>
+      </c>
+      <c r="W183" s="0">
+        <v>0.29418900000000003</v>
+      </c>
+      <c r="X183" s="0">
+        <v>384.54700000000003</v>
+      </c>
+      <c r="Y183" s="0">
+        <v>741.48533350500065</v>
+      </c>
+      <c r="Z183" s="0">
+        <v>0.018387625657579645</v>
       </c>
     </row>
     <row r="184">
@@ -9550,7 +14527,34 @@
         <v>0.059414062500000003</v>
       </c>
       <c r="Q184" s="0">
+        <v>0.034414062500000002</v>
+      </c>
+      <c r="R184" s="0">
+        <v>0.058046874999999998</v>
+      </c>
+      <c r="S184" s="0">
         <v>0.023632812499999999</v>
+      </c>
+      <c r="T184" s="0">
+        <v>0.011562499999999996</v>
+      </c>
+      <c r="U184" s="0">
+        <v>0.015156249999999996</v>
+      </c>
+      <c r="V184" s="0">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="W184" s="0">
+        <v>0.27130199999999999</v>
+      </c>
+      <c r="X184" s="0">
+        <v>384.56000000000085</v>
+      </c>
+      <c r="Y184" s="0">
+        <v>825.98197992600035</v>
+      </c>
+      <c r="Z184" s="0">
+        <v>0.068336906159658511</v>
       </c>
     </row>
     <row r="185">
@@ -9601,7 +14605,34 @@
         <v>0.056757812500000004</v>
       </c>
       <c r="Q185" s="0">
+        <v>0.031718750000000004</v>
+      </c>
+      <c r="R185" s="0">
+        <v>0.055390624999999999</v>
+      </c>
+      <c r="S185" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T185" s="0">
+        <v>0.010546874999999997</v>
+      </c>
+      <c r="U185" s="0">
+        <v>0.014140624999999997</v>
+      </c>
+      <c r="V185" s="0">
+        <v>0.025039062500000001</v>
+      </c>
+      <c r="W185" s="0">
+        <v>0.26947000000000004</v>
+      </c>
+      <c r="X185" s="0">
+        <v>366.2510000000002</v>
+      </c>
+      <c r="Y185" s="0">
+        <v>737.15682072499976</v>
+      </c>
+      <c r="Z185" s="0">
+        <v>0.15366222706977226</v>
       </c>
     </row>
     <row r="186">
@@ -9652,7 +14683,34 @@
         <v>0.049140625</v>
       </c>
       <c r="Q186" s="0">
+        <v>0.0239453125</v>
+      </c>
+      <c r="R186" s="0">
+        <v>0.047617187499999998</v>
+      </c>
+      <c r="S186" s="0">
         <v>0.023671875000000002</v>
+      </c>
+      <c r="T186" s="0">
+        <v>0.0115625</v>
+      </c>
+      <c r="U186" s="0">
+        <v>0.013125000000000001</v>
+      </c>
+      <c r="V186" s="0">
+        <v>0.025195312500000001</v>
+      </c>
+      <c r="W186" s="0">
+        <v>0.28137199999999996</v>
+      </c>
+      <c r="X186" s="0">
+        <v>439.47600000000011</v>
+      </c>
+      <c r="Y186" s="0">
+        <v>741.27905261999967</v>
+      </c>
+      <c r="Z186" s="0">
+        <v>0.0070575441362324279</v>
       </c>
     </row>
   </sheetData>

--- a/features.xlsx
+++ b/features.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="419" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1071" uniqueCount="42">
   <si>
     <t>TestNumber</t>
   </si>
@@ -128,6 +128,18 @@
   <si>
     <t>dRMax</t>
   </si>
+  <si>
+    <t>Vrms</t>
+  </si>
+  <si>
+    <t>Irms</t>
+  </si>
+  <si>
+    <t>Prms</t>
+  </si>
+  <si>
+    <t>Carga_C_</t>
+  </si>
 </sst>
 </file>
 
@@ -172,7 +184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z186"/>
+  <dimension ref="A1:AD186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="true"/>
@@ -197,10 +209,14 @@
     <col min="20" max="20" width="13.21875" customWidth="true"/>
     <col min="21" max="21" width="12.6640625" customWidth="true"/>
     <col min="22" max="22" width="13.21875" customWidth="true"/>
-    <col min="23" max="23" width="8.5546875" customWidth="true"/>
-    <col min="24" max="24" width="7.5546875" customWidth="true"/>
+    <col min="23" max="23" width="9.5546875" customWidth="true"/>
+    <col min="24" max="24" width="10.5546875" customWidth="true"/>
     <col min="25" max="25" width="11.5546875" customWidth="true"/>
-    <col min="26" max="26" width="15.5546875" customWidth="true"/>
+    <col min="26" max="26" width="11.5546875" customWidth="true"/>
+    <col min="27" max="27" width="12.5546875" customWidth="true"/>
+    <col min="28" max="28" width="11.5546875" customWidth="true"/>
+    <col min="29" max="29" width="11.5546875" customWidth="true"/>
+    <col min="30" max="30" width="11.5546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -282,6 +298,18 @@
       <c r="Z1" s="0" t="s">
         <v>37</v>
       </c>
+      <c r="AA1" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB1" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC1" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD1" s="0" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
@@ -349,16 +377,28 @@
         <v>0.025898437500000003</v>
       </c>
       <c r="W2" s="0">
-        <v>0.28350799999999998</v>
+        <v>7257.804799999999</v>
       </c>
       <c r="X2" s="0">
-        <v>402.84700000000021</v>
+        <v>10312883.200000005</v>
       </c>
       <c r="Y2" s="0">
-        <v>770.13897130599935</v>
+        <v>19715557.665433582</v>
       </c>
       <c r="Z2" s="0">
-        <v>0.012138380782745397</v>
+        <v>310.74254803828217</v>
+      </c>
+      <c r="AA2" s="0">
+        <v>0.35725222998860856</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>1557.8512371981119</v>
+      </c>
+      <c r="AC2" s="0">
+        <v>1318.7148929194373</v>
+      </c>
+      <c r="AD2" s="0">
+        <v>70.919735585937474</v>
       </c>
     </row>
     <row r="3">
@@ -427,16 +467,28 @@
         <v>0.025039062500000007</v>
       </c>
       <c r="W3" s="0">
-        <v>0.28839100000000001</v>
+        <v>7382.8096000000005</v>
       </c>
       <c r="X3" s="0">
-        <v>347.94000000000005</v>
+        <v>8907264.0000000019</v>
       </c>
       <c r="Y3" s="0">
-        <v>772.40805613400016</v>
+        <v>19773646.237030406</v>
       </c>
       <c r="Z3" s="0">
-        <v>0.016199931059953036</v>
+        <v>414.71823513479774</v>
+      </c>
+      <c r="AA3" s="0">
+        <v>0.36372760722628583</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>1558.7565719199538</v>
+      </c>
+      <c r="AC3" s="0">
+        <v>1334.5131770103467</v>
+      </c>
+      <c r="AD3" s="0">
+        <v>70.54747281249999</v>
       </c>
     </row>
     <row r="4">
@@ -505,16 +557,28 @@
         <v>-0.00058593750000000139</v>
       </c>
       <c r="W4" s="0">
-        <v>0.28228799999999998</v>
+        <v>7226.572799999999</v>
       </c>
       <c r="X4" s="0">
-        <v>384.54500000000007</v>
+        <v>9844352.0000000019</v>
       </c>
       <c r="Y4" s="0">
-        <v>792.40563442600023</v>
+        <v>20285584.241305605</v>
       </c>
       <c r="Z4" s="0">
-        <v>0.061380492205549968</v>
+        <v>1571.3406004620792</v>
+      </c>
+      <c r="AA4" s="0">
+        <v>0.36104104985244651</v>
+      </c>
+      <c r="AB4" s="0">
+        <v>1555.7082945987702</v>
+      </c>
+      <c r="AC4" s="0">
+        <v>1326.7154895397637</v>
+      </c>
+      <c r="AD4" s="0">
+        <v>69.480442851562515</v>
       </c>
     </row>
     <row r="5">
@@ -583,16 +647,28 @@
         <v>-0.0001171874999999975</v>
       </c>
       <c r="W5" s="0">
-        <v>0.28900100000000001</v>
+        <v>7398.4256000000005</v>
       </c>
       <c r="X5" s="0">
-        <v>384.52800000000002</v>
+        <v>9843916.8000000007</v>
       </c>
       <c r="Y5" s="0">
-        <v>757.87909787499939</v>
+        <v>19401704.905599985</v>
       </c>
       <c r="Z5" s="0">
-        <v>0.016419739620687341</v>
+        <v>420.34533428959594</v>
+      </c>
+      <c r="AA5" s="0">
+        <v>0.3603673457679244</v>
+      </c>
+      <c r="AB5" s="0">
+        <v>1562.5301535232302</v>
+      </c>
+      <c r="AC5" s="0">
+        <v>1329.6565142644761</v>
+      </c>
+      <c r="AD5" s="0">
+        <v>71.459795312500034</v>
       </c>
     </row>
     <row r="6">
@@ -661,16 +737,28 @@
         <v>0.025078125</v>
       </c>
       <c r="W6" s="0">
-        <v>0.26946999999999999</v>
+        <v>6898.4319999999998</v>
       </c>
       <c r="X6" s="0">
-        <v>366.22899999999981</v>
+        <v>9375462.3999999948</v>
       </c>
       <c r="Y6" s="0">
-        <v>746.46685336799965</v>
+        <v>19109551.446220789</v>
       </c>
       <c r="Z6" s="0">
-        <v>0.018483989905611911</v>
+        <v>473.19014158366491</v>
+      </c>
+      <c r="AA6" s="0">
+        <v>0.36006600024854629</v>
+      </c>
+      <c r="AB6" s="0">
+        <v>1560.7310397834256</v>
+      </c>
+      <c r="AC6" s="0">
+        <v>1324.9816697180659</v>
+      </c>
+      <c r="AD6" s="0">
+        <v>70.47220257812495</v>
       </c>
     </row>
     <row r="7">
@@ -739,16 +827,28 @@
         <v>0.025507812499999998</v>
       </c>
       <c r="W7" s="0">
-        <v>0.28961099999999995</v>
+        <v>7414.0415999999987</v>
       </c>
       <c r="X7" s="0">
-        <v>402.86900000000014</v>
+        <v>10313446.400000004</v>
       </c>
       <c r="Y7" s="0">
-        <v>763.99617609100005</v>
+        <v>19558302.107929602</v>
       </c>
       <c r="Z7" s="0">
-        <v>0.0096110953460419798</v>
+        <v>246.04404085867469</v>
+      </c>
+      <c r="AA7" s="0">
+        <v>0.36486076530761508</v>
+      </c>
+      <c r="AB7" s="0">
+        <v>1565.4166609075573</v>
+      </c>
+      <c r="AC7" s="0">
+        <v>1342.7858295700034</v>
+      </c>
+      <c r="AD7" s="0">
+        <v>70.299244960937529</v>
       </c>
     </row>
     <row r="8">
@@ -817,16 +917,28 @@
         <v>0.025507812500000001</v>
       </c>
       <c r="W8" s="0">
-        <v>0.28686500000000004</v>
+        <v>7343.7440000000006</v>
       </c>
       <c r="X8" s="0">
-        <v>384.54700000000003</v>
+        <v>9844403.2000000011</v>
       </c>
       <c r="Y8" s="0">
-        <v>749.72822682599963</v>
+        <v>19193042.60674559</v>
       </c>
       <c r="Z8" s="0">
-        <v>0.03761440230284975</v>
+        <v>962.9286989529536</v>
+      </c>
+      <c r="AA8" s="0">
+        <v>0.36028371084553573</v>
+      </c>
+      <c r="AB8" s="0">
+        <v>1551.5451339546951</v>
+      </c>
+      <c r="AC8" s="0">
+        <v>1321.3680897253689</v>
+      </c>
+      <c r="AD8" s="0">
+        <v>69.595155117187502</v>
       </c>
     </row>
     <row r="9">
@@ -895,16 +1007,28 @@
         <v>0.025468749999999998</v>
       </c>
       <c r="W9" s="0">
-        <v>0.27191100000000001</v>
+        <v>6960.9216000000006</v>
       </c>
       <c r="X9" s="0">
-        <v>366.23500000000013</v>
+        <v>9375616.0000000037</v>
       </c>
       <c r="Y9" s="0">
-        <v>777.45598713800018</v>
+        <v>19902873.270732805</v>
       </c>
       <c r="Z9" s="0">
-        <v>0.0097580344680125355</v>
+        <v>249.8056823811209</v>
+      </c>
+      <c r="AA9" s="0">
+        <v>0.35880605556063949</v>
+      </c>
+      <c r="AB9" s="0">
+        <v>1550.9646202839392</v>
+      </c>
+      <c r="AC9" s="0">
+        <v>1314.1310032091012</v>
+      </c>
+      <c r="AD9" s="0">
+        <v>69.60409710937499</v>
       </c>
     </row>
     <row r="10">
@@ -973,16 +1097,28 @@
         <v>0.025195312500000004</v>
       </c>
       <c r="W10" s="0">
-        <v>0.28320299999999998</v>
+        <v>7249.996799999999</v>
       </c>
       <c r="X10" s="0">
-        <v>366.23500000000013</v>
+        <v>9375616.0000000037</v>
       </c>
       <c r="Y10" s="0">
-        <v>781.71107254800063</v>
+        <v>20011803.457228817</v>
       </c>
       <c r="Z10" s="0">
-        <v>0.012291018334008953</v>
+        <v>314.65006935062922</v>
+      </c>
+      <c r="AA10" s="0">
+        <v>0.36359121281991341</v>
+      </c>
+      <c r="AB10" s="0">
+        <v>1560.7447564765585</v>
+      </c>
+      <c r="AC10" s="0">
+        <v>1330.7100542091591</v>
+      </c>
+      <c r="AD10" s="0">
+        <v>69.848916367187513</v>
       </c>
     </row>
     <row r="11">
@@ -1051,16 +1187,28 @@
         <v>0.025273437500000002</v>
       </c>
       <c r="W11" s="0">
-        <v>0.28350799999999998</v>
+        <v>7257.804799999999</v>
       </c>
       <c r="X11" s="0">
-        <v>366.22200000000009</v>
+        <v>9375283.200000003</v>
       </c>
       <c r="Y11" s="0">
-        <v>754.26571249300014</v>
+        <v>19309202.239820804</v>
       </c>
       <c r="Z11" s="0">
-        <v>0.010593886982163493</v>
+        <v>271.20350674338545</v>
+      </c>
+      <c r="AA11" s="0">
+        <v>0.36381019159343958</v>
+      </c>
+      <c r="AB11" s="0">
+        <v>1559.6056526832083</v>
+      </c>
+      <c r="AC11" s="0">
+        <v>1336.6572348083855</v>
+      </c>
+      <c r="AD11" s="0">
+        <v>69.677589179687473</v>
       </c>
     </row>
     <row r="12">
@@ -1129,16 +1277,28 @@
         <v>0.025039062500000001</v>
       </c>
       <c r="W12" s="0">
-        <v>0.26824899999999996</v>
+        <v>6867.174399999999</v>
       </c>
       <c r="X12" s="0">
-        <v>384.53300000000013</v>
+        <v>9844044.8000000026</v>
       </c>
       <c r="Y12" s="0">
-        <v>781.6211288720001</v>
+        <v>20009500.899123203</v>
       </c>
       <c r="Z12" s="0">
-        <v>0.017043374180892055</v>
+        <v>436.3103790308366</v>
+      </c>
+      <c r="AA12" s="0">
+        <v>0.35955924874205064</v>
+      </c>
+      <c r="AB12" s="0">
+        <v>1554.6954634081135</v>
+      </c>
+      <c r="AC12" s="0">
+        <v>1323.9785539760296</v>
+      </c>
+      <c r="AD12" s="0">
+        <v>69.519236132812452</v>
       </c>
     </row>
     <row r="13">
@@ -1207,16 +1367,28 @@
         <v>0.024960937500000002</v>
       </c>
       <c r="W13" s="0">
-        <v>0.27282699999999999</v>
+        <v>6984.3711999999996</v>
       </c>
       <c r="X13" s="0">
-        <v>402.84299999999996</v>
+        <v>10312780.799999999</v>
       </c>
       <c r="Y13" s="0">
-        <v>729.24586604700016</v>
+        <v>18668694.170803204</v>
       </c>
       <c r="Z13" s="0">
-        <v>0.012332799070084222</v>
+        <v>315.71965619415607</v>
+      </c>
+      <c r="AA13" s="0">
+        <v>0.36118706288600955</v>
+      </c>
+      <c r="AB13" s="0">
+        <v>1553.0723900983962</v>
+      </c>
+      <c r="AC13" s="0">
+        <v>1326.845356249235</v>
+      </c>
+      <c r="AD13" s="0">
+        <v>68.864999531250049</v>
       </c>
     </row>
     <row r="14">
@@ -1285,16 +1457,28 @@
         <v>-0.00062499999999999362</v>
       </c>
       <c r="W14" s="0">
-        <v>0.28747599999999995</v>
+        <v>7359.3855999999987</v>
       </c>
       <c r="X14" s="0">
-        <v>366.23599999999988</v>
+        <v>9375641.5999999959</v>
       </c>
       <c r="Y14" s="0">
-        <v>716.50680113599992</v>
+        <v>18342574.109081596</v>
       </c>
       <c r="Z14" s="0">
-        <v>0.033380564733293296</v>
+        <v>854.54245717230833</v>
+      </c>
+      <c r="AA14" s="0">
+        <v>0.36290556202256508</v>
+      </c>
+      <c r="AB14" s="0">
+        <v>1543.3008378052953</v>
+      </c>
+      <c r="AC14" s="0">
+        <v>1318.8740859053628</v>
+      </c>
+      <c r="AD14" s="0">
+        <v>67.611269218749982</v>
       </c>
     </row>
     <row r="15">
@@ -1363,16 +1547,28 @@
         <v>0.024960937499999999</v>
       </c>
       <c r="W15" s="0">
-        <v>0.28472900000000001</v>
+        <v>7289.0623999999998</v>
       </c>
       <c r="X15" s="0">
-        <v>384.53199999999993</v>
+        <v>9844019.1999999974</v>
       </c>
       <c r="Y15" s="0">
-        <v>781.65203279599973</v>
+        <v>20010292.039577592</v>
       </c>
       <c r="Z15" s="0">
-        <v>0.031412170597581113</v>
+        <v>804.15156729807643</v>
+      </c>
+      <c r="AA15" s="0">
+        <v>0.35907958340983359</v>
+      </c>
+      <c r="AB15" s="0">
+        <v>1551.180581424908</v>
+      </c>
+      <c r="AC15" s="0">
+        <v>1318.4046850302427</v>
+      </c>
+      <c r="AD15" s="0">
+        <v>69.927900156249976</v>
       </c>
     </row>
     <row r="16">
@@ -1441,16 +1637,28 @@
         <v>0.025117187500000006</v>
       </c>
       <c r="W16" s="0">
-        <v>0.28533999999999998</v>
+        <v>7304.7039999999997</v>
       </c>
       <c r="X16" s="0">
-        <v>384.54600000000028</v>
+        <v>9844377.6000000071</v>
       </c>
       <c r="Y16" s="0">
-        <v>755.4165667240004</v>
+        <v>19338664.108134411</v>
       </c>
       <c r="Z16" s="0">
-        <v>0.040713163392491918</v>
+        <v>1042.2569828477931</v>
+      </c>
+      <c r="AA16" s="0">
+        <v>0.36055843966410139</v>
+      </c>
+      <c r="AB16" s="0">
+        <v>1565.2946723219152</v>
+      </c>
+      <c r="AC16" s="0">
+        <v>1334.4262067820314</v>
+      </c>
+      <c r="AD16" s="0">
+        <v>70.685554296875011</v>
       </c>
     </row>
     <row r="17">
@@ -1519,16 +1727,28 @@
         <v>0.025000000000000005</v>
       </c>
       <c r="W17" s="0">
-        <v>0.28289800000000004</v>
+        <v>7242.1888000000008</v>
       </c>
       <c r="X17" s="0">
-        <v>384.54700000000003</v>
+        <v>9844403.2000000011</v>
       </c>
       <c r="Y17" s="0">
-        <v>765.46309170899985</v>
+        <v>19595855.147750396</v>
       </c>
       <c r="Z17" s="0">
-        <v>0.28104861919430668</v>
+        <v>7194.844651374251</v>
+      </c>
+      <c r="AA17" s="0">
+        <v>0.35114812085380898</v>
+      </c>
+      <c r="AB17" s="0">
+        <v>1547.0341072780075</v>
+      </c>
+      <c r="AC17" s="0">
+        <v>1298.6317510630665</v>
+      </c>
+      <c r="AD17" s="0">
+        <v>69.407966953124998</v>
       </c>
     </row>
     <row r="18">
@@ -1597,16 +1817,28 @@
         <v>0.024960937500000002</v>
       </c>
       <c r="W18" s="0">
-        <v>0.26092499999999996</v>
+        <v>6679.6799999999985</v>
       </c>
       <c r="X18" s="0">
-        <v>421.14899999999994</v>
+        <v>10781414.399999999</v>
       </c>
       <c r="Y18" s="0">
-        <v>716.85607173200015</v>
+        <v>18351515.436339203</v>
       </c>
       <c r="Z18" s="0">
-        <v>0.015681650531139624</v>
+        <v>401.45025359717437</v>
+      </c>
+      <c r="AA18" s="0">
+        <v>0.34765500779296121</v>
+      </c>
+      <c r="AB18" s="0">
+        <v>1551.7201613752595</v>
+      </c>
+      <c r="AC18" s="0">
+        <v>1293.7070836027963</v>
+      </c>
+      <c r="AD18" s="0">
+        <v>69.973698906250021</v>
       </c>
     </row>
     <row r="19">
@@ -1675,16 +1907,28 @@
         <v>0.025039062500000001</v>
       </c>
       <c r="W19" s="0">
-        <v>0.26184000000000007</v>
+        <v>6703.1040000000021</v>
       </c>
       <c r="X19" s="0">
-        <v>439.49199999999973</v>
+        <v>11250995.199999994</v>
       </c>
       <c r="Y19" s="0">
-        <v>752.06999235600051</v>
+        <v>19252991.804313611</v>
       </c>
       <c r="Z19" s="0">
-        <v>0.048615084512761607</v>
+        <v>1244.546163526697</v>
+      </c>
+      <c r="AA19" s="0">
+        <v>0.35134591990780462</v>
+      </c>
+      <c r="AB19" s="0">
+        <v>1560.8594588412136</v>
+      </c>
+      <c r="AC19" s="0">
+        <v>1309.007348492675</v>
+      </c>
+      <c r="AD19" s="0">
+        <v>70.30168535156254</v>
       </c>
     </row>
     <row r="20">
@@ -1753,16 +1997,28 @@
         <v>-0.00058593750000000139</v>
       </c>
       <c r="W20" s="0">
-        <v>0.26916500000000004</v>
+        <v>6890.6240000000007</v>
       </c>
       <c r="X20" s="0">
-        <v>366.24999999999955</v>
+        <v>9375999.9999999888</v>
       </c>
       <c r="Y20" s="0">
-        <v>762.42194301300015</v>
+        <v>19518001.741132803</v>
       </c>
       <c r="Z20" s="0">
-        <v>0.027094176268970142</v>
+        <v>693.61091248563559</v>
+      </c>
+      <c r="AA20" s="0">
+        <v>0.35190271919304511</v>
+      </c>
+      <c r="AB20" s="0">
+        <v>1543.650256436872</v>
+      </c>
+      <c r="AC20" s="0">
+        <v>1299.0547713333228</v>
+      </c>
+      <c r="AD20" s="0">
+        <v>68.796595507812512</v>
       </c>
     </row>
     <row r="21">
@@ -1831,16 +2087,28 @@
         <v>0.025078124999999996</v>
       </c>
       <c r="W21" s="0">
-        <v>0.25970400000000005</v>
+        <v>6648.4224000000013</v>
       </c>
       <c r="X21" s="0">
-        <v>347.9399999999996</v>
+        <v>8907263.9999999888</v>
       </c>
       <c r="Y21" s="0">
-        <v>717.63404893300003</v>
+        <v>18371431.6526848</v>
       </c>
       <c r="Z21" s="0">
-        <v>0.024278985037541671</v>
+        <v>621.54201696106679</v>
+      </c>
+      <c r="AA21" s="0">
+        <v>0.34788504511939417</v>
+      </c>
+      <c r="AB21" s="0">
+        <v>1557.1399550759122</v>
+      </c>
+      <c r="AC21" s="0">
+        <v>1301.1706384593199</v>
+      </c>
+      <c r="AD21" s="0">
+        <v>70.329375039062541</v>
       </c>
     </row>
     <row r="22">
@@ -1909,16 +2177,28 @@
         <v>0.025117187499999999</v>
       </c>
       <c r="W22" s="0">
-        <v>0.26122999999999996</v>
+        <v>6687.4879999999985</v>
       </c>
       <c r="X22" s="0">
-        <v>366.22700000000009</v>
+        <v>9375411.200000003</v>
       </c>
       <c r="Y22" s="0">
-        <v>746.41148292000025</v>
+        <v>19108133.962752007</v>
       </c>
       <c r="Z22" s="0">
-        <v>0.0082443675337928977</v>
+        <v>211.05580886509819</v>
+      </c>
+      <c r="AA22" s="0">
+        <v>0.34613405679789944</v>
+      </c>
+      <c r="AB22" s="0">
+        <v>1548.5686534574504</v>
+      </c>
+      <c r="AC22" s="0">
+        <v>1288.3115283580619</v>
+      </c>
+      <c r="AD22" s="0">
+        <v>68.92243617187502</v>
       </c>
     </row>
     <row r="23">
@@ -1987,16 +2267,28 @@
         <v>0.025156249999999998</v>
       </c>
       <c r="W23" s="0">
-        <v>0.26336599999999999</v>
+        <v>6742.1695999999993</v>
       </c>
       <c r="X23" s="0">
-        <v>384.54599999999982</v>
+        <v>9844377.5999999959</v>
       </c>
       <c r="Y23" s="0">
-        <v>762.07675161999987</v>
+        <v>19509164.841471996</v>
       </c>
       <c r="Z23" s="0">
-        <v>0.013624533568407215</v>
+        <v>348.78805935122472</v>
+      </c>
+      <c r="AA23" s="0">
+        <v>0.34973413996789643</v>
+      </c>
+      <c r="AB23" s="0">
+        <v>1555.2606044964989</v>
+      </c>
+      <c r="AC23" s="0">
+        <v>1298.5607705578605</v>
+      </c>
+      <c r="AD23" s="0">
+        <v>70.454876015625018</v>
       </c>
     </row>
     <row r="24">
@@ -2065,16 +2357,28 @@
         <v>0.024960937500000002</v>
       </c>
       <c r="W24" s="0">
-        <v>0.26489299999999999</v>
+        <v>6781.2608</v>
       </c>
       <c r="X24" s="0">
-        <v>366.22500000000014</v>
+        <v>9375360.0000000037</v>
       </c>
       <c r="Y24" s="0">
-        <v>745.99390835400027</v>
+        <v>19097444.053862408</v>
       </c>
       <c r="Z24" s="0">
-        <v>0.02138741506694735</v>
+        <v>547.51782571385218</v>
+      </c>
+      <c r="AA24" s="0">
+        <v>0.35242786918039043</v>
+      </c>
+      <c r="AB24" s="0">
+        <v>1548.7082777941757</v>
+      </c>
+      <c r="AC24" s="0">
+        <v>1301.8387673847431</v>
+      </c>
+      <c r="AD24" s="0">
+        <v>69.677292851562541</v>
       </c>
     </row>
     <row r="25">
@@ -2143,16 +2447,28 @@
         <v>0.024960937500000002</v>
       </c>
       <c r="W25" s="0">
-        <v>0.25848400000000005</v>
+        <v>6617.1904000000013</v>
       </c>
       <c r="X25" s="0">
-        <v>402.85500000000002</v>
+        <v>10313088</v>
       </c>
       <c r="Y25" s="0">
-        <v>756.56952619599952</v>
+        <v>19368179.870617587</v>
       </c>
       <c r="Z25" s="0">
-        <v>0.012610403831727962</v>
+        <v>322.8263380922358</v>
+      </c>
+      <c r="AA25" s="0">
+        <v>0.34651160272701137</v>
+      </c>
+      <c r="AB25" s="0">
+        <v>1545.2075570026739</v>
+      </c>
+      <c r="AC25" s="0">
+        <v>1284.4532847949554</v>
+      </c>
+      <c r="AD25" s="0">
+        <v>69.284013828124998</v>
       </c>
     </row>
     <row r="26">
@@ -2221,16 +2537,28 @@
         <v>-0.00062500000000000056</v>
       </c>
       <c r="W26" s="0">
-        <v>0.25940000000000002</v>
+        <v>6640.6400000000003</v>
       </c>
       <c r="X26" s="0">
-        <v>402.85800000000017</v>
+        <v>10313164.800000004</v>
       </c>
       <c r="Y26" s="0">
-        <v>746.36185411299994</v>
+        <v>19106863.465292796</v>
       </c>
       <c r="Z26" s="0">
-        <v>0.01357836961871055</v>
+        <v>347.60626223899004</v>
+      </c>
+      <c r="AA26" s="0">
+        <v>0.34794520476924451</v>
+      </c>
+      <c r="AB26" s="0">
+        <v>1552.6363224126096</v>
+      </c>
+      <c r="AC26" s="0">
+        <v>1297.0032734766207</v>
+      </c>
+      <c r="AD26" s="0">
+        <v>68.993690390625005</v>
       </c>
     </row>
     <row r="27">
@@ -2299,16 +2627,28 @@
         <v>0.025000000000000001</v>
       </c>
       <c r="W27" s="0">
-        <v>0.26519800000000004</v>
+        <v>6789.0688000000009</v>
       </c>
       <c r="X27" s="0">
-        <v>421.16699999999992</v>
+        <v>10781875.199999997</v>
       </c>
       <c r="Y27" s="0">
-        <v>737.47307665599919</v>
+        <v>18879310.762393579</v>
       </c>
       <c r="Z27" s="0">
-        <v>0.064223986029312702</v>
+        <v>1644.134042350405</v>
+      </c>
+      <c r="AA27" s="0">
+        <v>0.350391779998521</v>
+      </c>
+      <c r="AB27" s="0">
+        <v>1551.0000828669097</v>
+      </c>
+      <c r="AC27" s="0">
+        <v>1299.6767586532144</v>
+      </c>
+      <c r="AD27" s="0">
+        <v>70.176530507812515</v>
       </c>
     </row>
     <row r="28">
@@ -2377,16 +2717,28 @@
         <v>0.025039062500000001</v>
       </c>
       <c r="W28" s="0">
-        <v>0.25970399999999999</v>
+        <v>6648.4223999999995</v>
       </c>
       <c r="X28" s="0">
-        <v>347.92899999999963</v>
+        <v>8906982.3999999911</v>
       </c>
       <c r="Y28" s="0">
-        <v>743.62532328400039</v>
+        <v>19036808.276070409</v>
       </c>
       <c r="Z28" s="0">
-        <v>0.27804046229685558</v>
+        <v>7117.8358347995027</v>
+      </c>
+      <c r="AA28" s="0">
+        <v>0.35210360072554858</v>
+      </c>
+      <c r="AB28" s="0">
+        <v>1548.3894418770819</v>
+      </c>
+      <c r="AC28" s="0">
+        <v>1302.4788427719684</v>
+      </c>
+      <c r="AD28" s="0">
+        <v>68.556870117187472</v>
       </c>
     </row>
     <row r="29">
@@ -2455,16 +2807,28 @@
         <v>0.025039062500000001</v>
       </c>
       <c r="W29" s="0">
-        <v>0.26123099999999999</v>
+        <v>6687.5135999999993</v>
       </c>
       <c r="X29" s="0">
-        <v>384.54299999999989</v>
+        <v>9844300.799999997</v>
       </c>
       <c r="Y29" s="0">
-        <v>722.37816185599922</v>
+        <v>18492880.94351358</v>
       </c>
       <c r="Z29" s="0">
-        <v>0.015470825954359037</v>
+        <v>396.05314443159131</v>
+      </c>
+      <c r="AA29" s="0">
+        <v>0.34765748914719397</v>
+      </c>
+      <c r="AB29" s="0">
+        <v>1546.7205832139994</v>
+      </c>
+      <c r="AC29" s="0">
+        <v>1291.3153994606091</v>
+      </c>
+      <c r="AD29" s="0">
+        <v>69.922736914062511</v>
       </c>
     </row>
     <row r="30">
@@ -2533,16 +2897,28 @@
         <v>0.025546875000000004</v>
       </c>
       <c r="W30" s="0">
-        <v>0.27862599999999998</v>
+        <v>7132.8255999999992</v>
       </c>
       <c r="X30" s="0">
-        <v>384.54100000000017</v>
+        <v>9844249.6000000034</v>
       </c>
       <c r="Y30" s="0">
-        <v>728.474148530001</v>
+        <v>18648938.202368025</v>
       </c>
       <c r="Z30" s="0">
-        <v>0.016965575763407813</v>
+        <v>434.31873954323999</v>
+      </c>
+      <c r="AA30" s="0">
+        <v>0.34745668483191788</v>
+      </c>
+      <c r="AB30" s="0">
+        <v>1555.3598056314784</v>
+      </c>
+      <c r="AC30" s="0">
+        <v>1286.9749854731963</v>
+      </c>
+      <c r="AD30" s="0">
+        <v>70.667081601562501</v>
       </c>
     </row>
     <row r="31">
@@ -2611,16 +2987,28 @@
         <v>0.025195312499999997</v>
       </c>
       <c r="W31" s="0">
-        <v>0.26458699999999996</v>
+        <v>6773.4271999999992</v>
       </c>
       <c r="X31" s="0">
-        <v>384.54600000000028</v>
+        <v>9844377.6000000071</v>
       </c>
       <c r="Y31" s="0">
-        <v>775.88260679800032</v>
+        <v>19862594.734028809</v>
       </c>
       <c r="Z31" s="0">
-        <v>0.0092834259815561156</v>
+        <v>237.65570512783654</v>
+      </c>
+      <c r="AA31" s="0">
+        <v>0.35202763966728579</v>
+      </c>
+      <c r="AB31" s="0">
+        <v>1555.5535648241439</v>
+      </c>
+      <c r="AC31" s="0">
+        <v>1304.6416470823433</v>
+      </c>
+      <c r="AD31" s="0">
+        <v>69.989908242187497</v>
       </c>
     </row>
     <row r="32">
@@ -2689,16 +3077,28 @@
         <v>0.025351562500000001</v>
       </c>
       <c r="W32" s="0">
-        <v>0.27099600000000001</v>
+        <v>6937.4976000000006</v>
       </c>
       <c r="X32" s="0">
-        <v>384.54400000000032</v>
+        <v>9844326.4000000078</v>
       </c>
       <c r="Y32" s="0">
-        <v>754.71795018300099</v>
+        <v>19320779.524684824</v>
       </c>
       <c r="Z32" s="0">
-        <v>0.0089829724693345908</v>
+        <v>229.96409521496551</v>
+      </c>
+      <c r="AA32" s="0">
+        <v>0.34235180652411518</v>
+      </c>
+      <c r="AB32" s="0">
+        <v>1556.0809903767888</v>
+      </c>
+      <c r="AC32" s="0">
+        <v>1286.6340343383888</v>
+      </c>
+      <c r="AD32" s="0">
+        <v>70.545089179687452</v>
       </c>
     </row>
     <row r="33">
@@ -2767,16 +3167,28 @@
         <v>-0.00062500000000000056</v>
       </c>
       <c r="W33" s="0">
-        <v>0.26031499999999996</v>
+        <v>6664.0639999999985</v>
       </c>
       <c r="X33" s="0">
-        <v>347.93899999999985</v>
+        <v>8907238.3999999966</v>
       </c>
       <c r="Y33" s="0">
-        <v>730.61244253199993</v>
+        <v>18703678.5288192</v>
       </c>
       <c r="Z33" s="0">
-        <v>0.018272505842049064</v>
+        <v>467.77614955645601</v>
+      </c>
+      <c r="AA33" s="0">
+        <v>0.34247442172712506</v>
+      </c>
+      <c r="AB33" s="0">
+        <v>1549.0240947203351</v>
+      </c>
+      <c r="AC33" s="0">
+        <v>1279.9808140301536</v>
+      </c>
+      <c r="AD33" s="0">
+        <v>69.968198710937472</v>
       </c>
     </row>
     <row r="34">
@@ -2845,16 +3257,28 @@
         <v>0.025078124999999993</v>
       </c>
       <c r="W34" s="0">
-        <v>0.26092499999999996</v>
+        <v>6679.6799999999985</v>
       </c>
       <c r="X34" s="0">
-        <v>384.54500000000007</v>
+        <v>9844352.0000000019</v>
       </c>
       <c r="Y34" s="0">
-        <v>732.08106725299967</v>
+        <v>18741275.321676791</v>
       </c>
       <c r="Z34" s="0">
-        <v>0.025541614941425945</v>
+        <v>653.8653425005042</v>
+      </c>
+      <c r="AA34" s="0">
+        <v>0.34063123364325326</v>
+      </c>
+      <c r="AB34" s="0">
+        <v>1547.713553831614</v>
+      </c>
+      <c r="AC34" s="0">
+        <v>1270.4883479562839</v>
+      </c>
+      <c r="AD34" s="0">
+        <v>70.178464453125073</v>
       </c>
     </row>
     <row r="35">
@@ -2923,16 +3347,28 @@
         <v>0.025039062500000001</v>
       </c>
       <c r="W35" s="0">
-        <v>0.26580799999999999</v>
+        <v>6804.6848</v>
       </c>
       <c r="X35" s="0">
-        <v>347.92600000000039</v>
+        <v>8906905.6000000089</v>
       </c>
       <c r="Y35" s="0">
-        <v>731.66969813700007</v>
+        <v>18730744.272307202</v>
       </c>
       <c r="Z35" s="0">
-        <v>0.018984037549254939</v>
+        <v>485.99136126092645</v>
+      </c>
+      <c r="AA35" s="0">
+        <v>0.34246203898202032</v>
+      </c>
+      <c r="AB35" s="0">
+        <v>1558.8041412034145</v>
+      </c>
+      <c r="AC35" s="0">
+        <v>1285.9676343769452</v>
+      </c>
+      <c r="AD35" s="0">
+        <v>71.136778359374986</v>
       </c>
     </row>
     <row r="36">
@@ -3001,16 +3437,28 @@
         <v>-0.00066406249999999972</v>
       </c>
       <c r="W36" s="0">
-        <v>0.25695799999999996</v>
+        <v>6578.1247999999987</v>
       </c>
       <c r="X36" s="0">
-        <v>384.54700000000003</v>
+        <v>9844403.2000000011</v>
       </c>
       <c r="Y36" s="0">
-        <v>772.43099211199933</v>
+        <v>19774233.398067184</v>
       </c>
       <c r="Z36" s="0">
-        <v>0.618327235266242</v>
+        <v>15829.177222815795</v>
+      </c>
+      <c r="AA36" s="0">
+        <v>0.34116809346082588</v>
+      </c>
+      <c r="AB36" s="0">
+        <v>1554.0559519916908</v>
+      </c>
+      <c r="AC36" s="0">
+        <v>1281.2677100557476</v>
+      </c>
+      <c r="AD36" s="0">
+        <v>69.937795468749954</v>
       </c>
     </row>
     <row r="37">
@@ -3079,16 +3527,28 @@
         <v>0.025078125</v>
       </c>
       <c r="W37" s="0">
-        <v>0.25848399999999999</v>
+        <v>6617.1903999999995</v>
       </c>
       <c r="X37" s="0">
-        <v>366.23000000000002</v>
+        <v>9375488</v>
       </c>
       <c r="Y37" s="0">
-        <v>757.78058648200022</v>
+        <v>19399183.013939206</v>
       </c>
       <c r="Z37" s="0">
-        <v>0.008708629074975438</v>
+        <v>222.94090431937121</v>
+      </c>
+      <c r="AA37" s="0">
+        <v>0.3416045660137621</v>
+      </c>
+      <c r="AB37" s="0">
+        <v>1556.2012013234012</v>
+      </c>
+      <c r="AC37" s="0">
+        <v>1281.5652901413205</v>
+      </c>
+      <c r="AD37" s="0">
+        <v>70.57929007812497</v>
       </c>
     </row>
     <row r="38">
@@ -3157,16 +3617,28 @@
         <v>0.025703125</v>
       </c>
       <c r="W38" s="0">
-        <v>0.26031500000000007</v>
+        <v>6664.0640000000021</v>
       </c>
       <c r="X38" s="0">
-        <v>421.16600000000017</v>
+        <v>10781849.600000003</v>
       </c>
       <c r="Y38" s="0">
-        <v>746.00790017899953</v>
+        <v>19097802.244582389</v>
       </c>
       <c r="Z38" s="0">
-        <v>0.036415334461045994</v>
+        <v>932.23256220277744</v>
+      </c>
+      <c r="AA38" s="0">
+        <v>0.34220436224172812</v>
+      </c>
+      <c r="AB38" s="0">
+        <v>1544.780057987919</v>
+      </c>
+      <c r="AC38" s="0">
+        <v>1271.9748295936047</v>
+      </c>
+      <c r="AD38" s="0">
+        <v>68.887528945312482</v>
       </c>
     </row>
     <row r="39">
@@ -3235,16 +3707,28 @@
         <v>0.024921875</v>
       </c>
       <c r="W39" s="0">
-        <v>0.25817899999999994</v>
+        <v>6609.3823999999986</v>
       </c>
       <c r="X39" s="0">
-        <v>402.86199999999963</v>
+        <v>10313267.19999999</v>
       </c>
       <c r="Y39" s="0">
-        <v>829.67610923500024</v>
+        <v>21239708.396416005</v>
       </c>
       <c r="Z39" s="0">
-        <v>0.010492761192709716</v>
+        <v>268.61468653336874</v>
+      </c>
+      <c r="AA39" s="0">
+        <v>0.34517499167869292</v>
+      </c>
+      <c r="AB39" s="0">
+        <v>1546.3771882538185</v>
+      </c>
+      <c r="AC39" s="0">
+        <v>1281.6310378682765</v>
+      </c>
+      <c r="AD39" s="0">
+        <v>68.649566796874993</v>
       </c>
     </row>
     <row r="40">
@@ -3313,16 +3797,28 @@
         <v>-0.00062500000000000056</v>
       </c>
       <c r="W40" s="0">
-        <v>0.26001000000000002</v>
+        <v>6656.2560000000003</v>
       </c>
       <c r="X40" s="0">
-        <v>366.23099999999977</v>
+        <v>9375513.599999994</v>
       </c>
       <c r="Y40" s="0">
-        <v>746.88071933299989</v>
+        <v>19120146.414924797</v>
       </c>
       <c r="Z40" s="0">
-        <v>0.10816085455433164</v>
+        <v>2768.91787659089</v>
+      </c>
+      <c r="AA40" s="0">
+        <v>0.33874069412672719</v>
+      </c>
+      <c r="AB40" s="0">
+        <v>1553.3690964570471</v>
+      </c>
+      <c r="AC40" s="0">
+        <v>1270.4357094370075</v>
+      </c>
+      <c r="AD40" s="0">
+        <v>70.021141914062497</v>
       </c>
     </row>
     <row r="41">
@@ -3391,16 +3887,28 @@
         <v>0.025351562500000001</v>
       </c>
       <c r="W41" s="0">
-        <v>0.26275700000000002</v>
+        <v>6726.5792000000001</v>
       </c>
       <c r="X41" s="0">
-        <v>347.94100000000071</v>
+        <v>8907289.6000000183</v>
       </c>
       <c r="Y41" s="0">
-        <v>737.55778786199971</v>
+        <v>18881479.369267192</v>
       </c>
       <c r="Z41" s="0">
-        <v>0.033467324152458913</v>
+        <v>856.76349830294816</v>
+      </c>
+      <c r="AA41" s="0">
+        <v>0.34034152532683354</v>
+      </c>
+      <c r="AB41" s="0">
+        <v>1562.2906142469033</v>
+      </c>
+      <c r="AC41" s="0">
+        <v>1285.4664297758573</v>
+      </c>
+      <c r="AD41" s="0">
+        <v>71.399879999999996</v>
       </c>
     </row>
     <row r="42">
@@ -3469,16 +3977,28 @@
         <v>-0.00062500000000000056</v>
       </c>
       <c r="W42" s="0">
-        <v>0.25512699999999999</v>
+        <v>6531.2511999999997</v>
       </c>
       <c r="X42" s="0">
-        <v>384.53100000000006</v>
+        <v>9843993.6000000015</v>
       </c>
       <c r="Y42" s="0">
-        <v>734.644000409</v>
+        <v>18806886.4104704</v>
       </c>
       <c r="Z42" s="0">
-        <v>0.012518938745498734</v>
+        <v>320.48483188476757</v>
+      </c>
+      <c r="AA42" s="0">
+        <v>0.34174276496451977</v>
+      </c>
+      <c r="AB42" s="0">
+        <v>1553.8365537673219</v>
+      </c>
+      <c r="AC42" s="0">
+        <v>1281.9517166154778</v>
+      </c>
+      <c r="AD42" s="0">
+        <v>70.099111601562456</v>
       </c>
     </row>
     <row r="43">
@@ -3547,16 +4067,28 @@
         <v>0.025390625</v>
       </c>
       <c r="W43" s="0">
-        <v>0.25787399999999999</v>
+        <v>6601.5743999999995</v>
       </c>
       <c r="X43" s="0">
-        <v>366.25099999999975</v>
+        <v>9376025.599999994</v>
       </c>
       <c r="Y43" s="0">
-        <v>751.28459976000022</v>
+        <v>19232885.753856007</v>
       </c>
       <c r="Z43" s="0">
-        <v>0.011323204219852466</v>
+        <v>289.87402802822311</v>
+      </c>
+      <c r="AA43" s="0">
+        <v>0.34453297555782503</v>
+      </c>
+      <c r="AB43" s="0">
+        <v>1559.7235429869497</v>
+      </c>
+      <c r="AC43" s="0">
+        <v>1292.4889557402996</v>
+      </c>
+      <c r="AD43" s="0">
+        <v>71.099310937500036</v>
       </c>
     </row>
     <row r="44">
@@ -3625,16 +4157,28 @@
         <v>0.024960937500000002</v>
       </c>
       <c r="W44" s="0">
-        <v>0.25665200000000005</v>
+        <v>6570.2912000000015</v>
       </c>
       <c r="X44" s="0">
-        <v>384.52900000000011</v>
+        <v>9843942.4000000022</v>
       </c>
       <c r="Y44" s="0">
-        <v>736.60681184000032</v>
+        <v>18857134.383104008</v>
       </c>
       <c r="Z44" s="0">
-        <v>0.0082890658663892103</v>
+        <v>212.20008617956378</v>
+      </c>
+      <c r="AA44" s="0">
+        <v>0.34063507436107282</v>
+      </c>
+      <c r="AB44" s="0">
+        <v>1552.1692742989389</v>
+      </c>
+      <c r="AC44" s="0">
+        <v>1277.4769374892624</v>
+      </c>
+      <c r="AD44" s="0">
+        <v>69.826015742187465</v>
       </c>
     </row>
     <row r="45">
@@ -3703,16 +4247,28 @@
         <v>-0.00062500000000000056</v>
       </c>
       <c r="W45" s="0">
-        <v>0.26946999999999999</v>
+        <v>6898.4319999999998</v>
       </c>
       <c r="X45" s="0">
-        <v>347.94100000000026</v>
+        <v>8907289.6000000071</v>
       </c>
       <c r="Y45" s="0">
-        <v>712.08404835100009</v>
+        <v>18229351.637785602</v>
       </c>
       <c r="Z45" s="0">
-        <v>0.004750314617670089</v>
+        <v>121.60805421235428</v>
+      </c>
+      <c r="AA45" s="0">
+        <v>0.34080066874654086</v>
+      </c>
+      <c r="AB45" s="0">
+        <v>1539.1405731196805</v>
+      </c>
+      <c r="AC45" s="0">
+        <v>1266.2811381112469</v>
+      </c>
+      <c r="AD45" s="0">
+        <v>67.848493242187502</v>
       </c>
     </row>
     <row r="46">
@@ -3781,16 +4337,28 @@
         <v>0.025039062500000001</v>
       </c>
       <c r="W46" s="0">
-        <v>0.27160699999999999</v>
+        <v>6953.1391999999996</v>
       </c>
       <c r="X46" s="0">
-        <v>366.23399999999992</v>
+        <v>9375590.3999999985</v>
       </c>
       <c r="Y46" s="0">
-        <v>743.47298025200007</v>
+        <v>19032908.294451203</v>
       </c>
       <c r="Z46" s="0">
-        <v>0.011193520107729955</v>
+        <v>286.55411475788685</v>
+      </c>
+      <c r="AA46" s="0">
+        <v>0.34257210328369381</v>
+      </c>
+      <c r="AB46" s="0">
+        <v>1554.0319790636504</v>
+      </c>
+      <c r="AC46" s="0">
+        <v>1281.4845522522144</v>
+      </c>
+      <c r="AD46" s="0">
+        <v>70.384347968749978</v>
       </c>
     </row>
     <row r="47">
@@ -3859,16 +4427,28 @@
         <v>0.025039062499999994</v>
       </c>
       <c r="W47" s="0">
-        <v>0.26672299999999999</v>
+        <v>6828.1088</v>
       </c>
       <c r="X47" s="0">
-        <v>347.92500000000018</v>
+        <v>8906880.0000000037</v>
       </c>
       <c r="Y47" s="0">
-        <v>761.25944484399997</v>
+        <v>19488241.788006399</v>
       </c>
       <c r="Z47" s="0">
-        <v>0.013689159536472213</v>
+        <v>350.44248413368865</v>
+      </c>
+      <c r="AA47" s="0">
+        <v>0.33847169038732694</v>
+      </c>
+      <c r="AB47" s="0">
+        <v>1543.5115781341085</v>
+      </c>
+      <c r="AC47" s="0">
+        <v>1265.7447654036355</v>
+      </c>
+      <c r="AD47" s="0">
+        <v>69.467430820312501</v>
       </c>
     </row>
     <row r="48">
@@ -3937,16 +4517,28 @@
         <v>0.024999999999999998</v>
       </c>
       <c r="W48" s="0">
-        <v>0.25665299999999996</v>
+        <v>6570.3167999999987</v>
       </c>
       <c r="X48" s="0">
-        <v>402.85399999999936</v>
+        <v>10313062.399999984</v>
       </c>
       <c r="Y48" s="0">
-        <v>739.99588085400046</v>
+        <v>18943894.549862411</v>
       </c>
       <c r="Z48" s="0">
-        <v>0.12516664405036068</v>
+        <v>3204.2660876892332</v>
+      </c>
+      <c r="AA48" s="0">
+        <v>0.33725234693591266</v>
+      </c>
+      <c r="AB48" s="0">
+        <v>1547.5461196655185</v>
+      </c>
+      <c r="AC48" s="0">
+        <v>1264.4387657832044</v>
+      </c>
+      <c r="AD48" s="0">
+        <v>69.405629179687523</v>
       </c>
     </row>
     <row r="49">
@@ -4015,16 +4607,28 @@
         <v>0.024999999999999994</v>
       </c>
       <c r="W49" s="0">
-        <v>0.26428200000000002</v>
+        <v>6765.6192000000001</v>
       </c>
       <c r="X49" s="0">
-        <v>366.24099999999999</v>
+        <v>9375769.5999999996</v>
       </c>
       <c r="Y49" s="0">
-        <v>749.62124667499984</v>
+        <v>19190303.914879996</v>
       </c>
       <c r="Z49" s="0">
-        <v>0.038919884302220542</v>
+        <v>996.34903813684582</v>
+      </c>
+      <c r="AA49" s="0">
+        <v>0.33823180962372018</v>
+      </c>
+      <c r="AB49" s="0">
+        <v>1547.8482261713509</v>
+      </c>
+      <c r="AC49" s="0">
+        <v>1268.9563006294518</v>
+      </c>
+      <c r="AD49" s="0">
+        <v>69.338475117187528</v>
       </c>
     </row>
     <row r="50">
@@ -4093,16 +4697,28 @@
         <v>0.025039062500000001</v>
       </c>
       <c r="W50" s="0">
-        <v>0.25512699999999999</v>
+        <v>6531.2511999999997</v>
       </c>
       <c r="X50" s="0">
-        <v>366.24099999999999</v>
+        <v>9375769.5999999996</v>
       </c>
       <c r="Y50" s="0">
-        <v>742.37547657100004</v>
+        <v>19004812.200217601</v>
       </c>
       <c r="Z50" s="0">
-        <v>0.016476308624736397</v>
+        <v>421.79350079325172</v>
+      </c>
+      <c r="AA50" s="0">
+        <v>0.33879940092926203</v>
+      </c>
+      <c r="AB50" s="0">
+        <v>1542.1347937365326</v>
+      </c>
+      <c r="AC50" s="0">
+        <v>1263.4181540350871</v>
+      </c>
+      <c r="AD50" s="0">
+        <v>68.482190390624979</v>
       </c>
     </row>
     <row r="51">
@@ -4171,16 +4787,28 @@
         <v>-0.00058593749999999792</v>
       </c>
       <c r="W51" s="0">
-        <v>0.26397700000000002</v>
+        <v>6757.8112000000001</v>
       </c>
       <c r="X51" s="0">
-        <v>366.23700000000008</v>
+        <v>9375667.2000000011</v>
       </c>
       <c r="Y51" s="0">
-        <v>761.68895046000034</v>
+        <v>19499237.131776009</v>
       </c>
       <c r="Z51" s="0">
-        <v>0.10932905191095892</v>
+        <v>2798.8237289205481</v>
+      </c>
+      <c r="AA51" s="0">
+        <v>0.34003174826019422</v>
+      </c>
+      <c r="AB51" s="0">
+        <v>1544.230838824592</v>
+      </c>
+      <c r="AC51" s="0">
+        <v>1270.309709694151</v>
+      </c>
+      <c r="AD51" s="0">
+        <v>68.861269999999976</v>
       </c>
     </row>
     <row r="52">
@@ -4249,16 +4877,28 @@
         <v>0.025117187499999999</v>
       </c>
       <c r="W52" s="0">
-        <v>0.24993900000000002</v>
+        <v>6398.4384</v>
       </c>
       <c r="X52" s="0">
-        <v>366.23399999999992</v>
+        <v>9375590.3999999985</v>
       </c>
       <c r="Y52" s="0">
-        <v>729.00366836199964</v>
+        <v>18662493.910067189</v>
       </c>
       <c r="Z52" s="0">
-        <v>0.030047681117144287</v>
+        <v>769.22063659889375</v>
+      </c>
+      <c r="AA52" s="0">
+        <v>0.33708154719340788</v>
+      </c>
+      <c r="AB52" s="0">
+        <v>1544.9029516824714</v>
+      </c>
+      <c r="AC52" s="0">
+        <v>1261.0196788500359</v>
+      </c>
+      <c r="AD52" s="0">
+        <v>69.76368917968756</v>
       </c>
     </row>
     <row r="53">
@@ -4327,16 +4967,28 @@
         <v>0.025117187499999999</v>
       </c>
       <c r="W53" s="0">
-        <v>0.25634800000000002</v>
+        <v>6562.5088000000005</v>
       </c>
       <c r="X53" s="0">
-        <v>384.54500000000007</v>
+        <v>9844352.0000000019</v>
       </c>
       <c r="Y53" s="0">
-        <v>723.47852119200024</v>
+        <v>18521050.142515205</v>
       </c>
       <c r="Z53" s="0">
-        <v>0.048783629450088975</v>
+        <v>1248.8609139222776</v>
+      </c>
+      <c r="AA53" s="0">
+        <v>0.33868198351784606</v>
+      </c>
+      <c r="AB53" s="0">
+        <v>1537.0393591058523</v>
+      </c>
+      <c r="AC53" s="0">
+        <v>1258.6287798079504</v>
+      </c>
+      <c r="AD53" s="0">
+        <v>67.628283984375017</v>
       </c>
     </row>
     <row r="54">
@@ -4405,16 +5057,28 @@
         <v>0.024999999999999998</v>
       </c>
       <c r="W54" s="0">
-        <v>0.26458800000000005</v>
+        <v>6773.4528000000009</v>
       </c>
       <c r="X54" s="0">
-        <v>402.83800000000008</v>
+        <v>10312652.800000003</v>
       </c>
       <c r="Y54" s="0">
-        <v>733.67678460299976</v>
+        <v>18782125.685836792</v>
       </c>
       <c r="Z54" s="0">
-        <v>0.50384886561648845</v>
+        <v>12898.530959782103</v>
+      </c>
+      <c r="AA54" s="0">
+        <v>0.3397635336929698</v>
+      </c>
+      <c r="AB54" s="0">
+        <v>1537.5974378902838</v>
+      </c>
+      <c r="AC54" s="0">
+        <v>1263.7763643178346</v>
+      </c>
+      <c r="AD54" s="0">
+        <v>68.835448554687446</v>
       </c>
     </row>
     <row r="55">
@@ -4483,16 +5147,28 @@
         <v>0.025000000000000001</v>
       </c>
       <c r="W55" s="0">
-        <v>0.25299100000000002</v>
+        <v>6476.5696000000007</v>
       </c>
       <c r="X55" s="0">
-        <v>347.92700000000013</v>
+        <v>8906931.200000003</v>
       </c>
       <c r="Y55" s="0">
-        <v>718.42527437799981</v>
+        <v>18391687.024076793</v>
       </c>
       <c r="Z55" s="0">
-        <v>0.014298935507951046</v>
+        <v>366.05274900354675</v>
+      </c>
+      <c r="AA55" s="0">
+        <v>0.33881259750001702</v>
+      </c>
+      <c r="AB55" s="0">
+        <v>1527.5650166357893</v>
+      </c>
+      <c r="AC55" s="0">
+        <v>1253.9691921389613</v>
+      </c>
+      <c r="AD55" s="0">
+        <v>67.481423632812508</v>
       </c>
     </row>
     <row r="56">
@@ -4561,16 +5237,28 @@
         <v>0.025000000000000001</v>
       </c>
       <c r="W56" s="0">
-        <v>0.25787399999999999</v>
+        <v>6601.5743999999995</v>
       </c>
       <c r="X56" s="0">
-        <v>421.16600000000017</v>
+        <v>10781849.600000003</v>
       </c>
       <c r="Y56" s="0">
-        <v>726.07420716600063</v>
+        <v>18587499.703449614</v>
       </c>
       <c r="Z56" s="0">
-        <v>0.012353405506153469</v>
+        <v>316.24718095752883</v>
+      </c>
+      <c r="AA56" s="0">
+        <v>0.33480513407985868</v>
+      </c>
+      <c r="AB56" s="0">
+        <v>1550.4512642718068</v>
+      </c>
+      <c r="AC56" s="0">
+        <v>1257.8234314767935</v>
+      </c>
+      <c r="AD56" s="0">
+        <v>69.138876484374961</v>
       </c>
     </row>
     <row r="57">
@@ -4639,16 +5327,28 @@
         <v>0.024960937500000002</v>
       </c>
       <c r="W57" s="0">
-        <v>0.25817800000000002</v>
+        <v>6609.3568000000005</v>
       </c>
       <c r="X57" s="0">
-        <v>402.8420000000001</v>
+        <v>10312755.200000003</v>
       </c>
       <c r="Y57" s="0">
-        <v>735.4052472479998</v>
+        <v>18826374.329548795</v>
       </c>
       <c r="Z57" s="0">
-        <v>0.016392720038089306</v>
+        <v>419.65363297508623</v>
+      </c>
+      <c r="AA57" s="0">
+        <v>0.33754387467909674</v>
+      </c>
+      <c r="AB57" s="0">
+        <v>1549.7425091993593</v>
+      </c>
+      <c r="AC57" s="0">
+        <v>1264.1476458202633</v>
+      </c>
+      <c r="AD57" s="0">
+        <v>69.677253046874995</v>
       </c>
     </row>
     <row r="58">
@@ -4717,16 +5417,28 @@
         <v>0.024960937500000002</v>
       </c>
       <c r="W58" s="0">
-        <v>0.26275599999999999</v>
+        <v>6726.5535999999993</v>
       </c>
       <c r="X58" s="0">
-        <v>366.2510000000002</v>
+        <v>9376025.6000000052</v>
       </c>
       <c r="Y58" s="0">
-        <v>753.99520271599977</v>
+        <v>19302277.189529594</v>
       </c>
       <c r="Z58" s="0">
-        <v>0.023552406989464845</v>
+        <v>602.94161893030002</v>
+      </c>
+      <c r="AA58" s="0">
+        <v>0.33775256322197633</v>
+      </c>
+      <c r="AB58" s="0">
+        <v>1543.5383613733534</v>
+      </c>
+      <c r="AC58" s="0">
+        <v>1260.9157925928478</v>
+      </c>
+      <c r="AD58" s="0">
+        <v>68.550867812500002</v>
       </c>
     </row>
     <row r="59">
@@ -4795,16 +5507,28 @@
         <v>0.025468750000000002</v>
       </c>
       <c r="W59" s="0">
-        <v>0.26794399999999996</v>
+        <v>6859.366399999999</v>
       </c>
       <c r="X59" s="0">
-        <v>347.93899999999985</v>
+        <v>8907238.3999999966</v>
       </c>
       <c r="Y59" s="0">
-        <v>733.916996036</v>
+        <v>18788275.098521601</v>
       </c>
       <c r="Z59" s="0">
-        <v>0.02517055129395868</v>
+        <v>644.36611312534217</v>
+      </c>
+      <c r="AA59" s="0">
+        <v>0.33848388800053714</v>
+      </c>
+      <c r="AB59" s="0">
+        <v>1545.4766601632173</v>
+      </c>
+      <c r="AC59" s="0">
+        <v>1267.2976657889731</v>
+      </c>
+      <c r="AD59" s="0">
+        <v>69.056104882812477</v>
       </c>
     </row>
     <row r="60">
@@ -4873,16 +5597,28 @@
         <v>0.024960937500000006</v>
       </c>
       <c r="W60" s="0">
-        <v>0.25787399999999999</v>
+        <v>6601.5743999999995</v>
       </c>
       <c r="X60" s="0">
-        <v>384.54600000000028</v>
+        <v>9844377.6000000071</v>
       </c>
       <c r="Y60" s="0">
-        <v>731.98239384999988</v>
+        <v>18738749.282559998</v>
       </c>
       <c r="Z60" s="0">
-        <v>0.01928476818921248</v>
+        <v>493.69006564383949</v>
+      </c>
+      <c r="AA60" s="0">
+        <v>0.33782737420179865</v>
+      </c>
+      <c r="AB60" s="0">
+        <v>1551.9184086550026</v>
+      </c>
+      <c r="AC60" s="0">
+        <v>1270.1805202667135</v>
+      </c>
+      <c r="AD60" s="0">
+        <v>70.137075000000024</v>
       </c>
     </row>
     <row r="61">
@@ -4951,16 +5687,28 @@
         <v>0.024921875000000003</v>
       </c>
       <c r="W61" s="0">
-        <v>0.26184099999999993</v>
+        <v>6703.1295999999984</v>
       </c>
       <c r="X61" s="0">
-        <v>366.25</v>
+        <v>9376000</v>
       </c>
       <c r="Y61" s="0">
-        <v>745.68198171699987</v>
+        <v>19089458.731955197</v>
       </c>
       <c r="Z61" s="0">
-        <v>0.014711706390466369</v>
+        <v>376.61968359593902</v>
+      </c>
+      <c r="AA61" s="0">
+        <v>0.33838610026925042</v>
+      </c>
+      <c r="AB61" s="0">
+        <v>1544.6616721037219</v>
+      </c>
+      <c r="AC61" s="0">
+        <v>1263.9126621977864</v>
+      </c>
+      <c r="AD61" s="0">
+        <v>69.281249375000058</v>
       </c>
     </row>
     <row r="62">
@@ -5029,16 +5777,28 @@
         <v>0.025312500000000002</v>
       </c>
       <c r="W62" s="0">
-        <v>0.25451699999999999</v>
+        <v>6515.6351999999997</v>
       </c>
       <c r="X62" s="0">
-        <v>366.2510000000002</v>
+        <v>9376025.6000000052</v>
       </c>
       <c r="Y62" s="0">
-        <v>754.13704986500034</v>
+        <v>19305908.476544008</v>
       </c>
       <c r="Z62" s="0">
-        <v>0.011761954626477118</v>
+        <v>301.10603843781422</v>
+      </c>
+      <c r="AA62" s="0">
+        <v>0.33871690132834326</v>
+      </c>
+      <c r="AB62" s="0">
+        <v>1552.5278851442799</v>
+      </c>
+      <c r="AC62" s="0">
+        <v>1273.779131194487</v>
+      </c>
+      <c r="AD62" s="0">
+        <v>70.399124570312495</v>
       </c>
     </row>
     <row r="63">
@@ -5107,16 +5867,28 @@
         <v>0.025820312499999998</v>
       </c>
       <c r="W63" s="0">
-        <v>0.26153599999999999</v>
+        <v>6695.3215999999993</v>
       </c>
       <c r="X63" s="0">
-        <v>384.54600000000028</v>
+        <v>9844377.6000000071</v>
       </c>
       <c r="Y63" s="0">
-        <v>751.88176572900056</v>
+        <v>19248173.202662416</v>
       </c>
       <c r="Z63" s="0">
-        <v>0.0075494637098274982</v>
+        <v>193.26627097158394</v>
+      </c>
+      <c r="AA63" s="0">
+        <v>0.33471279598884551</v>
+      </c>
+      <c r="AB63" s="0">
+        <v>1550.8366707393573</v>
+      </c>
+      <c r="AC63" s="0">
+        <v>1259.3416037526781</v>
+      </c>
+      <c r="AD63" s="0">
+        <v>69.081705546875014</v>
       </c>
     </row>
     <row r="64">
@@ -5185,16 +5957,28 @@
         <v>0.025156250000000005</v>
       </c>
       <c r="W64" s="0">
-        <v>0.27038600000000002</v>
+        <v>6921.8816000000006</v>
       </c>
       <c r="X64" s="0">
-        <v>421.16799999999967</v>
+        <v>10781900.799999991</v>
       </c>
       <c r="Y64" s="0">
-        <v>726.92442340799971</v>
+        <v>18609265.239244793</v>
       </c>
       <c r="Z64" s="0">
-        <v>0.0097072079952605691</v>
+        <v>248.50452467867058</v>
+      </c>
+      <c r="AA64" s="0">
+        <v>0.33847862432373688</v>
+      </c>
+      <c r="AB64" s="0">
+        <v>1550.9475102082761</v>
+      </c>
+      <c r="AC64" s="0">
+        <v>1267.7568418051778</v>
+      </c>
+      <c r="AD64" s="0">
+        <v>70.048501953125026</v>
       </c>
     </row>
     <row r="65">
@@ -5263,16 +6047,28 @@
         <v>0.025039062500000001</v>
       </c>
       <c r="W65" s="0">
-        <v>0.25787300000000002</v>
+        <v>6601.5488000000005</v>
       </c>
       <c r="X65" s="0">
-        <v>421.17999999999984</v>
+        <v>10782207.999999996</v>
       </c>
       <c r="Y65" s="0">
-        <v>770.54745349099994</v>
+        <v>19726014.809369598</v>
       </c>
       <c r="Z65" s="0">
-        <v>0.018918103037330335</v>
+        <v>484.3034377556566</v>
+      </c>
+      <c r="AA65" s="0">
+        <v>0.33730827081062992</v>
+      </c>
+      <c r="AB65" s="0">
+        <v>1549.8035773907079</v>
+      </c>
+      <c r="AC65" s="0">
+        <v>1263.2768007377767</v>
+      </c>
+      <c r="AD65" s="0">
+        <v>70.021692851562491</v>
       </c>
     </row>
     <row r="66">
@@ -5341,16 +6137,28 @@
         <v>-0.00058593750000000139</v>
       </c>
       <c r="W66" s="0">
-        <v>0.25939999999999996</v>
+        <v>6640.6399999999985</v>
       </c>
       <c r="X66" s="0">
-        <v>384.53100000000018</v>
+        <v>9843993.6000000052</v>
       </c>
       <c r="Y66" s="0">
-        <v>740.65069248599957</v>
+        <v>18960657.72764159</v>
       </c>
       <c r="Z66" s="0">
-        <v>0.15282319254503551</v>
+        <v>3912.2737291529093</v>
+      </c>
+      <c r="AA66" s="0">
+        <v>0.33683365743345628</v>
+      </c>
+      <c r="AB66" s="0">
+        <v>1551.8805204757318</v>
+      </c>
+      <c r="AC66" s="0">
+        <v>1265.2705560824556</v>
+      </c>
+      <c r="AD66" s="0">
+        <v>70.594713710937469</v>
       </c>
     </row>
     <row r="67">
@@ -5419,16 +6227,28 @@
         <v>0.025039062500000001</v>
       </c>
       <c r="W67" s="0">
-        <v>0.26245099999999999</v>
+        <v>6718.7455999999993</v>
       </c>
       <c r="X67" s="0">
-        <v>366.23499999999967</v>
+        <v>9375615.9999999907</v>
       </c>
       <c r="Y67" s="0">
-        <v>727.7388446609998</v>
+        <v>18630114.423321594</v>
       </c>
       <c r="Z67" s="0">
-        <v>0.019980443158404686</v>
+        <v>511.49934485515996</v>
+      </c>
+      <c r="AA67" s="0">
+        <v>0.33302871214324309</v>
+      </c>
+      <c r="AB67" s="0">
+        <v>1543.9423628807281</v>
+      </c>
+      <c r="AC67" s="0">
+        <v>1246.5812833609098</v>
+      </c>
+      <c r="AD67" s="0">
+        <v>69.596315312500025</v>
       </c>
     </row>
     <row r="68">
@@ -5497,16 +6317,28 @@
         <v>0.025078125</v>
       </c>
       <c r="W68" s="0">
-        <v>0.26123000000000002</v>
+        <v>6687.4880000000003</v>
       </c>
       <c r="X68" s="0">
-        <v>366.23399999999992</v>
+        <v>9375590.3999999985</v>
       </c>
       <c r="Y68" s="0">
-        <v>738.07963893099986</v>
+        <v>18894838.756633595</v>
       </c>
       <c r="Z68" s="0">
-        <v>0.012369923190529774</v>
+        <v>316.67003367756223</v>
+      </c>
+      <c r="AA68" s="0">
+        <v>0.33425503232929399</v>
+      </c>
+      <c r="AB68" s="0">
+        <v>1549.662597931992</v>
+      </c>
+      <c r="AC68" s="0">
+        <v>1258.6987036618082</v>
+      </c>
+      <c r="AD68" s="0">
+        <v>69.67603011718748</v>
       </c>
     </row>
     <row r="69">
@@ -5575,16 +6407,28 @@
         <v>0.025546874999999997</v>
       </c>
       <c r="W69" s="0">
-        <v>0.26245099999999999</v>
+        <v>6718.7455999999993</v>
       </c>
       <c r="X69" s="0">
-        <v>402.85699999999997</v>
+        <v>10313139.199999999</v>
       </c>
       <c r="Y69" s="0">
-        <v>727.0604948199998</v>
+        <v>18612748.667391993</v>
       </c>
       <c r="Z69" s="0">
-        <v>0.030849088714244639</v>
+        <v>789.7366710846627</v>
+      </c>
+      <c r="AA69" s="0">
+        <v>0.3359741045654156</v>
+      </c>
+      <c r="AB69" s="0">
+        <v>1554.264359714876</v>
+      </c>
+      <c r="AC69" s="0">
+        <v>1267.1418395095748</v>
+      </c>
+      <c r="AD69" s="0">
+        <v>70.566976835937496</v>
       </c>
     </row>
     <row r="70">
@@ -5653,16 +6497,28 @@
         <v>-0.00058593750000000139</v>
       </c>
       <c r="W70" s="0">
-        <v>0.26458800000000005</v>
+        <v>6773.4528000000009</v>
       </c>
       <c r="X70" s="0">
-        <v>402.85800000000017</v>
+        <v>10313164.800000004</v>
       </c>
       <c r="Y70" s="0">
-        <v>758.63588306800011</v>
+        <v>19421078.606540803</v>
       </c>
       <c r="Z70" s="0">
-        <v>0.0064271919491618781</v>
+        <v>164.53611389854407</v>
+      </c>
+      <c r="AA70" s="0">
+        <v>0.3347265768423775</v>
+      </c>
+      <c r="AB70" s="0">
+        <v>1541.9119771277208</v>
+      </c>
+      <c r="AC70" s="0">
+        <v>1252.3114630804523</v>
+      </c>
+      <c r="AD70" s="0">
+        <v>69.250957421875057</v>
       </c>
     </row>
     <row r="71">
@@ -5742,6 +6598,18 @@
       <c r="Z71" s="0">
         <v>0</v>
       </c>
+      <c r="AA71" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
@@ -5809,16 +6677,28 @@
         <v>0.025195312499999997</v>
       </c>
       <c r="W72" s="0">
-        <v>0.26611299999999999</v>
+        <v>6812.4928</v>
       </c>
       <c r="X72" s="0">
-        <v>402.85799999999927</v>
+        <v>10313164.79999998</v>
       </c>
       <c r="Y72" s="0">
-        <v>772.47514400399996</v>
+        <v>19775363.686502397</v>
       </c>
       <c r="Z72" s="0">
-        <v>0.0069362390003434738</v>
+        <v>177.56771840879293</v>
+      </c>
+      <c r="AA72" s="0">
+        <v>0.33589439245999719</v>
+      </c>
+      <c r="AB72" s="0">
+        <v>1551.2026747204552</v>
+      </c>
+      <c r="AC72" s="0">
+        <v>1266.8017656334673</v>
+      </c>
+      <c r="AD72" s="0">
+        <v>70.133478359375005</v>
       </c>
     </row>
     <row r="73">
@@ -5887,16 +6767,28 @@
         <v>-0.00062500000000000056</v>
       </c>
       <c r="W73" s="0">
-        <v>0.25482199999999999</v>
+        <v>6523.4431999999997</v>
       </c>
       <c r="X73" s="0">
-        <v>384.5600000000004</v>
+        <v>9844736.0000000093</v>
       </c>
       <c r="Y73" s="0">
-        <v>789.35447118000002</v>
+        <v>20207474.462207999</v>
       </c>
       <c r="Z73" s="0">
-        <v>0.014101971549877431</v>
+        <v>361.01047167686221</v>
+      </c>
+      <c r="AA73" s="0">
+        <v>0.33662516692617489</v>
+      </c>
+      <c r="AB73" s="0">
+        <v>1545.4972301198218</v>
+      </c>
+      <c r="AC73" s="0">
+        <v>1261.7041250285804</v>
+      </c>
+      <c r="AD73" s="0">
+        <v>68.696507929687485</v>
       </c>
     </row>
     <row r="74">
@@ -5976,6 +6868,18 @@
       <c r="Z74" s="0">
         <v>0</v>
       </c>
+      <c r="AA74" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
@@ -6043,16 +6947,28 @@
         <v>0.026210937500000003</v>
       </c>
       <c r="W75" s="0">
-        <v>0.26763900000000002</v>
+        <v>6851.5583999999999</v>
       </c>
       <c r="X75" s="0">
-        <v>347.9409999999998</v>
+        <v>8907289.599999994</v>
       </c>
       <c r="Y75" s="0">
-        <v>738.62743393600022</v>
+        <v>18908862.308761604</v>
       </c>
       <c r="Z75" s="0">
-        <v>0.0079770599961925467</v>
+        <v>204.2127359025292</v>
+      </c>
+      <c r="AA75" s="0">
+        <v>0.34054695484612152</v>
+      </c>
+      <c r="AB75" s="0">
+        <v>1549.3006258113708</v>
+      </c>
+      <c r="AC75" s="0">
+        <v>1277.5036528447868</v>
+      </c>
+      <c r="AD75" s="0">
+        <v>70.194264687499967</v>
       </c>
     </row>
     <row r="76">
@@ -6121,16 +7037,28 @@
         <v>0.025078124999999996</v>
       </c>
       <c r="W76" s="0">
-        <v>0.26611299999999999</v>
+        <v>6812.4928</v>
       </c>
       <c r="X76" s="0">
-        <v>366.23599999999988</v>
+        <v>9375641.5999999959</v>
       </c>
       <c r="Y76" s="0">
-        <v>735.36465871100017</v>
+        <v>18825335.263001606</v>
       </c>
       <c r="Z76" s="0">
-        <v>0.014960847882173951</v>
+        <v>382.99770578365315</v>
+      </c>
+      <c r="AA76" s="0">
+        <v>0.33747869073944764</v>
+      </c>
+      <c r="AB76" s="0">
+        <v>1536.1692880024978</v>
+      </c>
+      <c r="AC76" s="0">
+        <v>1257.3965765429725</v>
+      </c>
+      <c r="AD76" s="0">
+        <v>68.255403789062527</v>
       </c>
     </row>
     <row r="77">
@@ -6199,16 +7127,28 @@
         <v>-0.0001171874999999975</v>
       </c>
       <c r="W77" s="0">
-        <v>0.30364999999999998</v>
+        <v>7773.4399999999996</v>
       </c>
       <c r="X77" s="0">
-        <v>366.24199999999973</v>
+        <v>9375795.1999999937</v>
       </c>
       <c r="Y77" s="0">
-        <v>792.71665446799898</v>
+        <v>20293546.354380775</v>
       </c>
       <c r="Z77" s="0">
-        <v>0.010874233964609339</v>
+        <v>278.38038949399908</v>
+      </c>
+      <c r="AA77" s="0">
+        <v>0.36473524129858209</v>
+      </c>
+      <c r="AB77" s="0">
+        <v>1560.8287850430506</v>
+      </c>
+      <c r="AC77" s="0">
+        <v>1338.6166645687708</v>
+      </c>
+      <c r="AD77" s="0">
+        <v>70.965781289062477</v>
       </c>
     </row>
     <row r="78">
@@ -6277,16 +7217,28 @@
         <v>0.025429687500000003</v>
       </c>
       <c r="W78" s="0">
-        <v>0.28747600000000001</v>
+        <v>7359.3856000000005</v>
       </c>
       <c r="X78" s="0">
-        <v>347.92700000000013</v>
+        <v>8906931.200000003</v>
       </c>
       <c r="Y78" s="0">
-        <v>746.72947993499929</v>
+        <v>19116274.686335981</v>
       </c>
       <c r="Z78" s="0">
-        <v>0.014931676809117719</v>
+        <v>382.25092631341357</v>
+      </c>
+      <c r="AA78" s="0">
+        <v>0.36387945313916775</v>
+      </c>
+      <c r="AB78" s="0">
+        <v>1550.5074594134383</v>
+      </c>
+      <c r="AC78" s="0">
+        <v>1329.8520415870044</v>
+      </c>
+      <c r="AD78" s="0">
+        <v>67.824955703125028</v>
       </c>
     </row>
     <row r="79">
@@ -6355,16 +7307,28 @@
         <v>0.025859374999999997</v>
       </c>
       <c r="W79" s="0">
-        <v>0.299072</v>
+        <v>7656.2431999999999</v>
       </c>
       <c r="X79" s="0">
-        <v>384.54399999999987</v>
+        <v>9844326.3999999966</v>
       </c>
       <c r="Y79" s="0">
-        <v>802.68463631100076</v>
+        <v>20548726.68956162</v>
       </c>
       <c r="Z79" s="0">
-        <v>0.0094809917157249561</v>
+        <v>242.71338792255887</v>
+      </c>
+      <c r="AA79" s="0">
+        <v>0.36456399498343944</v>
+      </c>
+      <c r="AB79" s="0">
+        <v>1566.4442965129779</v>
+      </c>
+      <c r="AC79" s="0">
+        <v>1341.7355211163442</v>
+      </c>
+      <c r="AD79" s="0">
+        <v>71.091864179687533</v>
       </c>
     </row>
     <row r="80">
@@ -6433,16 +7397,28 @@
         <v>-0.00011718750000000097</v>
       </c>
       <c r="W80" s="0">
-        <v>0.28198299999999998</v>
+        <v>7218.764799999999</v>
       </c>
       <c r="X80" s="0">
-        <v>366.22099999999989</v>
+        <v>9375257.5999999978</v>
       </c>
       <c r="Y80" s="0">
-        <v>753.70649844399941</v>
+        <v>19294886.360166386</v>
       </c>
       <c r="Z80" s="0">
-        <v>0.9817552281580687</v>
+        <v>25132.933840846559</v>
+      </c>
+      <c r="AA80" s="0">
+        <v>0.36135176728880203</v>
+      </c>
+      <c r="AB80" s="0">
+        <v>1561.82926277807</v>
+      </c>
+      <c r="AC80" s="0">
+        <v>1333.9898194451191</v>
+      </c>
+      <c r="AD80" s="0">
+        <v>71.721218242187533</v>
       </c>
     </row>
     <row r="81">
@@ -6511,16 +7487,28 @@
         <v>0.025664062500000001</v>
       </c>
       <c r="W81" s="0">
-        <v>0.299682</v>
+        <v>7671.8591999999999</v>
       </c>
       <c r="X81" s="0">
-        <v>366.25200000000041</v>
+        <v>9376051.2000000104</v>
       </c>
       <c r="Y81" s="0">
-        <v>801.63876873599929</v>
+        <v>20521952.479641583</v>
       </c>
       <c r="Z81" s="0">
-        <v>0.0085442290311940061</v>
+        <v>218.73226319856656</v>
+      </c>
+      <c r="AA81" s="0">
+        <v>0.35921370634290511</v>
+      </c>
+      <c r="AB81" s="0">
+        <v>1562.1025105388064</v>
+      </c>
+      <c r="AC81" s="0">
+        <v>1326.24167907325</v>
+      </c>
+      <c r="AD81" s="0">
+        <v>70.339017968750014</v>
       </c>
     </row>
     <row r="82">
@@ -6589,16 +7577,28 @@
         <v>0.025468749999999998</v>
       </c>
       <c r="W82" s="0">
-        <v>0.30120900000000006</v>
+        <v>7710.9504000000015</v>
       </c>
       <c r="X82" s="0">
-        <v>366.23900000000049</v>
+        <v>9375718.4000000115</v>
       </c>
       <c r="Y82" s="0">
-        <v>779.06416463000096</v>
+        <v>19944042.614528023</v>
       </c>
       <c r="Z82" s="0">
-        <v>0.020408048443440227</v>
+        <v>522.44604015206983</v>
+      </c>
+      <c r="AA82" s="0">
+        <v>0.3651023463823852</v>
+      </c>
+      <c r="AB82" s="0">
+        <v>1559.9118868319299</v>
+      </c>
+      <c r="AC82" s="0">
+        <v>1340.8374038128861</v>
+      </c>
+      <c r="AD82" s="0">
+        <v>69.381045976562504</v>
       </c>
     </row>
     <row r="83">
@@ -6667,16 +7667,28 @@
         <v>0.025117187499999999</v>
       </c>
       <c r="W83" s="0">
-        <v>0.27526899999999993</v>
+        <v>7046.8863999999985</v>
       </c>
       <c r="X83" s="0">
-        <v>402.85300000000007</v>
+        <v>10313036.800000001</v>
       </c>
       <c r="Y83" s="0">
-        <v>774.26637868000012</v>
+        <v>19821219.294208001</v>
       </c>
       <c r="Z83" s="0">
-        <v>0.038587309549868838</v>
+        <v>987.83512447664225</v>
+      </c>
+      <c r="AA83" s="0">
+        <v>0.36248285072718511</v>
+      </c>
+      <c r="AB83" s="0">
+        <v>1559.534975927708</v>
+      </c>
+      <c r="AC83" s="0">
+        <v>1334.5008074009918</v>
+      </c>
+      <c r="AD83" s="0">
+        <v>69.861624882812507</v>
       </c>
     </row>
     <row r="84">
@@ -6745,16 +7757,28 @@
         <v>0.025664062500000001</v>
       </c>
       <c r="W84" s="0">
-        <v>0.28045599999999998</v>
+        <v>7179.6735999999992</v>
       </c>
       <c r="X84" s="0">
-        <v>366.24499999999989</v>
+        <v>9375871.9999999963</v>
       </c>
       <c r="Y84" s="0">
-        <v>789.7259802450003</v>
+        <v>20216985.094272006</v>
       </c>
       <c r="Z84" s="0">
-        <v>0.010523618932390493</v>
+        <v>269.40464466919661</v>
+      </c>
+      <c r="AA84" s="0">
+        <v>0.36092513092446793</v>
+      </c>
+      <c r="AB84" s="0">
+        <v>1558.0631982779405</v>
+      </c>
+      <c r="AC84" s="0">
+        <v>1331.82798628469</v>
+      </c>
+      <c r="AD84" s="0">
+        <v>69.21241824218751</v>
       </c>
     </row>
     <row r="85">
@@ -6823,16 +7847,28 @@
         <v>0.025078125000000003</v>
       </c>
       <c r="W85" s="0">
-        <v>0.27496299999999996</v>
+        <v>7039.0527999999986</v>
       </c>
       <c r="X85" s="0">
-        <v>366.23500000000013</v>
+        <v>9375616.0000000037</v>
       </c>
       <c r="Y85" s="0">
-        <v>809.21138656199992</v>
+        <v>20715811.495987199</v>
       </c>
       <c r="Z85" s="0">
-        <v>0.015345463704147111</v>
+        <v>392.84387082616604</v>
+      </c>
+      <c r="AA85" s="0">
+        <v>0.36054354786686371</v>
+      </c>
+      <c r="AB85" s="0">
+        <v>1564.5116566824265</v>
+      </c>
+      <c r="AC85" s="0">
+        <v>1332.8517361278748</v>
+      </c>
+      <c r="AD85" s="0">
+        <v>70.784980312499954</v>
       </c>
     </row>
     <row r="86">
@@ -6901,16 +7937,28 @@
         <v>0.025078125</v>
       </c>
       <c r="W86" s="0">
-        <v>0.27435300000000007</v>
+        <v>7023.4368000000013</v>
       </c>
       <c r="X86" s="0">
-        <v>384.54800000000023</v>
+        <v>9844428.8000000063</v>
       </c>
       <c r="Y86" s="0">
-        <v>762.16940937499976</v>
+        <v>19511536.879999995</v>
       </c>
       <c r="Z86" s="0">
-        <v>0.027553390362777607</v>
+        <v>705.3667932871067</v>
+      </c>
+      <c r="AA86" s="0">
+        <v>0.36295327807388728</v>
+      </c>
+      <c r="AB86" s="0">
+        <v>1554.1688241099323</v>
+      </c>
+      <c r="AC86" s="0">
+        <v>1334.3403011561477</v>
+      </c>
+      <c r="AD86" s="0">
+        <v>69.335924570312471</v>
       </c>
     </row>
     <row r="87">
@@ -6979,16 +8027,28 @@
         <v>0.025703125000000004</v>
       </c>
       <c r="W87" s="0">
-        <v>0.27099600000000001</v>
+        <v>6937.4976000000006</v>
       </c>
       <c r="X87" s="0">
-        <v>384.54799999999977</v>
+        <v>9844428.7999999933</v>
       </c>
       <c r="Y87" s="0">
-        <v>794.95579135499975</v>
+        <v>20350868.258687992</v>
       </c>
       <c r="Z87" s="0">
-        <v>0.15475482649457264</v>
+        <v>3961.7235582610597</v>
+      </c>
+      <c r="AA87" s="0">
+        <v>0.36016839737360923</v>
+      </c>
+      <c r="AB87" s="0">
+        <v>1545.898574159861</v>
+      </c>
+      <c r="AC87" s="0">
+        <v>1319.1415662526831</v>
+      </c>
+      <c r="AD87" s="0">
+        <v>69.312385429687481</v>
       </c>
     </row>
     <row r="88">
@@ -7057,16 +8117,28 @@
         <v>0.026132812499999998</v>
       </c>
       <c r="W88" s="0">
-        <v>0.27465800000000007</v>
+        <v>7031.2448000000013</v>
       </c>
       <c r="X88" s="0">
-        <v>366.23399999999992</v>
+        <v>9375590.3999999985</v>
       </c>
       <c r="Y88" s="0">
-        <v>750.12447237600054</v>
+        <v>19203186.492825612</v>
       </c>
       <c r="Z88" s="0">
-        <v>0.0086480064744080994</v>
+        <v>221.38896574484733</v>
+      </c>
+      <c r="AA88" s="0">
+        <v>0.36021791494177174</v>
+      </c>
+      <c r="AB88" s="0">
+        <v>1547.3903230262522</v>
+      </c>
+      <c r="AC88" s="0">
+        <v>1321.4213711729392</v>
+      </c>
+      <c r="AD88" s="0">
+        <v>69.061081054687534</v>
       </c>
     </row>
     <row r="89">
@@ -7135,16 +8207,28 @@
         <v>-0.023046874999999998</v>
       </c>
       <c r="W89" s="0">
-        <v>0.29571600000000003</v>
+        <v>7570.3296000000009</v>
       </c>
       <c r="X89" s="0">
-        <v>384.53700000000026</v>
+        <v>9844147.2000000067</v>
       </c>
       <c r="Y89" s="0">
-        <v>758.39944805299956</v>
+        <v>19415025.870156787</v>
       </c>
       <c r="Z89" s="0">
         <v>65535</v>
+      </c>
+      <c r="AA89" s="0">
+        <v>0.36117918377278485</v>
+      </c>
+      <c r="AB89" s="0">
+        <v>1551.8860431888759</v>
+      </c>
+      <c r="AC89" s="0">
+        <v>1327.2823804883265</v>
+      </c>
+      <c r="AD89" s="0">
+        <v>68.962849804687522</v>
       </c>
     </row>
     <row r="90">
@@ -7213,16 +8297,28 @@
         <v>0.025429687499999999</v>
       </c>
       <c r="W90" s="0">
-        <v>0.28594999999999998</v>
+        <v>7320.3199999999997</v>
       </c>
       <c r="X90" s="0">
-        <v>366.22500000000014</v>
+        <v>9375360.0000000037</v>
       </c>
       <c r="Y90" s="0">
-        <v>777.87883524600056</v>
+        <v>19913698.182297613</v>
       </c>
       <c r="Z90" s="0">
-        <v>0.015774938487874035</v>
+        <v>403.8384252895753</v>
+      </c>
+      <c r="AA90" s="0">
+        <v>0.35993921377357641</v>
+      </c>
+      <c r="AB90" s="0">
+        <v>1563.6298201120592</v>
+      </c>
+      <c r="AC90" s="0">
+        <v>1329.334266358813</v>
+      </c>
+      <c r="AD90" s="0">
+        <v>70.961887734374983</v>
       </c>
     </row>
     <row r="91">
@@ -7291,16 +8387,28 @@
         <v>0.025703125</v>
       </c>
       <c r="W91" s="0">
-        <v>0.29022200000000004</v>
+        <v>7429.6832000000004</v>
       </c>
       <c r="X91" s="0">
-        <v>402.87100000000055</v>
+        <v>10313497.600000015</v>
       </c>
       <c r="Y91" s="0">
-        <v>788.20580638399952</v>
+        <v>20178068.643430386</v>
       </c>
       <c r="Z91" s="0">
-        <v>0.0086518865563162423</v>
+        <v>221.48829584169579</v>
+      </c>
+      <c r="AA91" s="0">
+        <v>0.36015545928902887</v>
+      </c>
+      <c r="AB91" s="0">
+        <v>1557.5606341035225</v>
+      </c>
+      <c r="AC91" s="0">
+        <v>1326.0516378979582</v>
+      </c>
+      <c r="AD91" s="0">
+        <v>70.495191562500054</v>
       </c>
     </row>
     <row r="92">
@@ -7369,16 +8477,28 @@
         <v>0.025585937500000003</v>
       </c>
       <c r="W92" s="0">
-        <v>0.28656000000000004</v>
+        <v>7335.9360000000006</v>
       </c>
       <c r="X92" s="0">
-        <v>384.53199999999993</v>
+        <v>9844019.1999999974</v>
       </c>
       <c r="Y92" s="0">
-        <v>778.30052447000025</v>
+        <v>19924493.426432006</v>
       </c>
       <c r="Z92" s="0">
-        <v>0.0099155299133470189</v>
+        <v>253.83756578168368</v>
+      </c>
+      <c r="AA92" s="0">
+        <v>0.35385257421246169</v>
+      </c>
+      <c r="AB92" s="0">
+        <v>1482.42233866116</v>
+      </c>
+      <c r="AC92" s="0">
+        <v>1236.4407224998411</v>
+      </c>
+      <c r="AD92" s="0">
+        <v>67.069437617187489</v>
       </c>
     </row>
     <row r="93">
@@ -7447,16 +8567,28 @@
         <v>0.025546875000000004</v>
       </c>
       <c r="W93" s="0">
-        <v>0.27526900000000004</v>
+        <v>7046.8864000000012</v>
       </c>
       <c r="X93" s="0">
-        <v>384.5590000000002</v>
+        <v>9844710.4000000041</v>
       </c>
       <c r="Y93" s="0">
-        <v>768.70619796599931</v>
+        <v>19678878.667929582</v>
       </c>
       <c r="Z93" s="0">
-        <v>0.02251870471588234</v>
+        <v>576.47884072658792</v>
+      </c>
+      <c r="AA93" s="0">
+        <v>0.35457692996059043</v>
+      </c>
+      <c r="AB93" s="0">
+        <v>1488.5088811731116</v>
+      </c>
+      <c r="AC93" s="0">
+        <v>1245.3878841573235</v>
+      </c>
+      <c r="AD93" s="0">
+        <v>68.015563515625075</v>
       </c>
     </row>
     <row r="94">
@@ -7525,16 +8657,28 @@
         <v>0.025781250000000002</v>
       </c>
       <c r="W94" s="0">
-        <v>0.29388500000000001</v>
+        <v>7523.4560000000001</v>
       </c>
       <c r="X94" s="0">
-        <v>366.24699999999984</v>
+        <v>9375923.1999999955</v>
       </c>
       <c r="Y94" s="0">
-        <v>759.50327456399964</v>
+        <v>19443283.828838389</v>
       </c>
       <c r="Z94" s="0">
-        <v>0.03647091538938195</v>
+        <v>933.65543396817793</v>
+      </c>
+      <c r="AA94" s="0">
+        <v>0.35670115278274267</v>
+      </c>
+      <c r="AB94" s="0">
+        <v>1488.3931012458388</v>
+      </c>
+      <c r="AC94" s="0">
+        <v>1248.0511081728978</v>
+      </c>
+      <c r="AD94" s="0">
+        <v>66.839229296874933</v>
       </c>
     </row>
     <row r="95">
@@ -7603,16 +8747,28 @@
         <v>0.025039062499999997</v>
       </c>
       <c r="W95" s="0">
-        <v>0.28869599999999995</v>
+        <v>7390.6175999999987</v>
       </c>
       <c r="X95" s="0">
-        <v>347.94000000000096</v>
+        <v>8907264.0000000242</v>
       </c>
       <c r="Y95" s="0">
-        <v>736.39523087199905</v>
+        <v>18851717.910323177</v>
       </c>
       <c r="Z95" s="0">
-        <v>0.14199181993355364</v>
+        <v>3634.9905902989731</v>
+      </c>
+      <c r="AA95" s="0">
+        <v>0.35638698211979264</v>
+      </c>
+      <c r="AB95" s="0">
+        <v>1489.4093659140967</v>
+      </c>
+      <c r="AC95" s="0">
+        <v>1250.5556030550906</v>
+      </c>
+      <c r="AD95" s="0">
+        <v>66.965288867187539</v>
       </c>
     </row>
     <row r="96">
@@ -7681,16 +8837,28 @@
         <v>0.025546874999999997</v>
       </c>
       <c r="W96" s="0">
-        <v>0.28564499999999998</v>
+        <v>7312.5119999999997</v>
       </c>
       <c r="X96" s="0">
-        <v>366.24600000000009</v>
+        <v>9375897.6000000015</v>
       </c>
       <c r="Y96" s="0">
-        <v>813.04806762099997</v>
+        <v>20814030.531097598</v>
       </c>
       <c r="Z96" s="0">
-        <v>0.0086836202384553696</v>
+        <v>222.30067810445746</v>
+      </c>
+      <c r="AA96" s="0">
+        <v>0.3532603318755137</v>
+      </c>
+      <c r="AB96" s="0">
+        <v>1481.3143794805806</v>
+      </c>
+      <c r="AC96" s="0">
+        <v>1237.1485288027259</v>
+      </c>
+      <c r="AD96" s="0">
+        <v>67.573488789062509</v>
       </c>
     </row>
     <row r="97">
@@ -7759,16 +8927,28 @@
         <v>0.025820312500000001</v>
       </c>
       <c r="W97" s="0">
-        <v>0.28686499999999998</v>
+        <v>7343.7439999999997</v>
       </c>
       <c r="X97" s="0">
-        <v>421.16799999999967</v>
+        <v>10781900.799999991</v>
       </c>
       <c r="Y97" s="0">
-        <v>793.84675204799987</v>
+        <v>20322476.852428798</v>
       </c>
       <c r="Z97" s="0">
-        <v>0.01253265797911029</v>
+        <v>320.83604426522345</v>
+      </c>
+      <c r="AA97" s="0">
+        <v>0.35344330125083295</v>
+      </c>
+      <c r="AB97" s="0">
+        <v>1484.7531825524259</v>
+      </c>
+      <c r="AC97" s="0">
+        <v>1236.7592970280425</v>
+      </c>
+      <c r="AD97" s="0">
+        <v>66.599843281249974</v>
       </c>
     </row>
     <row r="98">
@@ -7837,16 +9017,28 @@
         <v>0.025546874999999997</v>
       </c>
       <c r="W98" s="0">
-        <v>0.29052799999999995</v>
+        <v>7437.5167999999985</v>
       </c>
       <c r="X98" s="0">
-        <v>384.53999999999996</v>
+        <v>9844223.9999999981</v>
       </c>
       <c r="Y98" s="0">
-        <v>782.55865873199946</v>
+        <v>20033501.663539186</v>
       </c>
       <c r="Z98" s="0">
-        <v>0.013696323168722078</v>
+        <v>350.62587311928519</v>
+      </c>
+      <c r="AA98" s="0">
+        <v>0.35549467592196632</v>
+      </c>
+      <c r="AB98" s="0">
+        <v>1474.6484329433722</v>
+      </c>
+      <c r="AC98" s="0">
+        <v>1235.7112883719194</v>
+      </c>
+      <c r="AD98" s="0">
+        <v>66.234212421875029</v>
       </c>
     </row>
     <row r="99">
@@ -7915,16 +9107,28 @@
         <v>-0.00015625000000000361</v>
       </c>
       <c r="W99" s="0">
-        <v>0.27710000000000001</v>
+        <v>7093.7600000000002</v>
       </c>
       <c r="X99" s="0">
-        <v>366.2470000000003</v>
+        <v>9375923.2000000067</v>
       </c>
       <c r="Y99" s="0">
-        <v>797.35576210800036</v>
+        <v>20412307.509964809</v>
       </c>
       <c r="Z99" s="0">
-        <v>0.060618303159083183</v>
+        <v>1551.8285608725294</v>
+      </c>
+      <c r="AA99" s="0">
+        <v>0.35741040687172121</v>
+      </c>
+      <c r="AB99" s="0">
+        <v>1482.1029653607659</v>
+      </c>
+      <c r="AC99" s="0">
+        <v>1247.5042607613095</v>
+      </c>
+      <c r="AD99" s="0">
+        <v>66.575745546874984</v>
       </c>
     </row>
     <row r="100">
@@ -7993,16 +9197,28 @@
         <v>0.025351562500000001</v>
       </c>
       <c r="W100" s="0">
-        <v>0.27435300000000001</v>
+        <v>7023.4368000000004</v>
       </c>
       <c r="X100" s="0">
-        <v>384.54499999999962</v>
+        <v>9844351.9999999907</v>
       </c>
       <c r="Y100" s="0">
-        <v>792.92796399600047</v>
+        <v>20298955.878297612</v>
       </c>
       <c r="Z100" s="0">
-        <v>0.014694271856666016</v>
+        <v>376.17335953064998</v>
+      </c>
+      <c r="AA100" s="0">
+        <v>0.35450986614298069</v>
+      </c>
+      <c r="AB100" s="0">
+        <v>1476.9340264842408</v>
+      </c>
+      <c r="AC100" s="0">
+        <v>1235.4647285721687</v>
+      </c>
+      <c r="AD100" s="0">
+        <v>65.890201601562481</v>
       </c>
     </row>
     <row r="101">
@@ -8071,16 +9287,28 @@
         <v>0.025429687499999999</v>
       </c>
       <c r="W101" s="0">
-        <v>0.28625499999999998</v>
+        <v>7328.1279999999997</v>
       </c>
       <c r="X101" s="0">
-        <v>366.22999999999979</v>
+        <v>9375487.9999999944</v>
       </c>
       <c r="Y101" s="0">
-        <v>744.02768904400091</v>
+        <v>19047108.839526422</v>
       </c>
       <c r="Z101" s="0">
-        <v>0.016257079844450018</v>
+        <v>416.18124401792045</v>
+      </c>
+      <c r="AA101" s="0">
+        <v>0.35319818253057628</v>
+      </c>
+      <c r="AB101" s="0">
+        <v>1484.9587209201111</v>
+      </c>
+      <c r="AC101" s="0">
+        <v>1231.6824382387329</v>
+      </c>
+      <c r="AD101" s="0">
+        <v>67.123744726562478</v>
       </c>
     </row>
     <row r="102">
@@ -8149,16 +9377,28 @@
         <v>0.025937499999999995</v>
       </c>
       <c r="W102" s="0">
-        <v>0.27862600000000004</v>
+        <v>7132.825600000001</v>
       </c>
       <c r="X102" s="0">
-        <v>384.54399999999987</v>
+        <v>9844326.3999999966</v>
       </c>
       <c r="Y102" s="0">
-        <v>793.4668152029999</v>
+        <v>20312750.469196796</v>
       </c>
       <c r="Z102" s="0">
-        <v>0.010868643839754975</v>
+        <v>278.23728229772735</v>
+      </c>
+      <c r="AA102" s="0">
+        <v>0.35796596891650551</v>
+      </c>
+      <c r="AB102" s="0">
+        <v>1488.27624640163</v>
+      </c>
+      <c r="AC102" s="0">
+        <v>1250.0406405822769</v>
+      </c>
+      <c r="AD102" s="0">
+        <v>67.137516757812477</v>
       </c>
     </row>
     <row r="103">
@@ -8227,16 +9467,28 @@
         <v>0.025429687499999999</v>
       </c>
       <c r="W103" s="0">
-        <v>0.29327400000000003</v>
+        <v>7507.8144000000011</v>
       </c>
       <c r="X103" s="0">
-        <v>402.85400000000004</v>
+        <v>10313062.4</v>
       </c>
       <c r="Y103" s="0">
-        <v>816.36639124300018</v>
+        <v>20898979.615820803</v>
       </c>
       <c r="Z103" s="0">
-        <v>0.052533471829798853</v>
+        <v>1344.8568788428506</v>
+      </c>
+      <c r="AA103" s="0">
+        <v>0.35716585755182895</v>
+      </c>
+      <c r="AB103" s="0">
+        <v>1485.0728503516248</v>
+      </c>
+      <c r="AC103" s="0">
+        <v>1245.9529487200073</v>
+      </c>
+      <c r="AD103" s="0">
+        <v>66.205815351562492</v>
       </c>
     </row>
     <row r="104">
@@ -8305,16 +9557,28 @@
         <v>0.026679687500000007</v>
       </c>
       <c r="W104" s="0">
-        <v>0.28564500000000004</v>
+        <v>7312.5120000000006</v>
       </c>
       <c r="X104" s="0">
-        <v>402.85699999999997</v>
+        <v>10313139.199999999</v>
       </c>
       <c r="Y104" s="0">
-        <v>765.58647761900056</v>
+        <v>19599013.827046413</v>
       </c>
       <c r="Z104" s="0">
-        <v>0.018444362915176708</v>
+        <v>472.17569062852368</v>
+      </c>
+      <c r="AA104" s="0">
+        <v>0.3532588262285184</v>
+      </c>
+      <c r="AB104" s="0">
+        <v>1466.49179390052</v>
+      </c>
+      <c r="AC104" s="0">
+        <v>1226.2671575571455</v>
+      </c>
+      <c r="AD104" s="0">
+        <v>64.986929960937502</v>
       </c>
     </row>
     <row r="105">
@@ -8383,16 +9647,28 @@
         <v>0.025976562499999998</v>
       </c>
       <c r="W105" s="0">
-        <v>0.27923499999999996</v>
+        <v>7148.4159999999983</v>
       </c>
       <c r="X105" s="0">
-        <v>384.55899999999974</v>
+        <v>9844710.3999999929</v>
       </c>
       <c r="Y105" s="0">
-        <v>762.73463533999939</v>
+        <v>19526006.664703984</v>
       </c>
       <c r="Z105" s="0">
-        <v>0.01348152811350747</v>
+        <v>345.12711970579124</v>
+      </c>
+      <c r="AA105" s="0">
+        <v>0.35601379983313103</v>
+      </c>
+      <c r="AB105" s="0">
+        <v>1478.4661687674336</v>
+      </c>
+      <c r="AC105" s="0">
+        <v>1233.8473787526777</v>
+      </c>
+      <c r="AD105" s="0">
+        <v>66.777286445312498</v>
       </c>
     </row>
     <row r="106">
@@ -8461,16 +9737,28 @@
         <v>0.025390625000000003</v>
       </c>
       <c r="W106" s="0">
-        <v>0.29419000000000006</v>
+        <v>7531.264000000001</v>
       </c>
       <c r="X106" s="0">
-        <v>402.85300000000007</v>
+        <v>10313036.800000001</v>
       </c>
       <c r="Y106" s="0">
-        <v>784.22670872499998</v>
+        <v>20076203.743359998</v>
       </c>
       <c r="Z106" s="0">
-        <v>0.014163463823815902</v>
+        <v>362.58467388968711</v>
+      </c>
+      <c r="AA106" s="0">
+        <v>0.3542884425542292</v>
+      </c>
+      <c r="AB106" s="0">
+        <v>1474.9753835581616</v>
+      </c>
+      <c r="AC106" s="0">
+        <v>1231.3125233850485</v>
+      </c>
+      <c r="AD106" s="0">
+        <v>65.78492453124997</v>
       </c>
     </row>
     <row r="107">
@@ -8539,16 +9827,28 @@
         <v>0.025273437499999996</v>
       </c>
       <c r="W107" s="0">
-        <v>0.27404799999999996</v>
+        <v>7015.6287999999986</v>
       </c>
       <c r="X107" s="0">
-        <v>384.54099999999994</v>
+        <v>9844249.5999999978</v>
       </c>
       <c r="Y107" s="0">
-        <v>734.68423502600035</v>
+        <v>18807916.41666561</v>
       </c>
       <c r="Z107" s="0">
-        <v>0.0099896934176602926</v>
+        <v>255.73615149210349</v>
+      </c>
+      <c r="AA107" s="0">
+        <v>0.34487208438886247</v>
+      </c>
+      <c r="AB107" s="0">
+        <v>1359.7860248673605</v>
+      </c>
+      <c r="AC107" s="0">
+        <v>1095.8575373673061</v>
+      </c>
+      <c r="AD107" s="0">
+        <v>61.426173945312506</v>
       </c>
     </row>
     <row r="108">
@@ -8617,16 +9917,28 @@
         <v>0.025312500000000002</v>
       </c>
       <c r="W108" s="0">
-        <v>0.28045599999999998</v>
+        <v>7179.6735999999992</v>
       </c>
       <c r="X108" s="0">
-        <v>402.86300000000028</v>
+        <v>10313292.800000006</v>
       </c>
       <c r="Y108" s="0">
-        <v>724.16656560599995</v>
+        <v>18538664.079513598</v>
       </c>
       <c r="Z108" s="0">
-        <v>0.018826320490913682</v>
+        <v>481.95380456739025</v>
+      </c>
+      <c r="AA108" s="0">
+        <v>0.3451300414929348</v>
+      </c>
+      <c r="AB108" s="0">
+        <v>1370.1293778801642</v>
+      </c>
+      <c r="AC108" s="0">
+        <v>1107.0256974694453</v>
+      </c>
+      <c r="AD108" s="0">
+        <v>62.635012695312547</v>
       </c>
     </row>
     <row r="109">
@@ -8695,16 +10007,28 @@
         <v>0.025351562500000001</v>
       </c>
       <c r="W109" s="0">
-        <v>0.30792200000000003</v>
+        <v>7882.8032000000003</v>
       </c>
       <c r="X109" s="0">
-        <v>366.24500000000035</v>
+        <v>9375872.0000000093</v>
       </c>
       <c r="Y109" s="0">
-        <v>747.75323997199985</v>
+        <v>19142482.943283197</v>
       </c>
       <c r="Z109" s="0">
-        <v>0.016639113503238406</v>
+        <v>425.96130568290317</v>
+      </c>
+      <c r="AA109" s="0">
+        <v>0.34376993392268457</v>
+      </c>
+      <c r="AB109" s="0">
+        <v>1369.1071604369943</v>
+      </c>
+      <c r="AC109" s="0">
+        <v>1096.8742760491375</v>
+      </c>
+      <c r="AD109" s="0">
+        <v>62.996589726562441</v>
       </c>
     </row>
     <row r="110">
@@ -8773,16 +10097,28 @@
         <v>0.025312500000000002</v>
       </c>
       <c r="W110" s="0">
-        <v>0.28930699999999998</v>
+        <v>7406.2591999999995</v>
       </c>
       <c r="X110" s="0">
-        <v>384.55600000000004</v>
+        <v>9844633.6000000015</v>
       </c>
       <c r="Y110" s="0">
-        <v>745.15109156800008</v>
+        <v>19075867.944140803</v>
       </c>
       <c r="Z110" s="0">
-        <v>0.070155039506364203</v>
+        <v>1795.9690113629235</v>
+      </c>
+      <c r="AA110" s="0">
+        <v>0.34734331962661164</v>
+      </c>
+      <c r="AB110" s="0">
+        <v>1364.7155664395548</v>
+      </c>
+      <c r="AC110" s="0">
+        <v>1105.1843052595923</v>
+      </c>
+      <c r="AD110" s="0">
+        <v>62.779080273437508</v>
       </c>
     </row>
     <row r="111">
@@ -8851,16 +10187,28 @@
         <v>0.025429687499999999</v>
       </c>
       <c r="W111" s="0">
-        <v>0.29388400000000003</v>
+        <v>7523.4304000000011</v>
       </c>
       <c r="X111" s="0">
-        <v>366.24699999999984</v>
+        <v>9375923.1999999955</v>
       </c>
       <c r="Y111" s="0">
-        <v>725.81049146199939</v>
+        <v>18580748.581427183</v>
       </c>
       <c r="Z111" s="0">
-        <v>0.1303086588871977</v>
+        <v>3335.9016675122612</v>
+      </c>
+      <c r="AA111" s="0">
+        <v>0.3447145256626008</v>
+      </c>
+      <c r="AB111" s="0">
+        <v>1358.4750747670821</v>
+      </c>
+      <c r="AC111" s="0">
+        <v>1093.254545713671</v>
+      </c>
+      <c r="AD111" s="0">
+        <v>61.389471601562484</v>
       </c>
     </row>
     <row r="112">
@@ -8929,16 +10277,28 @@
         <v>0.025546874999999997</v>
       </c>
       <c r="W112" s="0">
-        <v>0.27710000000000001</v>
+        <v>7093.7600000000002</v>
       </c>
       <c r="X112" s="0">
-        <v>366.22500000000014</v>
+        <v>9375360.0000000037</v>
       </c>
       <c r="Y112" s="0">
-        <v>753.6667988690001</v>
+        <v>19293870.051046401</v>
       </c>
       <c r="Z112" s="0">
-        <v>0.012763706276738722</v>
+        <v>326.75088068451129</v>
+      </c>
+      <c r="AA112" s="0">
+        <v>0.34283292097562207</v>
+      </c>
+      <c r="AB112" s="0">
+        <v>1370.7074492622394</v>
+      </c>
+      <c r="AC112" s="0">
+        <v>1103.0225464334098</v>
+      </c>
+      <c r="AD112" s="0">
+        <v>63.080770664062513</v>
       </c>
     </row>
     <row r="113">
@@ -9007,16 +10367,28 @@
         <v>0.025429687500000006</v>
       </c>
       <c r="W113" s="0">
-        <v>0.30517599999999995</v>
+        <v>7812.5055999999986</v>
       </c>
       <c r="X113" s="0">
-        <v>347.9360000000006</v>
+        <v>8907161.6000000145</v>
       </c>
       <c r="Y113" s="0">
-        <v>707.17625731599992</v>
+        <v>18103712.187289599</v>
       </c>
       <c r="Z113" s="0">
-        <v>0.025459919326703787</v>
+        <v>651.77393476361692</v>
+      </c>
+      <c r="AA113" s="0">
+        <v>0.34458947414301039</v>
+      </c>
+      <c r="AB113" s="0">
+        <v>1369.1966110433709</v>
+      </c>
+      <c r="AC113" s="0">
+        <v>1099.772705289467</v>
+      </c>
+      <c r="AD113" s="0">
+        <v>62.828170859374985</v>
       </c>
     </row>
     <row r="114">
@@ -9085,16 +10457,28 @@
         <v>0.025351562500000001</v>
       </c>
       <c r="W114" s="0">
-        <v>0.28381299999999993</v>
+        <v>7265.6127999999981</v>
       </c>
       <c r="X114" s="0">
-        <v>366.21800000000002</v>
+        <v>9375180.8000000007</v>
       </c>
       <c r="Y114" s="0">
-        <v>723.87446550599998</v>
+        <v>18531186.316953599</v>
       </c>
       <c r="Z114" s="0">
-        <v>0.01547610389704703</v>
+        <v>396.18825976440394</v>
+      </c>
+      <c r="AA114" s="0">
+        <v>0.34265708120352395</v>
+      </c>
+      <c r="AB114" s="0">
+        <v>1368.4522688587933</v>
+      </c>
+      <c r="AC114" s="0">
+        <v>1096.0117830252434</v>
+      </c>
+      <c r="AD114" s="0">
+        <v>62.596924414062514</v>
       </c>
     </row>
     <row r="115">
@@ -9163,16 +10547,28 @@
         <v>0.025312499999999995</v>
       </c>
       <c r="W115" s="0">
-        <v>0.28198200000000001</v>
+        <v>7218.7392</v>
       </c>
       <c r="X115" s="0">
-        <v>384.55400000000009</v>
+        <v>9844582.4000000022</v>
       </c>
       <c r="Y115" s="0">
-        <v>736.10710382499974</v>
+        <v>18844341.857919995</v>
       </c>
       <c r="Z115" s="0">
-        <v>0.043446494514099689</v>
+        <v>1112.2302595609519</v>
+      </c>
+      <c r="AA115" s="0">
+        <v>0.34654299271217121</v>
+      </c>
+      <c r="AB115" s="0">
+        <v>1368.4435544656453</v>
+      </c>
+      <c r="AC115" s="0">
+        <v>1108.4211226228863</v>
+      </c>
+      <c r="AD115" s="0">
+        <v>62.173216953124992</v>
       </c>
     </row>
     <row r="116">
@@ -9241,16 +10637,28 @@
         <v>0.025429687500000003</v>
       </c>
       <c r="W116" s="0">
-        <v>0.27801599999999999</v>
+        <v>7117.2095999999992</v>
       </c>
       <c r="X116" s="0">
-        <v>384.54300000000035</v>
+        <v>9844300.8000000082</v>
       </c>
       <c r="Y116" s="0">
-        <v>742.01055461600026</v>
+        <v>18995470.198169608</v>
       </c>
       <c r="Z116" s="0">
-        <v>0.94836003540360192</v>
+        <v>24278.01690633221</v>
+      </c>
+      <c r="AA116" s="0">
+        <v>0.343027763531706</v>
+      </c>
+      <c r="AB116" s="0">
+        <v>1363.9131175598411</v>
+      </c>
+      <c r="AC116" s="0">
+        <v>1098.9483076865774</v>
+      </c>
+      <c r="AD116" s="0">
+        <v>62.380987539062467</v>
       </c>
     </row>
     <row r="117">
@@ -9319,16 +10727,28 @@
         <v>0.025429687500000003</v>
       </c>
       <c r="W117" s="0">
-        <v>0.299987</v>
+        <v>7679.6671999999999</v>
       </c>
       <c r="X117" s="0">
-        <v>402.85500000000002</v>
+        <v>10313088</v>
       </c>
       <c r="Y117" s="0">
-        <v>781.6274462299998</v>
+        <v>20009662.623487994</v>
       </c>
       <c r="Z117" s="0">
-        <v>0.0097111506382658117</v>
+        <v>248.60545633960479</v>
+      </c>
+      <c r="AA117" s="0">
+        <v>0.34561781613558318</v>
+      </c>
+      <c r="AB117" s="0">
+        <v>1368.6544555117148</v>
+      </c>
+      <c r="AC117" s="0">
+        <v>1101.1908081076538</v>
+      </c>
+      <c r="AD117" s="0">
+        <v>62.048753476562474</v>
       </c>
     </row>
     <row r="118">
@@ -9397,16 +10817,28 @@
         <v>0.025468750000000002</v>
       </c>
       <c r="W118" s="0">
-        <v>0.28930599999999995</v>
+        <v>7406.2335999999987</v>
       </c>
       <c r="X118" s="0">
-        <v>366.23799999999983</v>
+        <v>9375692.7999999952</v>
       </c>
       <c r="Y118" s="0">
-        <v>812.62321501400038</v>
+        <v>20803154.304358408</v>
       </c>
       <c r="Z118" s="0">
-        <v>0.011003561250024586</v>
+        <v>281.69116800062943</v>
+      </c>
+      <c r="AA118" s="0">
+        <v>0.34871030403237313</v>
+      </c>
+      <c r="AB118" s="0">
+        <v>1366.1084545620865</v>
+      </c>
+      <c r="AC118" s="0">
+        <v>1108.0869210294013</v>
+      </c>
+      <c r="AD118" s="0">
+        <v>62.214729453125003</v>
       </c>
     </row>
     <row r="119">
@@ -9475,16 +10907,28 @@
         <v>0.025390625000000007</v>
       </c>
       <c r="W119" s="0">
-        <v>0.27648900000000004</v>
+        <v>7078.1184000000012</v>
       </c>
       <c r="X119" s="0">
-        <v>384.55500000000029</v>
+        <v>9844608.0000000075</v>
       </c>
       <c r="Y119" s="0">
-        <v>732.64742016399941</v>
+        <v>18755773.956198383</v>
       </c>
       <c r="Z119" s="0">
-        <v>0.057778124548887977</v>
+        <v>1479.1199884515322</v>
+      </c>
+      <c r="AA119" s="0">
+        <v>0.34270589586357347</v>
+      </c>
+      <c r="AB119" s="0">
+        <v>1375.9035181810418</v>
+      </c>
+      <c r="AC119" s="0">
+        <v>1102.0178476443109</v>
+      </c>
+      <c r="AD119" s="0">
+        <v>63.439231796875021</v>
       </c>
     </row>
     <row r="120">
@@ -9553,16 +10997,28 @@
         <v>0.025429687499999999</v>
       </c>
       <c r="W120" s="0">
-        <v>0.305481</v>
+        <v>7820.3135999999995</v>
       </c>
       <c r="X120" s="0">
-        <v>384.54799999999977</v>
+        <v>9844428.7999999933</v>
       </c>
       <c r="Y120" s="0">
-        <v>708.70132928999965</v>
+        <v>18142754.029823992</v>
       </c>
       <c r="Z120" s="0">
-        <v>0.0091849248273608158</v>
+        <v>235.13407558043687</v>
+      </c>
+      <c r="AA120" s="0">
+        <v>0.3449976819226917</v>
+      </c>
+      <c r="AB120" s="0">
+        <v>1359.5607044234384</v>
+      </c>
+      <c r="AC120" s="0">
+        <v>1096.3844233350733</v>
+      </c>
+      <c r="AD120" s="0">
+        <v>61.5110558203125</v>
       </c>
     </row>
     <row r="121">
@@ -9631,16 +11087,28 @@
         <v>0.025351562500000001</v>
       </c>
       <c r="W121" s="0">
-        <v>0.29998799999999998</v>
+        <v>7679.6927999999989</v>
       </c>
       <c r="X121" s="0">
-        <v>384.55699999999933</v>
+        <v>9844659.1999999825</v>
       </c>
       <c r="Y121" s="0">
-        <v>733.27513670200028</v>
+        <v>18771843.499571208</v>
       </c>
       <c r="Z121" s="0">
-        <v>0.037133907890297947</v>
+        <v>950.62804199162747</v>
+      </c>
+      <c r="AA121" s="0">
+        <v>0.34512391151749211</v>
+      </c>
+      <c r="AB121" s="0">
+        <v>1371.9142184217174</v>
+      </c>
+      <c r="AC121" s="0">
+        <v>1103.735789166971</v>
+      </c>
+      <c r="AD121" s="0">
+        <v>63.133466992187522</v>
       </c>
     </row>
     <row r="122">
@@ -9720,6 +11188,18 @@
       <c r="Z122" s="0">
         <v>0</v>
       </c>
+      <c r="AA122" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB122" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC122" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD122" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="0">
@@ -9787,16 +11267,28 @@
         <v>0.025585937500000003</v>
       </c>
       <c r="W123" s="0">
-        <v>0.28991700000000004</v>
+        <v>7421.8752000000004</v>
       </c>
       <c r="X123" s="0">
-        <v>402.85800000000017</v>
+        <v>10313164.800000004</v>
       </c>
       <c r="Y123" s="0">
-        <v>745.89313692399992</v>
+        <v>19094864.305254396</v>
       </c>
       <c r="Z123" s="0">
-        <v>0.0096491743042743418</v>
+        <v>247.01886218942315</v>
+      </c>
+      <c r="AA123" s="0">
+        <v>0.33140805643072713</v>
+      </c>
+      <c r="AB123" s="0">
+        <v>1218.3210468520788</v>
+      </c>
+      <c r="AC123" s="0">
+        <v>930.26997747314635</v>
+      </c>
+      <c r="AD123" s="0">
+        <v>56.315335429687536</v>
       </c>
     </row>
     <row r="124">
@@ -9865,16 +11357,28 @@
         <v>0.025351562500000001</v>
       </c>
       <c r="W124" s="0">
-        <v>0.307923</v>
+        <v>7882.8288000000002</v>
       </c>
       <c r="X124" s="0">
-        <v>384.55099999999993</v>
+        <v>9844505.5999999978</v>
       </c>
       <c r="Y124" s="0">
-        <v>729.66691682199962</v>
+        <v>18679473.07064319</v>
       </c>
       <c r="Z124" s="0">
-        <v>0.011298765351603814</v>
+        <v>289.24839300105765</v>
+      </c>
+      <c r="AA124" s="0">
+        <v>0.33003146239395226</v>
+      </c>
+      <c r="AB124" s="0">
+        <v>1214.6646183791265</v>
+      </c>
+      <c r="AC124" s="0">
+        <v>924.57518896316549</v>
+      </c>
+      <c r="AD124" s="0">
+        <v>55.560827070312534</v>
       </c>
     </row>
     <row r="125">
@@ -9943,16 +11447,28 @@
         <v>0.025468749999999998</v>
       </c>
       <c r="W125" s="0">
-        <v>0.30029300000000003</v>
+        <v>7687.5008000000007</v>
       </c>
       <c r="X125" s="0">
-        <v>384.53400000000033</v>
+        <v>9844070.4000000078</v>
       </c>
       <c r="Y125" s="0">
-        <v>679.85497962000022</v>
+        <v>17404287.478272006</v>
       </c>
       <c r="Z125" s="0">
-        <v>0.018351348413293923</v>
+        <v>469.7945193803244</v>
+      </c>
+      <c r="AA125" s="0">
+        <v>0.33129879004394269</v>
+      </c>
+      <c r="AB125" s="0">
+        <v>1205.2833542740057</v>
+      </c>
+      <c r="AC125" s="0">
+        <v>921.21138059172733</v>
+      </c>
+      <c r="AD125" s="0">
+        <v>54.595848242187429</v>
       </c>
     </row>
     <row r="126">
@@ -10021,16 +11537,28 @@
         <v>0.025351562500000001</v>
       </c>
       <c r="W126" s="0">
-        <v>0.29724099999999998</v>
+        <v>7609.3695999999991</v>
       </c>
       <c r="X126" s="0">
-        <v>366.23599999999988</v>
+        <v>9375641.5999999959</v>
       </c>
       <c r="Y126" s="0">
-        <v>716.82524858800025</v>
+        <v>18350726.363852806</v>
       </c>
       <c r="Z126" s="0">
-        <v>0.043629467965429561</v>
+        <v>1116.9143799149967</v>
+      </c>
+      <c r="AA126" s="0">
+        <v>0.33320714580835764</v>
+      </c>
+      <c r="AB126" s="0">
+        <v>1222.0025500331742</v>
+      </c>
+      <c r="AC126" s="0">
+        <v>935.4531209864216</v>
+      </c>
+      <c r="AD126" s="0">
+        <v>57.633320976562473</v>
       </c>
     </row>
     <row r="127">
@@ -10099,16 +11627,28 @@
         <v>0.025312499999999998</v>
       </c>
       <c r="W127" s="0">
-        <v>0.29357900000000003</v>
+        <v>7515.6224000000011</v>
       </c>
       <c r="X127" s="0">
-        <v>366.22900000000004</v>
+        <v>9375462.4000000004</v>
       </c>
       <c r="Y127" s="0">
-        <v>710.47975285400025</v>
+        <v>18188281.673062406</v>
       </c>
       <c r="Z127" s="0">
-        <v>0.010232568807211328</v>
+        <v>261.95376146461001</v>
+      </c>
+      <c r="AA127" s="0">
+        <v>0.33121301457539482</v>
+      </c>
+      <c r="AB127" s="0">
+        <v>1219.2236019560082</v>
+      </c>
+      <c r="AC127" s="0">
+        <v>932.34344221715571</v>
+      </c>
+      <c r="AD127" s="0">
+        <v>56.244947773437438</v>
       </c>
     </row>
     <row r="128">
@@ -10177,16 +11717,28 @@
         <v>0.025546875000000004</v>
       </c>
       <c r="W128" s="0">
-        <v>0.29266399999999998</v>
+        <v>7492.1983999999993</v>
       </c>
       <c r="X128" s="0">
-        <v>384.54200000000014</v>
+        <v>9844275.200000003</v>
       </c>
       <c r="Y128" s="0">
-        <v>707.62847548500031</v>
+        <v>18115288.972416006</v>
       </c>
       <c r="Z128" s="0">
-        <v>0.021125170323416629</v>
+        <v>540.80436027946564</v>
+      </c>
+      <c r="AA128" s="0">
+        <v>0.32993229397913337</v>
+      </c>
+      <c r="AB128" s="0">
+        <v>1212.9292059042359</v>
+      </c>
+      <c r="AC128" s="0">
+        <v>925.09623755152893</v>
+      </c>
+      <c r="AD128" s="0">
+        <v>54.701176171874998</v>
       </c>
     </row>
     <row r="129">
@@ -10255,16 +11807,28 @@
         <v>0.025156249999999998</v>
       </c>
       <c r="W129" s="0">
-        <v>0.29144300000000001</v>
+        <v>7460.9408000000003</v>
       </c>
       <c r="X129" s="0">
-        <v>366.2320000000002</v>
+        <v>9375539.2000000048</v>
       </c>
       <c r="Y129" s="0">
-        <v>702.6828867820002</v>
+        <v>17988681.901619203</v>
       </c>
       <c r="Z129" s="0">
-        <v>0.055725082663506904</v>
+        <v>1426.5621161857766</v>
+      </c>
+      <c r="AA129" s="0">
+        <v>0.3297685271127237</v>
+      </c>
+      <c r="AB129" s="0">
+        <v>1221.1722559872642</v>
+      </c>
+      <c r="AC129" s="0">
+        <v>929.27788399307371</v>
+      </c>
+      <c r="AD129" s="0">
+        <v>56.18655476562499</v>
       </c>
     </row>
     <row r="130">
@@ -10333,16 +11897,28 @@
         <v>0.025195312500000004</v>
       </c>
       <c r="W130" s="0">
-        <v>0.28137200000000007</v>
+        <v>7203.1232000000018</v>
       </c>
       <c r="X130" s="0">
-        <v>402.85400000000027</v>
+        <v>10313062.400000006</v>
       </c>
       <c r="Y130" s="0">
-        <v>697.61508150699956</v>
+        <v>17858946.086579189</v>
       </c>
       <c r="Z130" s="0">
-        <v>0.0099740387131242707</v>
+        <v>255.33539105598132</v>
+      </c>
+      <c r="AA130" s="0">
+        <v>0.33289382837023168</v>
+      </c>
+      <c r="AB130" s="0">
+        <v>1220.4546938532712</v>
+      </c>
+      <c r="AC130" s="0">
+        <v>936.80244917012408</v>
+      </c>
+      <c r="AD130" s="0">
+        <v>56.257636914062481</v>
       </c>
     </row>
     <row r="131">
@@ -10411,16 +11987,28 @@
         <v>0.025195312500000004</v>
       </c>
       <c r="W131" s="0">
-        <v>0.29968299999999998</v>
+        <v>7671.8847999999989</v>
       </c>
       <c r="X131" s="0">
-        <v>384.55100000000039</v>
+        <v>9844505.6000000089</v>
       </c>
       <c r="Y131" s="0">
-        <v>678.52602174899948</v>
+        <v>17370266.156774387</v>
       </c>
       <c r="Z131" s="0">
-        <v>0.66560718798719931</v>
+        <v>17039.544012472303</v>
+      </c>
+      <c r="AA131" s="0">
+        <v>0.33228203180337579</v>
+      </c>
+      <c r="AB131" s="0">
+        <v>1215.0995690444283</v>
+      </c>
+      <c r="AC131" s="0">
+        <v>931.27731088709197</v>
+      </c>
+      <c r="AD131" s="0">
+        <v>55.873345195312503</v>
       </c>
     </row>
     <row r="132">
@@ -10489,16 +12077,28 @@
         <v>0.025156249999999998</v>
       </c>
       <c r="W132" s="0">
-        <v>0.30090299999999998</v>
+        <v>7703.1167999999989</v>
       </c>
       <c r="X132" s="0">
-        <v>366.22599999999989</v>
+        <v>9375385.5999999978</v>
       </c>
       <c r="Y132" s="0">
-        <v>710.91262964800012</v>
+        <v>18199363.318988804</v>
       </c>
       <c r="Z132" s="0">
-        <v>0.07245190467771187</v>
+        <v>1854.7687597494239</v>
+      </c>
+      <c r="AA132" s="0">
+        <v>0.32976408236419724</v>
+      </c>
+      <c r="AB132" s="0">
+        <v>1211.0580413090534</v>
+      </c>
+      <c r="AC132" s="0">
+        <v>922.37331054951085</v>
+      </c>
+      <c r="AD132" s="0">
+        <v>54.936090351562505</v>
       </c>
     </row>
     <row r="133">
@@ -10567,16 +12167,28 @@
         <v>-0.00011718750000000097</v>
       </c>
       <c r="W133" s="0">
-        <v>0.30548099999999995</v>
+        <v>7820.3135999999986</v>
       </c>
       <c r="X133" s="0">
-        <v>384.55200000000013</v>
+        <v>9844531.200000003</v>
       </c>
       <c r="Y133" s="0">
-        <v>680.46452201700026</v>
+        <v>17419891.763635207</v>
       </c>
       <c r="Z133" s="0">
-        <v>0.06069375812314616</v>
+        <v>1553.7602079525416</v>
+      </c>
+      <c r="AA133" s="0">
+        <v>0.3300998650543232</v>
+      </c>
+      <c r="AB133" s="0">
+        <v>1220.489722497829</v>
+      </c>
+      <c r="AC133" s="0">
+        <v>926.68037911432953</v>
+      </c>
+      <c r="AD133" s="0">
+        <v>56.87261085937498</v>
       </c>
     </row>
     <row r="134">
@@ -10645,16 +12257,28 @@
         <v>-0.0001171874999999975</v>
       </c>
       <c r="W134" s="0">
-        <v>0.30456599999999995</v>
+        <v>7796.8895999999986</v>
       </c>
       <c r="X134" s="0">
-        <v>402.85300000000007</v>
+        <v>10313036.800000001</v>
       </c>
       <c r="Y134" s="0">
-        <v>727.80334976999984</v>
+        <v>18631765.754111994</v>
       </c>
       <c r="Z134" s="0">
-        <v>0.022727475170461562</v>
+        <v>581.82336436381593</v>
+      </c>
+      <c r="AA134" s="0">
+        <v>0.32906911552275503</v>
+      </c>
+      <c r="AB134" s="0">
+        <v>1223.3549952906687</v>
+      </c>
+      <c r="AC134" s="0">
+        <v>925.83121315149276</v>
+      </c>
+      <c r="AD134" s="0">
+        <v>56.973911562500014</v>
       </c>
     </row>
     <row r="135">
@@ -10723,16 +12347,28 @@
         <v>0.025859375</v>
       </c>
       <c r="W135" s="0">
-        <v>0.30731199999999997</v>
+        <v>7867.1871999999994</v>
       </c>
       <c r="X135" s="0">
-        <v>347.92500000000018</v>
+        <v>8906880.0000000037</v>
       </c>
       <c r="Y135" s="0">
-        <v>712.14767293500063</v>
+        <v>18230980.427136015</v>
       </c>
       <c r="Z135" s="0">
-        <v>0.020184037359716644</v>
+        <v>516.71135640874604</v>
+      </c>
+      <c r="AA135" s="0">
+        <v>0.33138865559597008</v>
+      </c>
+      <c r="AB135" s="0">
+        <v>1214.4073828463481</v>
+      </c>
+      <c r="AC135" s="0">
+        <v>927.24349777435418</v>
+      </c>
+      <c r="AD135" s="0">
+        <v>55.928759882812535</v>
       </c>
     </row>
     <row r="136">
@@ -10801,16 +12437,28 @@
         <v>0.025468749999999998</v>
       </c>
       <c r="W136" s="0">
-        <v>0.30700699999999997</v>
+        <v>7859.3791999999994</v>
       </c>
       <c r="X136" s="0">
-        <v>384.53800000000001</v>
+        <v>9844172.8000000007</v>
       </c>
       <c r="Y136" s="0">
-        <v>683.66710691499998</v>
+        <v>17501877.937023997</v>
       </c>
       <c r="Z136" s="0">
-        <v>0.020942531019178597</v>
+        <v>536.12879409097206</v>
+      </c>
+      <c r="AA136" s="0">
+        <v>0.33013352085207492</v>
+      </c>
+      <c r="AB136" s="0">
+        <v>1217.5534167365345</v>
+      </c>
+      <c r="AC136" s="0">
+        <v>927.28352515033782</v>
+      </c>
+      <c r="AD136" s="0">
+        <v>56.374972304687489</v>
       </c>
     </row>
     <row r="137">
@@ -10879,16 +12527,28 @@
         <v>-3.9062499999999167e-05</v>
       </c>
       <c r="W137" s="0">
-        <v>0.30975399999999997</v>
+        <v>7929.7023999999992</v>
       </c>
       <c r="X137" s="0">
-        <v>366.22600000000011</v>
+        <v>9375385.6000000034</v>
       </c>
       <c r="Y137" s="0">
-        <v>755.00282345999995</v>
+        <v>19328072.280575998</v>
       </c>
       <c r="Z137" s="0">
-        <v>0.00069563903064194521</v>
+        <v>17.808359184433797</v>
+      </c>
+      <c r="AA137" s="0">
+        <v>0.30931965218361557</v>
+      </c>
+      <c r="AB137" s="0">
+        <v>1282.1626439343377</v>
+      </c>
+      <c r="AC137" s="0">
+        <v>846.56971849638546</v>
+      </c>
+      <c r="AD137" s="0">
+        <v>82.288389062499988</v>
       </c>
     </row>
     <row r="138">
@@ -10957,16 +12617,28 @@
         <v>0.025312499999999995</v>
       </c>
       <c r="W138" s="0">
-        <v>0.31555199999999994</v>
+        <v>8078.131199999998</v>
       </c>
       <c r="X138" s="0">
-        <v>366.23600000000033</v>
+        <v>9375641.6000000089</v>
       </c>
       <c r="Y138" s="0">
-        <v>645.53378498800043</v>
+        <v>16525664.89569281</v>
       </c>
       <c r="Z138" s="0">
-        <v>0.011493266250460878</v>
+        <v>294.22761601179849</v>
+      </c>
+      <c r="AA138" s="0">
+        <v>0.30917843598529787</v>
+      </c>
+      <c r="AB138" s="0">
+        <v>1067.8099269913857</v>
+      </c>
+      <c r="AC138" s="0">
+        <v>747.54649695162391</v>
+      </c>
+      <c r="AD138" s="0">
+        <v>50.913116874999972</v>
       </c>
     </row>
     <row r="139">
@@ -11035,16 +12707,28 @@
         <v>0.025390625</v>
       </c>
       <c r="W139" s="0">
-        <v>0.30670100000000006</v>
+        <v>7851.5456000000013</v>
       </c>
       <c r="X139" s="0">
-        <v>366.23199999999997</v>
+        <v>9375539.1999999993</v>
       </c>
       <c r="Y139" s="0">
-        <v>655.63257050000038</v>
+        <v>16784193.804800011</v>
       </c>
       <c r="Z139" s="0">
-        <v>0.0057309972640560095</v>
+        <v>146.71352995983383</v>
+      </c>
+      <c r="AA139" s="0">
+        <v>0.3156682611812216</v>
+      </c>
+      <c r="AB139" s="0">
+        <v>1068.7382699937045</v>
+      </c>
+      <c r="AC139" s="0">
+        <v>763.22497260727175</v>
+      </c>
+      <c r="AD139" s="0">
+        <v>50.548144843750052</v>
       </c>
     </row>
     <row r="140">
@@ -11113,16 +12797,28 @@
         <v>0.025039062500000001</v>
       </c>
       <c r="W140" s="0">
-        <v>0.28625499999999998</v>
+        <v>7328.1279999999997</v>
       </c>
       <c r="X140" s="0">
-        <v>347.92699999999968</v>
+        <v>8906931.1999999918</v>
       </c>
       <c r="Y140" s="0">
-        <v>634.00747185599971</v>
+        <v>16230591.279513592</v>
       </c>
       <c r="Z140" s="0">
-        <v>0.01756240935165625</v>
+        <v>449.59767940239999</v>
+      </c>
+      <c r="AA140" s="0">
+        <v>0.31516249748346137</v>
+      </c>
+      <c r="AB140" s="0">
+        <v>1050.0864505229367</v>
+      </c>
+      <c r="AC140" s="0">
+        <v>748.90146239253522</v>
+      </c>
+      <c r="AD140" s="0">
+        <v>48.304562265625037</v>
       </c>
     </row>
     <row r="141">
@@ -11191,16 +12887,28 @@
         <v>0.025390625</v>
       </c>
       <c r="W141" s="0">
-        <v>0.28747599999999995</v>
+        <v>7359.3855999999987</v>
       </c>
       <c r="X141" s="0">
-        <v>366.23299999999972</v>
+        <v>9375564.7999999933</v>
       </c>
       <c r="Y141" s="0">
-        <v>644.94106126199995</v>
+        <v>16510491.168307198</v>
       </c>
       <c r="Z141" s="0">
-        <v>0.019267939781813511</v>
+        <v>493.25925841442586</v>
+      </c>
+      <c r="AA141" s="0">
+        <v>0.31039601608806039</v>
+      </c>
+      <c r="AB141" s="0">
+        <v>1071.6011824651061</v>
+      </c>
+      <c r="AC141" s="0">
+        <v>753.41654714796266</v>
+      </c>
+      <c r="AD141" s="0">
+        <v>50.590410078124982</v>
       </c>
     </row>
     <row r="142">
@@ -11269,16 +12977,28 @@
         <v>-7.8124999999998335e-05</v>
       </c>
       <c r="W142" s="0">
-        <v>0.29540999999999995</v>
+        <v>7562.4959999999983</v>
       </c>
       <c r="X142" s="0">
-        <v>402.84699999999998</v>
+        <v>10312883.199999999</v>
       </c>
       <c r="Y142" s="0">
-        <v>639.15544587699992</v>
+        <v>16362379.414451197</v>
       </c>
       <c r="Z142" s="0">
-        <v>0.16362607624492459</v>
+        <v>4188.8275518700693</v>
+      </c>
+      <c r="AA142" s="0">
+        <v>0.30661433275053124</v>
+      </c>
+      <c r="AB142" s="0">
+        <v>1065.9982071243044</v>
+      </c>
+      <c r="AC142" s="0">
+        <v>739.39580011362898</v>
+      </c>
+      <c r="AD142" s="0">
+        <v>50.263529531250001</v>
       </c>
     </row>
     <row r="143">
@@ -11347,16 +13067,28 @@
         <v>0.025078125</v>
       </c>
       <c r="W143" s="0">
-        <v>0.30395499999999992</v>
+        <v>7781.2479999999978</v>
       </c>
       <c r="X143" s="0">
-        <v>366.23300000000017</v>
+        <v>9375564.8000000045</v>
       </c>
       <c r="Y143" s="0">
-        <v>662.23106811700018</v>
+        <v>16953115.343795203</v>
       </c>
       <c r="Z143" s="0">
-        <v>0.0098008269608397328</v>
+        <v>250.90117019749715</v>
+      </c>
+      <c r="AA143" s="0">
+        <v>0.3137463118716714</v>
+      </c>
+      <c r="AB143" s="0">
+        <v>1076.6699379813949</v>
+      </c>
+      <c r="AC143" s="0">
+        <v>763.82726837503003</v>
+      </c>
+      <c r="AD143" s="0">
+        <v>51.34061308593747</v>
       </c>
     </row>
     <row r="144">
@@ -11425,16 +13157,28 @@
         <v>0.025195312500000004</v>
       </c>
       <c r="W144" s="0">
-        <v>0.30456499999999997</v>
+        <v>7796.8639999999996</v>
       </c>
       <c r="X144" s="0">
-        <v>384.54299999999989</v>
+        <v>9844300.799999997</v>
       </c>
       <c r="Y144" s="0">
-        <v>660.46933675499986</v>
+        <v>16908015.020927995</v>
       </c>
       <c r="Z144" s="0">
-        <v>0.013567862268514723</v>
+        <v>347.33727407397691</v>
+      </c>
+      <c r="AA144" s="0">
+        <v>0.3137424305459377</v>
+      </c>
+      <c r="AB144" s="0">
+        <v>1064.9167789129015</v>
+      </c>
+      <c r="AC144" s="0">
+        <v>755.3554210078355</v>
+      </c>
+      <c r="AD144" s="0">
+        <v>49.496947578124967</v>
       </c>
     </row>
     <row r="145">
@@ -11503,16 +13247,28 @@
         <v>-0.0001171874999999975</v>
       </c>
       <c r="W145" s="0">
-        <v>0.28747600000000001</v>
+        <v>7359.3856000000005</v>
       </c>
       <c r="X145" s="0">
-        <v>366.23599999999988</v>
+        <v>9375641.5999999959</v>
       </c>
       <c r="Y145" s="0">
-        <v>693.73330657200017</v>
+        <v>17759572.648243204</v>
       </c>
       <c r="Z145" s="0">
-        <v>0.014501551450256455</v>
+        <v>371.23971712656527</v>
+      </c>
+      <c r="AA145" s="0">
+        <v>0.30976732195067941</v>
+      </c>
+      <c r="AB145" s="0">
+        <v>1067.6619783105534</v>
+      </c>
+      <c r="AC145" s="0">
+        <v>748.70015124742963</v>
+      </c>
+      <c r="AD145" s="0">
+        <v>50.417566054687441</v>
       </c>
     </row>
     <row r="146">
@@ -11581,16 +13337,28 @@
         <v>-7.8124999999998335e-05</v>
       </c>
       <c r="W146" s="0">
-        <v>0.31250000000000006</v>
+        <v>8000.0000000000009</v>
       </c>
       <c r="X146" s="0">
-        <v>366.23700000000008</v>
+        <v>9375667.2000000011</v>
       </c>
       <c r="Y146" s="0">
-        <v>629.09889157599969</v>
+        <v>16104931.624345591</v>
       </c>
       <c r="Z146" s="0">
-        <v>0.0087039991488844972</v>
+        <v>222.82237821144312</v>
+      </c>
+      <c r="AA146" s="0">
+        <v>0.31298881509578236</v>
+      </c>
+      <c r="AB146" s="0">
+        <v>1079.2879672109025</v>
+      </c>
+      <c r="AC146" s="0">
+        <v>763.01444826987597</v>
+      </c>
+      <c r="AD146" s="0">
+        <v>51.406248671874984</v>
       </c>
     </row>
     <row r="147">
@@ -11659,16 +13427,28 @@
         <v>0.025078125</v>
       </c>
       <c r="W147" s="0">
-        <v>0.31372100000000003</v>
+        <v>8031.2576000000008</v>
       </c>
       <c r="X147" s="0">
-        <v>384.53299999999979</v>
+        <v>9844044.7999999952</v>
       </c>
       <c r="Y147" s="0">
-        <v>700.89633763799998</v>
+        <v>17942946.243532799</v>
       </c>
       <c r="Z147" s="0">
-        <v>0.018554812685121023</v>
+        <v>475.00320473909818</v>
+      </c>
+      <c r="AA147" s="0">
+        <v>0.30870358557172911</v>
+      </c>
+      <c r="AB147" s="0">
+        <v>1054.3478318109655</v>
+      </c>
+      <c r="AC147" s="0">
+        <v>736.98338776607943</v>
+      </c>
+      <c r="AD147" s="0">
+        <v>47.919085664062457</v>
       </c>
     </row>
     <row r="148">
@@ -11737,16 +13517,28 @@
         <v>-7.8125000000001804e-05</v>
       </c>
       <c r="W148" s="0">
-        <v>0.28625499999999993</v>
+        <v>7328.1279999999979</v>
       </c>
       <c r="X148" s="0">
-        <v>366.22300000000007</v>
+        <v>9375308.8000000007</v>
       </c>
       <c r="Y148" s="0">
-        <v>639.47901014399986</v>
+        <v>16370662.659686396</v>
       </c>
       <c r="Z148" s="0">
-        <v>0.059258741832732921</v>
+        <v>1517.0237909179627</v>
+      </c>
+      <c r="AA148" s="0">
+        <v>0.31566080278590281</v>
+      </c>
+      <c r="AB148" s="0">
+        <v>1057.2001079007841</v>
+      </c>
+      <c r="AC148" s="0">
+        <v>756.12961479051557</v>
+      </c>
+      <c r="AD148" s="0">
+        <v>48.27186449218749</v>
       </c>
     </row>
     <row r="149">
@@ -11815,16 +13607,28 @@
         <v>0.025195312500000004</v>
       </c>
       <c r="W149" s="0">
-        <v>0.319519</v>
+        <v>8179.6863999999996</v>
       </c>
       <c r="X149" s="0">
-        <v>347.92699999999968</v>
+        <v>8906931.1999999918</v>
       </c>
       <c r="Y149" s="0">
-        <v>631.9134256079999</v>
+        <v>16176983.695564797</v>
       </c>
       <c r="Z149" s="0">
-        <v>0.00970230820100558</v>
+        <v>248.37908994574283</v>
+      </c>
+      <c r="AA149" s="0">
+        <v>0.31014852837776746</v>
+      </c>
+      <c r="AB149" s="0">
+        <v>1055.7749065417192</v>
+      </c>
+      <c r="AC149" s="0">
+        <v>744.39698871138353</v>
+      </c>
+      <c r="AD149" s="0">
+        <v>48.563488632812508</v>
       </c>
     </row>
     <row r="150">
@@ -11893,16 +13697,28 @@
         <v>0.025234374999999996</v>
       </c>
       <c r="W150" s="0">
-        <v>0.32440200000000002</v>
+        <v>8304.6912000000011</v>
       </c>
       <c r="X150" s="0">
-        <v>366.23900000000003</v>
+        <v>9375718.4000000004</v>
       </c>
       <c r="Y150" s="0">
-        <v>624.53860832000009</v>
+        <v>15988188.372992001</v>
       </c>
       <c r="Z150" s="0">
-        <v>0.011064309563483936</v>
+        <v>283.24632482518876</v>
+      </c>
+      <c r="AA150" s="0">
+        <v>0.3167246769044943</v>
+      </c>
+      <c r="AB150" s="0">
+        <v>1064.5414695854595</v>
+      </c>
+      <c r="AC150" s="0">
+        <v>760.05817353478778</v>
+      </c>
+      <c r="AD150" s="0">
+        <v>49.742718164062488</v>
       </c>
     </row>
     <row r="151">
@@ -11971,16 +13787,28 @@
         <v>0.025039062500000001</v>
       </c>
       <c r="W151" s="0">
-        <v>0.30365000000000003</v>
+        <v>7773.4400000000005</v>
       </c>
       <c r="X151" s="0">
-        <v>384.52800000000002</v>
+        <v>9843916.8000000007</v>
       </c>
       <c r="Y151" s="0">
-        <v>629.70787661899976</v>
+        <v>16120521.641446393</v>
       </c>
       <c r="Z151" s="0">
-        <v>0.023014836393544812</v>
+        <v>589.17981167474716</v>
+      </c>
+      <c r="AA151" s="0">
+        <v>0.31040197060830682</v>
+      </c>
+      <c r="AB151" s="0">
+        <v>1053.8485629697363</v>
+      </c>
+      <c r="AC151" s="0">
+        <v>739.26444813492856</v>
+      </c>
+      <c r="AD151" s="0">
+        <v>48.424238789062521</v>
       </c>
     </row>
     <row r="152">
@@ -12049,16 +13877,28 @@
         <v>0.024960937500000002</v>
       </c>
       <c r="W152" s="0">
-        <v>0.28656000000000004</v>
+        <v>7335.9360000000006</v>
       </c>
       <c r="X152" s="0">
-        <v>366.23799999999983</v>
+        <v>9375692.7999999952</v>
       </c>
       <c r="Y152" s="0">
-        <v>766.14324562799948</v>
+        <v>19613267.088076785</v>
       </c>
       <c r="Z152" s="0">
-        <v>0.011505649862313958</v>
+        <v>294.54463647523733</v>
+      </c>
+      <c r="AA152" s="0">
+        <v>0.36492811428476246</v>
+      </c>
+      <c r="AB152" s="0">
+        <v>1563.161592117712</v>
+      </c>
+      <c r="AC152" s="0">
+        <v>1343.2289055534113</v>
+      </c>
+      <c r="AD152" s="0">
+        <v>70.98294964843754</v>
       </c>
     </row>
     <row r="153">
@@ -12127,16 +13967,28 @@
         <v>-0.00058593750000000139</v>
       </c>
       <c r="W153" s="0">
-        <v>0.29266300000000006</v>
+        <v>7492.1728000000012</v>
       </c>
       <c r="X153" s="0">
-        <v>347.92700000000013</v>
+        <v>8906931.200000003</v>
       </c>
       <c r="Y153" s="0">
-        <v>736.87725172399996</v>
+        <v>18864057.644134399</v>
       </c>
       <c r="Z153" s="0">
-        <v>0.075273378762968218</v>
+        <v>1926.9984963319864</v>
+      </c>
+      <c r="AA153" s="0">
+        <v>0.36216653254486003</v>
+      </c>
+      <c r="AB153" s="0">
+        <v>1554.6185726828708</v>
+      </c>
+      <c r="AC153" s="0">
+        <v>1331.5556995899983</v>
+      </c>
+      <c r="AD153" s="0">
+        <v>69.369934179687561</v>
       </c>
     </row>
     <row r="154">
@@ -12205,16 +14057,28 @@
         <v>0.025468749999999998</v>
       </c>
       <c r="W154" s="0">
-        <v>0.30364999999999998</v>
+        <v>7773.4399999999996</v>
       </c>
       <c r="X154" s="0">
-        <v>366.23099999999977</v>
+        <v>9375513.599999994</v>
       </c>
       <c r="Y154" s="0">
-        <v>775.48225824000019</v>
+        <v>19852345.810944006</v>
       </c>
       <c r="Z154" s="0">
-        <v>0.011158934590394005</v>
+        <v>285.66872551408653</v>
+      </c>
+      <c r="AA154" s="0">
+        <v>0.36294851906830328</v>
+      </c>
+      <c r="AB154" s="0">
+        <v>1565.2838472890062</v>
+      </c>
+      <c r="AC154" s="0">
+        <v>1331.9699685479211</v>
+      </c>
+      <c r="AD154" s="0">
+        <v>70.906731601562512</v>
       </c>
     </row>
     <row r="155">
@@ -12283,16 +14147,28 @@
         <v>0.025507812500000004</v>
       </c>
       <c r="W155" s="0">
-        <v>0.28533900000000001</v>
+        <v>7304.6783999999998</v>
       </c>
       <c r="X155" s="0">
-        <v>366.23699999999963</v>
+        <v>9375667.1999999899</v>
       </c>
       <c r="Y155" s="0">
-        <v>771.82706610600007</v>
+        <v>19758772.892313603</v>
       </c>
       <c r="Z155" s="0">
-        <v>0.012135875055505055</v>
+        <v>310.67840142092939</v>
+      </c>
+      <c r="AA155" s="0">
+        <v>0.36533445727871677</v>
+      </c>
+      <c r="AB155" s="0">
+        <v>1563.7664546396354</v>
+      </c>
+      <c r="AC155" s="0">
+        <v>1342.7931214832586</v>
+      </c>
+      <c r="AD155" s="0">
+        <v>71.216183124999986</v>
       </c>
     </row>
     <row r="156">
@@ -12361,16 +14237,28 @@
         <v>-0.00062500000000000056</v>
       </c>
       <c r="W156" s="0">
-        <v>0.28686499999999993</v>
+        <v>7343.7439999999979</v>
       </c>
       <c r="X156" s="0">
-        <v>366.21600000000001</v>
+        <v>9375129.5999999996</v>
       </c>
       <c r="Y156" s="0">
-        <v>738.23681899200028</v>
+        <v>18898862.566195209</v>
       </c>
       <c r="Z156" s="0">
-        <v>0.013255068991891902</v>
+        <v>339.32976619243266</v>
+      </c>
+      <c r="AA156" s="0">
+        <v>0.36204215213596519</v>
+      </c>
+      <c r="AB156" s="0">
+        <v>1567.0829175160573</v>
+      </c>
+      <c r="AC156" s="0">
+        <v>1341.4480094386522</v>
+      </c>
+      <c r="AD156" s="0">
+        <v>71.000799296875002</v>
       </c>
     </row>
     <row r="157">
@@ -12439,16 +14327,28 @@
         <v>0.025585937500000003</v>
       </c>
       <c r="W157" s="0">
-        <v>0.28076200000000007</v>
+        <v>7187.5072000000018</v>
       </c>
       <c r="X157" s="0">
-        <v>366.25099999999884</v>
+        <v>9376025.5999999698</v>
       </c>
       <c r="Y157" s="0">
-        <v>770.73513108400039</v>
+        <v>19730819.355750408</v>
       </c>
       <c r="Z157" s="0">
-        <v>0.0099726669859082785</v>
+        <v>255.30027483925193</v>
+      </c>
+      <c r="AA157" s="0">
+        <v>0.35894612093316397</v>
+      </c>
+      <c r="AB157" s="0">
+        <v>1550.5641211954778</v>
+      </c>
+      <c r="AC157" s="0">
+        <v>1324.5716895750643</v>
+      </c>
+      <c r="AD157" s="0">
+        <v>69.781352734375005</v>
       </c>
     </row>
     <row r="158">
@@ -12517,16 +14417,28 @@
         <v>-0.00011718750000000097</v>
       </c>
       <c r="W158" s="0">
-        <v>0.29083300000000006</v>
+        <v>7445.3248000000012</v>
       </c>
       <c r="X158" s="0">
-        <v>366.2510000000002</v>
+        <v>9376025.6000000052</v>
       </c>
       <c r="Y158" s="0">
-        <v>789.20617362999974</v>
+        <v>20203678.044927992</v>
       </c>
       <c r="Z158" s="0">
-        <v>0.012765750920770784</v>
+        <v>326.80322357173208</v>
+      </c>
+      <c r="AA158" s="0">
+        <v>0.36073514329878043</v>
+      </c>
+      <c r="AB158" s="0">
+        <v>1566.8918923238286</v>
+      </c>
+      <c r="AC158" s="0">
+        <v>1337.877073569502</v>
+      </c>
+      <c r="AD158" s="0">
+        <v>70.93674648437505</v>
       </c>
     </row>
     <row r="159">
@@ -12595,16 +14507,28 @@
         <v>-0.0001171874999999975</v>
       </c>
       <c r="W159" s="0">
-        <v>0.29388500000000006</v>
+        <v>7523.456000000001</v>
       </c>
       <c r="X159" s="0">
-        <v>384.54800000000023</v>
+        <v>9844428.8000000063</v>
       </c>
       <c r="Y159" s="0">
-        <v>802.34633303999999</v>
+        <v>20540066.125824001</v>
       </c>
       <c r="Z159" s="0">
-        <v>0.076387534867366241</v>
+        <v>1955.5208926045757</v>
+      </c>
+      <c r="AA159" s="0">
+        <v>0.36269391465345707</v>
+      </c>
+      <c r="AB159" s="0">
+        <v>1567.3287845371758</v>
+      </c>
+      <c r="AC159" s="0">
+        <v>1343.9237836930449</v>
+      </c>
+      <c r="AD159" s="0">
+        <v>70.615820390625018</v>
       </c>
     </row>
     <row r="160">
@@ -12673,16 +14597,28 @@
         <v>0.025273437499999999</v>
       </c>
       <c r="W160" s="0">
-        <v>0.27130100000000001</v>
+        <v>6945.3056000000006</v>
       </c>
       <c r="X160" s="0">
-        <v>384.54600000000028</v>
+        <v>9844377.6000000071</v>
       </c>
       <c r="Y160" s="0">
-        <v>771.56380865700066</v>
+        <v>19752033.501619216</v>
       </c>
       <c r="Z160" s="0">
-        <v>0.057041211523089233</v>
+        <v>1460.2550149910844</v>
+      </c>
+      <c r="AA160" s="0">
+        <v>0.35948162610754014</v>
+      </c>
+      <c r="AB160" s="0">
+        <v>1568.0866603796605</v>
+      </c>
+      <c r="AC160" s="0">
+        <v>1331.687091121493</v>
+      </c>
+      <c r="AD160" s="0">
+        <v>71.416085351562529</v>
       </c>
     </row>
     <row r="161">
@@ -12751,16 +14687,28 @@
         <v>-0.0024218750000000004</v>
       </c>
       <c r="W161" s="0">
-        <v>0.27038599999999996</v>
+        <v>6921.8815999999988</v>
       </c>
       <c r="X161" s="0">
-        <v>384.54200000000014</v>
+        <v>9844275.200000003</v>
       </c>
       <c r="Y161" s="0">
-        <v>740.95682859399994</v>
+        <v>18968494.812006399</v>
       </c>
       <c r="Z161" s="0">
         <v>65535</v>
+      </c>
+      <c r="AA161" s="0">
+        <v>0.35968061545986169</v>
+      </c>
+      <c r="AB161" s="0">
+        <v>1543.5635108809315</v>
+      </c>
+      <c r="AC161" s="0">
+        <v>1317.7855755165463</v>
+      </c>
+      <c r="AD161" s="0">
+        <v>69.428385507812479</v>
       </c>
     </row>
     <row r="162">
@@ -12829,16 +14777,28 @@
         <v>0.025000000000000001</v>
       </c>
       <c r="W162" s="0">
-        <v>0.27465800000000001</v>
+        <v>7031.2448000000004</v>
       </c>
       <c r="X162" s="0">
-        <v>366.2320000000002</v>
+        <v>9375539.2000000048</v>
       </c>
       <c r="Y162" s="0">
-        <v>747.68902880799988</v>
+        <v>19140839.137484796</v>
       </c>
       <c r="Z162" s="0">
-        <v>0.024538573411139877</v>
+        <v>628.18747932518079</v>
+      </c>
+      <c r="AA162" s="0">
+        <v>0.36162682598456392</v>
+      </c>
+      <c r="AB162" s="0">
+        <v>1565.4445948785508</v>
+      </c>
+      <c r="AC162" s="0">
+        <v>1336.4789620111956</v>
+      </c>
+      <c r="AD162" s="0">
+        <v>70.733766367187499</v>
       </c>
     </row>
     <row r="163">
@@ -12907,16 +14867,28 @@
         <v>0.025546875</v>
       </c>
       <c r="W163" s="0">
-        <v>0.29327400000000003</v>
+        <v>7507.8144000000011</v>
       </c>
       <c r="X163" s="0">
-        <v>347.91800000000012</v>
+        <v>8906700.8000000026</v>
       </c>
       <c r="Y163" s="0">
-        <v>759.20126282400088</v>
+        <v>19435552.328294422</v>
       </c>
       <c r="Z163" s="0">
-        <v>0.018403095524141759</v>
+        <v>471.11924541802904</v>
+      </c>
+      <c r="AA163" s="0">
+        <v>0.3602897426447616</v>
+      </c>
+      <c r="AB163" s="0">
+        <v>1553.2981240255026</v>
+      </c>
+      <c r="AC163" s="0">
+        <v>1327.3412940284711</v>
+      </c>
+      <c r="AD163" s="0">
+        <v>69.18698167968742</v>
       </c>
     </row>
     <row r="164">
@@ -12985,16 +14957,28 @@
         <v>-0.00062500000000000056</v>
       </c>
       <c r="W164" s="0">
-        <v>0.27709899999999998</v>
+        <v>7093.7343999999994</v>
       </c>
       <c r="X164" s="0">
-        <v>476.09900000000016</v>
+        <v>12188134.400000004</v>
       </c>
       <c r="Y164" s="0">
-        <v>856.48199940899985</v>
+        <v>21925939.184870396</v>
       </c>
       <c r="Z164" s="0">
-        <v>0.016201918937447945</v>
+        <v>414.76912479866741</v>
+      </c>
+      <c r="AA164" s="0">
+        <v>0.3586470255767773</v>
+      </c>
+      <c r="AB164" s="0">
+        <v>1554.9940840159331</v>
+      </c>
+      <c r="AC164" s="0">
+        <v>1322.4598161219619</v>
+      </c>
+      <c r="AD164" s="0">
+        <v>70.142129609375033</v>
       </c>
     </row>
     <row r="165">
@@ -13063,16 +15047,28 @@
         <v>0.025429687500000006</v>
       </c>
       <c r="W165" s="0">
-        <v>0.29083300000000001</v>
+        <v>7445.3248000000003</v>
       </c>
       <c r="X165" s="0">
-        <v>366.23599999999988</v>
+        <v>9375641.5999999959</v>
       </c>
       <c r="Y165" s="0">
-        <v>736.23874284600015</v>
+        <v>18847711.816857602</v>
       </c>
       <c r="Z165" s="0">
-        <v>0.072225844156897881</v>
+        <v>1848.9816104165857</v>
+      </c>
+      <c r="AA165" s="0">
+        <v>0.35869108308239789</v>
+      </c>
+      <c r="AB165" s="0">
+        <v>1551.6215213182027</v>
+      </c>
+      <c r="AC165" s="0">
+        <v>1317.7029380928298</v>
+      </c>
+      <c r="AD165" s="0">
+        <v>69.86034824218747</v>
       </c>
     </row>
     <row r="166">
@@ -13141,16 +15137,28 @@
         <v>0.025468750000000002</v>
       </c>
       <c r="W166" s="0">
-        <v>0.29510499999999995</v>
+        <v>7554.6879999999983</v>
       </c>
       <c r="X166" s="0">
-        <v>384.55000000000018</v>
+        <v>9844480.0000000037</v>
       </c>
       <c r="Y166" s="0">
-        <v>792.68024440500039</v>
+        <v>20292614.256768011</v>
       </c>
       <c r="Z166" s="0">
-        <v>0.071867784102531543</v>
+        <v>1839.8152730248075</v>
+      </c>
+      <c r="AA166" s="0">
+        <v>0.36236646760288749</v>
+      </c>
+      <c r="AB166" s="0">
+        <v>1554.7562002057034</v>
+      </c>
+      <c r="AC166" s="0">
+        <v>1330.1239327170633</v>
+      </c>
+      <c r="AD166" s="0">
+        <v>69.956092304687516</v>
       </c>
     </row>
     <row r="167">
@@ -13219,16 +15227,28 @@
         <v>0.025273437499999999</v>
       </c>
       <c r="W167" s="0">
-        <v>0.28472899999999995</v>
+        <v>7289.0623999999989</v>
       </c>
       <c r="X167" s="0">
-        <v>384.53599999999983</v>
+        <v>9844121.5999999959</v>
       </c>
       <c r="Y167" s="0">
-        <v>802.57997476100081</v>
+        <v>20546047.35388162</v>
       </c>
       <c r="Z167" s="0">
-        <v>0.006537762746350863</v>
+        <v>167.36672630658208</v>
+      </c>
+      <c r="AA167" s="0">
+        <v>0.35370250401377579</v>
+      </c>
+      <c r="AB167" s="0">
+        <v>1555.2844123809703</v>
+      </c>
+      <c r="AC167" s="0">
+        <v>1319.9085755444339</v>
+      </c>
+      <c r="AD167" s="0">
+        <v>71.103969531249973</v>
       </c>
     </row>
     <row r="168">
@@ -13297,16 +15317,28 @@
         <v>-0.00015624999999999667</v>
       </c>
       <c r="W168" s="0">
-        <v>0.27648899999999998</v>
+        <v>7078.1183999999994</v>
       </c>
       <c r="X168" s="0">
-        <v>384.54500000000007</v>
+        <v>9844352.0000000019</v>
       </c>
       <c r="Y168" s="0">
-        <v>748.56491840099989</v>
+        <v>19163261.911065597</v>
       </c>
       <c r="Z168" s="0">
-        <v>0.018642596251451017</v>
+        <v>477.250464037146</v>
+      </c>
+      <c r="AA168" s="0">
+        <v>0.34616503773792373</v>
+      </c>
+      <c r="AB168" s="0">
+        <v>1536.14251825206</v>
+      </c>
+      <c r="AC168" s="0">
+        <v>1281.1322291494307</v>
+      </c>
+      <c r="AD168" s="0">
+        <v>68.23063558593752</v>
       </c>
     </row>
     <row r="169">
@@ -13375,16 +15407,28 @@
         <v>0.024960937500000002</v>
       </c>
       <c r="W169" s="0">
-        <v>0.28076199999999996</v>
+        <v>7187.5071999999991</v>
       </c>
       <c r="X169" s="0">
-        <v>439.47600000000011</v>
+        <v>11250585.600000003</v>
       </c>
       <c r="Y169" s="0">
-        <v>780.62105847899966</v>
+        <v>19983899.09706239</v>
       </c>
       <c r="Z169" s="0">
-        <v>0.011817389949868078</v>
+        <v>302.52518271662279</v>
+      </c>
+      <c r="AA169" s="0">
+        <v>0.3490702674889809</v>
+      </c>
+      <c r="AB169" s="0">
+        <v>1546.5255250896671</v>
+      </c>
+      <c r="AC169" s="0">
+        <v>1297.0485896103469</v>
+      </c>
+      <c r="AD169" s="0">
+        <v>69.418888671875024</v>
       </c>
     </row>
     <row r="170">
@@ -13453,16 +15497,28 @@
         <v>-0.00058593749999999792</v>
       </c>
       <c r="W170" s="0">
-        <v>0.28625499999999998</v>
+        <v>7328.1279999999997</v>
       </c>
       <c r="X170" s="0">
-        <v>347.9369999999999</v>
+        <v>8907187.1999999974</v>
       </c>
       <c r="Y170" s="0">
-        <v>775.56799715199941</v>
+        <v>19854540.727091186</v>
       </c>
       <c r="Z170" s="0">
-        <v>0.024579577834804262</v>
+        <v>629.23719257098912</v>
+      </c>
+      <c r="AA170" s="0">
+        <v>0.35042987460792585</v>
+      </c>
+      <c r="AB170" s="0">
+        <v>1545.6572461026035</v>
+      </c>
+      <c r="AC170" s="0">
+        <v>1304.6563362068043</v>
+      </c>
+      <c r="AD170" s="0">
+        <v>69.622886250000022</v>
       </c>
     </row>
     <row r="171">
@@ -13531,16 +15587,28 @@
         <v>0.025898437500000003</v>
       </c>
       <c r="W171" s="0">
-        <v>0.28717000000000004</v>
+        <v>7351.5520000000006</v>
       </c>
       <c r="X171" s="0">
-        <v>384.55099999999948</v>
+        <v>9844505.5999999866</v>
       </c>
       <c r="Y171" s="0">
-        <v>798.80456352800002</v>
+        <v>20449396.8263168</v>
       </c>
       <c r="Z171" s="0">
-        <v>0.021521417450744481</v>
+        <v>550.94828673905874</v>
+      </c>
+      <c r="AA171" s="0">
+        <v>0.35155879925656619</v>
+      </c>
+      <c r="AB171" s="0">
+        <v>1549.0642004489066</v>
+      </c>
+      <c r="AC171" s="0">
+        <v>1313.2927916604451</v>
+      </c>
+      <c r="AD171" s="0">
+        <v>70.144552539062474</v>
       </c>
     </row>
     <row r="172">
@@ -13609,16 +15677,28 @@
         <v>0.024921875000000003</v>
       </c>
       <c r="W172" s="0">
-        <v>0.28503400000000001</v>
+        <v>7296.8703999999998</v>
       </c>
       <c r="X172" s="0">
-        <v>366.23599999999988</v>
+        <v>9375641.5999999959</v>
       </c>
       <c r="Y172" s="0">
-        <v>811.41687603399987</v>
+        <v>20772272.026470397</v>
       </c>
       <c r="Z172" s="0">
-        <v>0.03512889371997719</v>
+        <v>899.29967923141601</v>
+      </c>
+      <c r="AA172" s="0">
+        <v>0.35519247126379944</v>
+      </c>
+      <c r="AB172" s="0">
+        <v>1548.3794434881329</v>
+      </c>
+      <c r="AC172" s="0">
+        <v>1320.7421962515559</v>
+      </c>
+      <c r="AD172" s="0">
+        <v>70.248104140624989</v>
       </c>
     </row>
     <row r="173">
@@ -13687,16 +15767,28 @@
         <v>0.024960937500000002</v>
       </c>
       <c r="W173" s="0">
-        <v>0.27313200000000004</v>
+        <v>6992.1792000000005</v>
       </c>
       <c r="X173" s="0">
-        <v>402.86999999999989</v>
+        <v>10313471.999999996</v>
       </c>
       <c r="Y173" s="0">
-        <v>856.08216733999961</v>
+        <v>21915703.483903989</v>
       </c>
       <c r="Z173" s="0">
-        <v>0.018712476122874695</v>
+        <v>479.03938874559219</v>
+      </c>
+      <c r="AA173" s="0">
+        <v>0.35813438566388167</v>
+      </c>
+      <c r="AB173" s="0">
+        <v>1552.187097935775</v>
+      </c>
+      <c r="AC173" s="0">
+        <v>1330.6051830323722</v>
+      </c>
+      <c r="AD173" s="0">
+        <v>70.285336406250025</v>
       </c>
     </row>
     <row r="174">
@@ -13765,16 +15857,28 @@
         <v>0.025000000000000001</v>
       </c>
       <c r="W174" s="0">
-        <v>0.28625500000000004</v>
+        <v>7328.1280000000006</v>
       </c>
       <c r="X174" s="0">
-        <v>366.23000000000002</v>
+        <v>9375488</v>
       </c>
       <c r="Y174" s="0">
-        <v>736.07882939400042</v>
+        <v>18843618.032486409</v>
       </c>
       <c r="Z174" s="0">
-        <v>0.013074751575192237</v>
+        <v>334.71364032492124</v>
+      </c>
+      <c r="AA174" s="0">
+        <v>0.35396524513747241</v>
+      </c>
+      <c r="AB174" s="0">
+        <v>1544.5687469673071</v>
+      </c>
+      <c r="AC174" s="0">
+        <v>1311.9736959914214</v>
+      </c>
+      <c r="AD174" s="0">
+        <v>69.449333046874983</v>
       </c>
     </row>
     <row r="175">
@@ -13843,16 +15947,28 @@
         <v>-0.00062500000000000056</v>
       </c>
       <c r="W175" s="0">
-        <v>0.27862600000000004</v>
+        <v>7132.825600000001</v>
       </c>
       <c r="X175" s="0">
-        <v>402.85599999999977</v>
+        <v>10313113.599999994</v>
       </c>
       <c r="Y175" s="0">
-        <v>750.01436617799936</v>
+        <v>19200367.774156783</v>
       </c>
       <c r="Z175" s="0">
-        <v>0.011951520628348585</v>
+        <v>305.95892808572376</v>
+      </c>
+      <c r="AA175" s="0">
+        <v>0.3497526530333489</v>
+      </c>
+      <c r="AB175" s="0">
+        <v>1548.0636174686483</v>
+      </c>
+      <c r="AC175" s="0">
+        <v>1303.8989459614263</v>
+      </c>
+      <c r="AD175" s="0">
+        <v>69.961299687499974</v>
       </c>
     </row>
     <row r="176">
@@ -13921,16 +16037,28 @@
         <v>-0.00058593750000000139</v>
       </c>
       <c r="W176" s="0">
-        <v>0.28045700000000001</v>
+        <v>7179.6992</v>
       </c>
       <c r="X176" s="0">
-        <v>366.23300000000017</v>
+        <v>9375564.8000000045</v>
       </c>
       <c r="Y176" s="0">
-        <v>749.9308855940003</v>
+        <v>19198230.671206407</v>
       </c>
       <c r="Z176" s="0">
-        <v>0.017980454172642199</v>
+        <v>460.29962681964031</v>
+      </c>
+      <c r="AA176" s="0">
+        <v>0.35314795631570317</v>
+      </c>
+      <c r="AB176" s="0">
+        <v>1555.8266617601982</v>
+      </c>
+      <c r="AC176" s="0">
+        <v>1320.8539621277623</v>
+      </c>
+      <c r="AD176" s="0">
+        <v>70.613683085937481</v>
       </c>
     </row>
     <row r="177">
@@ -13999,16 +16127,28 @@
         <v>0.025078125</v>
       </c>
       <c r="W177" s="0">
-        <v>0.29052700000000004</v>
+        <v>7437.4912000000004</v>
       </c>
       <c r="X177" s="0">
-        <v>366.22500000000014</v>
+        <v>9375360.0000000037</v>
       </c>
       <c r="Y177" s="0">
-        <v>775.63654182999926</v>
+        <v>19856295.470847979</v>
       </c>
       <c r="Z177" s="0">
-        <v>0.010324959983939088</v>
+        <v>264.31897558884066</v>
+      </c>
+      <c r="AA177" s="0">
+        <v>0.34865815854865256</v>
+      </c>
+      <c r="AB177" s="0">
+        <v>1540.612567706442</v>
+      </c>
+      <c r="AC177" s="0">
+        <v>1293.7354542397977</v>
+      </c>
+      <c r="AD177" s="0">
+        <v>69.232091718750027</v>
       </c>
     </row>
     <row r="178">
@@ -14077,16 +16217,28 @@
         <v>0.025078125</v>
       </c>
       <c r="W178" s="0">
-        <v>0.28686600000000007</v>
+        <v>7343.7696000000014</v>
       </c>
       <c r="X178" s="0">
-        <v>402.8449999999998</v>
+        <v>10312831.999999994</v>
       </c>
       <c r="Y178" s="0">
-        <v>763.94262415399999</v>
+        <v>19556931.178342398</v>
       </c>
       <c r="Z178" s="0">
-        <v>0.018054627764152405</v>
+        <v>462.19847076230155</v>
+      </c>
+      <c r="AA178" s="0">
+        <v>0.35045560448298357</v>
+      </c>
+      <c r="AB178" s="0">
+        <v>1553.5207637821641</v>
+      </c>
+      <c r="AC178" s="0">
+        <v>1310.0596068002271</v>
+      </c>
+      <c r="AD178" s="0">
+        <v>70.970619140624947</v>
       </c>
     </row>
     <row r="179">
@@ -14155,16 +16307,28 @@
         <v>-0.00058593749999999445</v>
       </c>
       <c r="W179" s="0">
-        <v>0.27557399999999999</v>
+        <v>7054.6943999999994</v>
       </c>
       <c r="X179" s="0">
-        <v>384.55400000000009</v>
+        <v>9844582.4000000022</v>
       </c>
       <c r="Y179" s="0">
-        <v>752.43618235199983</v>
+        <v>19262366.268211197</v>
       </c>
       <c r="Z179" s="0">
-        <v>0.1892171906001259</v>
+        <v>4843.9600793632226</v>
+      </c>
+      <c r="AA179" s="0">
+        <v>0.34904364435197616</v>
+      </c>
+      <c r="AB179" s="0">
+        <v>1553.377563840744</v>
+      </c>
+      <c r="AC179" s="0">
+        <v>1306.4186582815378</v>
+      </c>
+      <c r="AD179" s="0">
+        <v>70.181673749999987</v>
       </c>
     </row>
     <row r="180">
@@ -14233,16 +16397,28 @@
         <v>0.024960937500000002</v>
       </c>
       <c r="W180" s="0">
-        <v>0.28137200000000001</v>
+        <v>7203.1232</v>
       </c>
       <c r="X180" s="0">
-        <v>347.94000000000051</v>
+        <v>8907264.000000013</v>
       </c>
       <c r="Y180" s="0">
-        <v>713.31033940700036</v>
+        <v>18260744.688819207</v>
       </c>
       <c r="Z180" s="0">
-        <v>0.024100934177414428</v>
+        <v>616.9839149418093</v>
+      </c>
+      <c r="AA180" s="0">
+        <v>0.34715158241767063</v>
+      </c>
+      <c r="AB180" s="0">
+        <v>1530.1863163833002</v>
+      </c>
+      <c r="AC180" s="0">
+        <v>1285.0689436879345</v>
+      </c>
+      <c r="AD180" s="0">
+        <v>68.31932472656257</v>
       </c>
     </row>
     <row r="181">
@@ -14311,16 +16487,28 @@
         <v>0.025039062500000001</v>
       </c>
       <c r="W181" s="0">
-        <v>0.27709900000000004</v>
+        <v>7093.7344000000012</v>
       </c>
       <c r="X181" s="0">
-        <v>384.54799999999977</v>
+        <v>9844428.7999999933</v>
       </c>
       <c r="Y181" s="0">
-        <v>773.46342153000023</v>
+        <v>19800663.591168005</v>
       </c>
       <c r="Z181" s="0">
-        <v>0.015779551548791664</v>
+        <v>403.95651964906659</v>
+      </c>
+      <c r="AA181" s="0">
+        <v>0.34621533115784786</v>
+      </c>
+      <c r="AB181" s="0">
+        <v>1545.0528753541982</v>
+      </c>
+      <c r="AC181" s="0">
+        <v>1290.2712965156713</v>
+      </c>
+      <c r="AD181" s="0">
+        <v>69.037097382812519</v>
       </c>
     </row>
     <row r="182">
@@ -14389,16 +16577,28 @@
         <v>0.024960937500000002</v>
       </c>
       <c r="W182" s="0">
-        <v>0.28533900000000001</v>
+        <v>7304.6783999999998</v>
       </c>
       <c r="X182" s="0">
-        <v>366.24699999999984</v>
+        <v>9375923.1999999955</v>
       </c>
       <c r="Y182" s="0">
-        <v>746.74724689599952</v>
+        <v>19116729.520537589</v>
       </c>
       <c r="Z182" s="0">
-        <v>0.019866601694951518</v>
+        <v>508.58500339075886</v>
+      </c>
+      <c r="AA182" s="0">
+        <v>0.34819787168070782</v>
+      </c>
+      <c r="AB182" s="0">
+        <v>1545.7260825894111</v>
+      </c>
+      <c r="AC182" s="0">
+        <v>1296.5520223657218</v>
+      </c>
+      <c r="AD182" s="0">
+        <v>69.221671640624976</v>
       </c>
     </row>
     <row r="183">
@@ -14467,16 +16667,28 @@
         <v>-0.00058593750000000139</v>
       </c>
       <c r="W183" s="0">
-        <v>0.29418900000000003</v>
+        <v>7531.2384000000011</v>
       </c>
       <c r="X183" s="0">
-        <v>384.54700000000003</v>
+        <v>9844403.2000000011</v>
       </c>
       <c r="Y183" s="0">
-        <v>741.48533350500065</v>
+        <v>18982024.537728015</v>
       </c>
       <c r="Z183" s="0">
-        <v>0.018387625657579645</v>
+        <v>470.72321683403891</v>
+      </c>
+      <c r="AA183" s="0">
+        <v>0.34471679538254374</v>
+      </c>
+      <c r="AB183" s="0">
+        <v>1543.4561757698009</v>
+      </c>
+      <c r="AC183" s="0">
+        <v>1285.3951356270888</v>
+      </c>
+      <c r="AD183" s="0">
+        <v>69.368760429687455</v>
       </c>
     </row>
     <row r="184">
@@ -14545,16 +16757,28 @@
         <v>0.025000000000000001</v>
       </c>
       <c r="W184" s="0">
-        <v>0.27130199999999999</v>
+        <v>6945.3311999999996</v>
       </c>
       <c r="X184" s="0">
-        <v>384.56000000000085</v>
+        <v>9844736.0000000224</v>
       </c>
       <c r="Y184" s="0">
-        <v>825.98197992600035</v>
+        <v>21145138.686105609</v>
       </c>
       <c r="Z184" s="0">
-        <v>0.068336906159658511</v>
+        <v>1749.4247976872578</v>
+      </c>
+      <c r="AA184" s="0">
+        <v>0.34160007619672</v>
+      </c>
+      <c r="AB184" s="0">
+        <v>1537.8004693742687</v>
+      </c>
+      <c r="AC184" s="0">
+        <v>1273.6696376449925</v>
+      </c>
+      <c r="AD184" s="0">
+        <v>68.817790234375011</v>
       </c>
     </row>
     <row r="185">
@@ -14623,16 +16847,28 @@
         <v>0.025039062500000001</v>
       </c>
       <c r="W185" s="0">
-        <v>0.26947000000000004</v>
+        <v>6898.4320000000007</v>
       </c>
       <c r="X185" s="0">
-        <v>366.2510000000002</v>
+        <v>9376025.6000000052</v>
       </c>
       <c r="Y185" s="0">
-        <v>737.15682072499976</v>
+        <v>18871214.610559992</v>
       </c>
       <c r="Z185" s="0">
-        <v>0.15366222706977226</v>
+        <v>3933.7530129861698</v>
+      </c>
+      <c r="AA185" s="0">
+        <v>0.34501871276421497</v>
+      </c>
+      <c r="AB185" s="0">
+        <v>1545.4007320420112</v>
+      </c>
+      <c r="AC185" s="0">
+        <v>1288.6443774910988</v>
+      </c>
+      <c r="AD185" s="0">
+        <v>69.537880625</v>
       </c>
     </row>
     <row r="186">
@@ -14701,16 +16937,28 @@
         <v>0.025195312500000001</v>
       </c>
       <c r="W186" s="0">
-        <v>0.28137199999999996</v>
+        <v>7203.1231999999991</v>
       </c>
       <c r="X186" s="0">
-        <v>439.47600000000011</v>
+        <v>11250585.600000003</v>
       </c>
       <c r="Y186" s="0">
-        <v>741.27905261999967</v>
+        <v>18976743.747071993</v>
       </c>
       <c r="Z186" s="0">
-        <v>0.0070575441362324279</v>
+        <v>180.67312988755015</v>
+      </c>
+      <c r="AA186" s="0">
+        <v>0.34771610172952377</v>
+      </c>
+      <c r="AB186" s="0">
+        <v>1546.0894979169691</v>
+      </c>
+      <c r="AC186" s="0">
+        <v>1304.4650111340413</v>
+      </c>
+      <c r="AD186" s="0">
+        <v>70.20309890625002</v>
       </c>
     </row>
   </sheetData>

--- a/features.xlsx
+++ b/features.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1071" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2161" uniqueCount="42">
   <si>
     <t>TestNumber</t>
   </si>

--- a/features.xlsx
+++ b/features.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2161" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2379" uniqueCount="50">
   <si>
     <t>TestNumber</t>
   </si>
@@ -140,6 +140,30 @@
   <si>
     <t>Carga_C_</t>
   </si>
+  <si>
+    <t>Energy_J_</t>
+  </si>
+  <si>
+    <t>CycleStart</t>
+  </si>
+  <si>
+    <t>CycleEnd</t>
+  </si>
+  <si>
+    <t>CycleTime</t>
+  </si>
+  <si>
+    <t>RelativeTVmax</t>
+  </si>
+  <si>
+    <t>RelativeTImax</t>
+  </si>
+  <si>
+    <t>RelativeTRmax</t>
+  </si>
+  <si>
+    <t>Charge_C_</t>
+  </si>
 </sst>
 </file>
 
@@ -206,8 +230,8 @@
     <col min="17" max="17" width="12.5546875" customWidth="true"/>
     <col min="18" max="18" width="12.5546875" customWidth="true"/>
     <col min="19" max="19" width="12.5546875" customWidth="true"/>
-    <col min="20" max="20" width="13.21875" customWidth="true"/>
-    <col min="21" max="21" width="12.6640625" customWidth="true"/>
+    <col min="20" max="20" width="13.109375" customWidth="true"/>
+    <col min="21" max="21" width="12.5546875" customWidth="true"/>
     <col min="22" max="22" width="13.21875" customWidth="true"/>
     <col min="23" max="23" width="9.5546875" customWidth="true"/>
     <col min="24" max="24" width="10.5546875" customWidth="true"/>
@@ -248,7 +272,7 @@
         <v>10</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="K1" s="0" t="s">
         <v>22</v>
@@ -269,22 +293,22 @@
         <v>27</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="U1" s="0" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="V1" s="0" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="W1" s="0" t="s">
         <v>34</v>
@@ -308,7 +332,7 @@
         <v>40</v>
       </c>
       <c r="AD1" s="0" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2">
